--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📺 Views" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🎧 Listens" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📱Socials" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👥 Subs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔑 KPIs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Charts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="▶️ Episodics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⭐ Best Of" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="📺 Views" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="🎧 Listens" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="📱Socials" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="👥 Subs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="🔑 KPIs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="🏆 Charts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="▶️ Episodics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="⭐ Best Of" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19725</v>
+        <v>231867</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>698490</v>
+        <v>697914</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>790809</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>400299</v>
+        <v>1211612</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2063548</v>
+        <v>2062452</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>2731804</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1001</v>
+        <v>44011</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>164782</v>
+        <v>164514</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>178277</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>157000</v>
+        <v>158000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156556</v>
+        <v>156388</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153073</v>
+        <v>152905</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148588</v>
+        <v>148420</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142086</v>
+        <v>141918</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>138798</v>
+        <v>138630</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>134950</v>
+        <v>134782</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>123929</v>
+        <v>123761</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119346</v>
+        <v>119178</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>115728</v>
+        <v>115560</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>114724</v>
+        <v>114556</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109629</v>
+        <v>109461</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100614</v>
+        <v>100446</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>96794</v>
+        <v>96626</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93191</v>
+        <v>93023</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92689</v>
+        <v>92521</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89117</v>
+        <v>88949</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87606</v>
+        <v>87438</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87441</v>
+        <v>87273</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87359</v>
+        <v>87191</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86437</v>
+        <v>86269</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86084</v>
+        <v>85916</v>
       </c>
     </row>
     <row r="6">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>58</v>
@@ -6760,31 +6760,31 @@
         <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>38</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="V8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8" s="7" t="n">
         <v>2</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.951</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>421025</v>
+        <v>1487490</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2926820</v>
+        <v>2924880</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>3700890</v>
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1001</v>
+        <v>44011</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>164782</v>
+        <v>164514</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>178277</v>
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 05, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 14, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>61397</v>
+        <v>63266</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1075</v>
+        <v>1094</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Perk SHREDS Rich Paul's Jordan Take, Brunson LOCKED In &amp; Kawhi OVER Pippen</t>
+          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6388</v>
+        <v>40325</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>181</v>
+        <v>838</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,191 +9524,455 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Fever Drama Could Be A BLESSING, Chicago’s Trades Were GHASTLY + 3x WNBA Champ Swin Cash</t>
+          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>25409</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>699</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>24905</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>654</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Cynthia Cooper: NEVER Call Out Teammates Publicly + Olivia Miles Has TAKEN OVER In Minnesota</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>7135</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SEGMENT CLIPS</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>476</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>47469</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>659</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SEGMENT CLIPS</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>14905</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>"Hit Him In THE RIBS" - Do The Knicks Need An ENFORCER For Wemby?</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>10777</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>243</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>What Brunson Told RJ After the Game 3 Loss</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>OG Or Brunson? The Crew CAN'T Agree On Finals MVP</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>3131</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Why OG Anunoby at the 5 Is the Knicks' Most LETHAL Lineup</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="D19" s="7" t="n">
+        <v>481909</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>18094</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>384129</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>14560</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>134303</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>3543</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Is Wemby Overrated? NBA Champion Robert Horry Says Pump the Brakes On the hype Train #nba</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>23179</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>524</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>121183</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Jalen Brunson GREATEST KNICK EVER!? Kendrick Perkins Thinks So #NBA #nyknicks #nbafinals</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>5120</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>162</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>95280</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Is Jalen Brunson a Superstar? #NBA #Knicks #NewYorkKnicks #basketball</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>59508</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>834</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9716,9 +9980,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25409</v>
+        <v>25496</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24905</v>
+        <v>24911</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7135</v>
+        <v>7147</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>219</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>47469</v>
+        <v>47743</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>14905</v>
+        <v>15790</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>10777</v>
+        <v>10778</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>243</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6088</v>
+        <v>6090</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>108</v>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>481909</v>
+        <v>481950</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18094</v>
+        <v>18097</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>134303</v>
+        <v>139275</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3543</v>
+        <v>3638</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>121183</v>
+        <v>121376</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2150</v>
+        <v>2154</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>95280</v>
+        <v>95401</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>59508</v>
+        <v>60336</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>834</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 14, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 15, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63266</v>
+        <v>63283</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40325</v>
+        <v>40369</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>838</v>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25496</v>
+        <v>25898</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24911</v>
+        <v>24943</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7147</v>
+        <v>7293</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>47743</v>
+        <v>50137</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15790</v>
+        <v>25806</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>10778</v>
+        <v>10782</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>243</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6090</v>
+        <v>6101</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>108</v>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3131</v>
+        <v>3233</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>64</v>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>481950</v>
+        <v>482574</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18097</v>
+        <v>18140</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>139275</v>
+        <v>170425</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3638</v>
+        <v>4453</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>121376</v>
+        <v>122174</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>95401</v>
+        <v>96359</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>60336</v>
+        <v>65095</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>834</v>
+        <v>920</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40369</v>
+        <v>40371</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>838</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25898</v>
+        <v>25900</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>704</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>50137</v>
+        <v>50199</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>25806</v>
+        <v>25871</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>292</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>108</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>170425</v>
+        <v>171232</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4453</v>
+        <v>4467</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>122174</v>
+        <v>122180</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2158</v>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>96359</v>
+        <v>96376</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>1073</v>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>65095</v>
+        <v>65261</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>231867</v>
+        <v>252374</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1211612</v>
+        <v>1379636</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>44011</v>
+        <v>52957</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>158000</v>
+        <v>159000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156388</v>
+        <v>157229</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>152905</v>
+        <v>153746</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148420</v>
+        <v>149261</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>141918</v>
+        <v>142759</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>138630</v>
+        <v>139471</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>134782</v>
+        <v>135623</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>123761</v>
+        <v>124602</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119178</v>
+        <v>120019</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>115560</v>
+        <v>116401</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>114556</v>
+        <v>115397</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109461</v>
+        <v>110302</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100446</v>
+        <v>101287</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>96626</v>
+        <v>97467</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93023</v>
+        <v>93864</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92521</v>
+        <v>93362</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>88949</v>
+        <v>89790</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87438</v>
+        <v>88279</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87273</v>
+        <v>88114</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87191</v>
+        <v>88032</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86269</v>
+        <v>87110</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>85916</v>
+        <v>86757</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>38</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1487490</v>
+        <v>1684967</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>44011</v>
+        <v>52957</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 15, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 16, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63283</v>
+        <v>63305</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1093</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40371</v>
+        <v>40437</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>838</v>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25900</v>
+        <v>26290</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24943</v>
+        <v>24998</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>652</v>
@@ -9590,19 +9590,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Cynthia Cooper: NEVER Call Out Teammates Publicly + Olivia Miles Has TAKEN OVER In Minnesota</t>
+          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7293</v>
+        <v>15021</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>221</v>
+        <v>592</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>50199</v>
+        <v>53759</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>686</v>
+        <v>736</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
+          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>25871</v>
+        <v>33178</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>292</v>
+        <v>823</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>"Hit Him In THE RIBS" - Do The Knicks Need An ENFORCER For Wemby?</t>
+          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>10782</v>
+        <v>28090</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>243</v>
+        <v>308</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>What Brunson Told RJ After the Game 3 Loss</t>
+          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6102</v>
+        <v>14466</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>108</v>
+        <v>426</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>OG Or Brunson? The Crew CAN'T Agree On Finals MVP</t>
+          <t>"Hit Him In THE RIBS" - Do The Knicks Need An ENFORCER For Wemby?</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3233</v>
+        <v>10794</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>482574</v>
+        <v>483093</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18140</v>
+        <v>18159</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>171232</v>
+        <v>195151</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4467</v>
+        <v>5035</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>122180</v>
+        <v>122947</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2158</v>
+        <v>2163</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>96376</v>
+        <v>100708</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1073</v>
+        <v>1136</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>65261</v>
+        <v>69585</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>921</v>
+        <v>961</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>252374</v>
+        <v>275451</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1379636</v>
+        <v>1469884</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>52957</v>
+        <v>53944</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>159000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157229</v>
+        <v>157160</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153746</v>
+        <v>153677</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149261</v>
+        <v>149192</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142759</v>
+        <v>142690</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139471</v>
+        <v>139402</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135623</v>
+        <v>135554</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124602</v>
+        <v>124533</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>120019</v>
+        <v>119950</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116401</v>
+        <v>116332</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115397</v>
+        <v>115328</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110302</v>
+        <v>110233</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101287</v>
+        <v>101218</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97467</v>
+        <v>97398</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93864</v>
+        <v>93795</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93362</v>
+        <v>93293</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89790</v>
+        <v>89721</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88279</v>
+        <v>88210</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88114</v>
+        <v>88045</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88032</v>
+        <v>87963</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87110</v>
+        <v>87041</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86757</v>
+        <v>86688</v>
       </c>
     </row>
     <row r="6">
@@ -6748,37 +6748,37 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>36</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.819</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1684967</v>
+        <v>1799279</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>52957</v>
+        <v>53944</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 16, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 17, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9458,19 +9458,19 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Knicks vs Spurs NBA Finals PREVIEW w/ James Worthy, Robert Horry &amp; DeAndre Jordan</t>
+          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63305</v>
+        <v>40496</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1093</v>
+        <v>838</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
+          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40437</v>
+        <v>26557</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>838</v>
+        <v>709</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
+          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26290</v>
+        <v>25022</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>708</v>
+        <v>652</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
+          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24998</v>
+        <v>18209</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>652</v>
+        <v>678</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9590,19 +9590,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
+          <t>Cynthia Cooper: NEVER Call Out Teammates Publicly + Olivia Miles Has TAKEN OVER In Minnesota</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>15021</v>
+        <v>7566</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>592</v>
+        <v>225</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>53759</v>
+        <v>55657</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>33178</v>
+        <v>51245</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>823</v>
+        <v>1155</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
+          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>28090</v>
+        <v>29127</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>308</v>
+        <v>652</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
+          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>14466</v>
+        <v>28640</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>426</v>
+        <v>310</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>"Hit Him In THE RIBS" - Do The Knicks Need An ENFORCER For Wemby?</t>
+          <t>Tracy Morgan: "I Cried Like A Baby" After The Knicks Won The Title</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>10794</v>
+        <v>15883</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>244</v>
+        <v>524</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>483093</v>
+        <v>483619</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18159</v>
+        <v>18180</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>195151</v>
+        <v>228729</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5035</v>
+        <v>5755</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>122947</v>
+        <v>123269</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2163</v>
+        <v>2168</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>100708</v>
+        <v>103745</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1136</v>
+        <v>1170</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>69585</v>
+        <v>75497</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>961</v>
+        <v>1026</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>275451</v>
+        <v>325225</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1469884</v>
+        <v>1541668</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>53944</v>
+        <v>68963</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5605,67 +5605,67 @@
         <v>159000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157160</v>
+        <v>156888</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153677</v>
+        <v>153405</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149192</v>
+        <v>148920</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142690</v>
+        <v>142418</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139402</v>
+        <v>139130</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135554</v>
+        <v>135282</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124533</v>
+        <v>124261</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119950</v>
+        <v>119678</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116332</v>
+        <v>116060</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115328</v>
+        <v>115056</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110233</v>
+        <v>109961</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101218</v>
+        <v>100946</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97398</v>
+        <v>97126</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93795</v>
+        <v>93523</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93293</v>
+        <v>93021</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89721</v>
+        <v>89449</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88210</v>
+        <v>87938</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88045</v>
+        <v>87773</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87963</v>
+        <v>87691</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87041</v>
+        <v>86769</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86688</v>
+        <v>86416</v>
       </c>
     </row>
     <row r="6">
@@ -6748,40 +6748,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>56</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>38</v>
-      </c>
       <c r="J8" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1799279</v>
+        <v>1935856</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>53944</v>
+        <v>68963</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 17, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 18, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9458,19 +9458,19 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
+          <t>Knicks vs Spurs NBA Finals PREVIEW w/ James Worthy, Robert Horry &amp; DeAndre Jordan</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>40496</v>
+        <v>63346</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>838</v>
+        <v>1093</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
+          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26557</v>
+        <v>40546</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>709</v>
+        <v>840</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
+          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25022</v>
+        <v>26701</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>652</v>
+        <v>714</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
+          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>18209</v>
+        <v>25042</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>678</v>
+        <v>653</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9590,19 +9590,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Cynthia Cooper: NEVER Call Out Teammates Publicly + Olivia Miles Has TAKEN OVER In Minnesota</t>
+          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7566</v>
+        <v>19353</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>225</v>
+        <v>698</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9636,19 +9636,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
+          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>55657</v>
+        <v>59307</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>752</v>
+        <v>1318</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
+          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>51245</v>
+        <v>57138</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1155</v>
+        <v>775</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>29127</v>
+        <v>35728</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>652</v>
+        <v>778</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>28640</v>
+        <v>29215</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>15883</v>
+        <v>23643</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>524</v>
+        <v>737</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>483619</v>
+        <v>484046</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18180</v>
+        <v>18197</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>228729</v>
+        <v>238851</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5755</v>
+        <v>5969</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>123269</v>
+        <v>123492</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>103745</v>
+        <v>105345</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1170</v>
+        <v>1193</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>75497</v>
+        <v>79150</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26701</v>
+        <v>26711</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>714</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19353</v>
+        <v>19350</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>698</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>59307</v>
+        <v>59351</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>35728</v>
+        <v>35803</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Tracy Morgan: "I Cried Like A Baby" After The Knicks Won The Title</t>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>23643</v>
+        <v>24383</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>737</v>
+        <v>699</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>484046</v>
+        <v>484096</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>18197</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>238851</v>
+        <v>239100</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5969</v>
+        <v>5974</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>123492</v>
+        <v>123521</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2172</v>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>105345</v>
+        <v>105326</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>1193</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>325225</v>
+        <v>407308</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1541668</v>
+        <v>1651964</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>68963</v>
+        <v>73097</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>159000</v>
+        <v>160000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156888</v>
+        <v>157440</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153405</v>
+        <v>153957</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148920</v>
+        <v>149472</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142418</v>
+        <v>142970</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139130</v>
+        <v>139682</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135282</v>
+        <v>135834</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124261</v>
+        <v>124813</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119678</v>
+        <v>120230</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116060</v>
+        <v>116612</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115056</v>
+        <v>115608</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109961</v>
+        <v>110513</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100946</v>
+        <v>101498</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97126</v>
+        <v>97678</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93523</v>
+        <v>94075</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93021</v>
+        <v>93573</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89449</v>
+        <v>90001</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87938</v>
+        <v>88490</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87773</v>
+        <v>88325</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87691</v>
+        <v>88243</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86769</v>
+        <v>87321</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86416</v>
+        <v>86968</v>
       </c>
     </row>
     <row r="6">
@@ -6748,28 +6748,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>28</v>
@@ -6778,10 +6778,10 @@
         <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
@@ -6796,7 +6796,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>14</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.796</v>
+        <v>0.775</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1935856</v>
+        <v>2132369</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>68963</v>
+        <v>73097</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 18, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 19, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63346</v>
+        <v>63360</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1093</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40546</v>
+        <v>40613</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26711</v>
+        <v>26821</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25042</v>
+        <v>25056</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19350</v>
+        <v>19666</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>59351</v>
+        <v>61623</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1319</v>
+        <v>1363</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>57138</v>
+        <v>57703</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>35803</v>
+        <v>48245</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>781</v>
+        <v>1148</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
+          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>29215</v>
+        <v>38422</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>312</v>
+        <v>827</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
+          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>24383</v>
+        <v>29301</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>699</v>
+        <v>314</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>484096</v>
+        <v>484616</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18197</v>
+        <v>18215</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>239100</v>
+        <v>243765</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5974</v>
+        <v>6088</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
+          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>123521</v>
+        <v>146256</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2172</v>
+        <v>8713</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>105326</v>
+        <v>105884</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Is Jalen Brunson a Superstar? #NBA #Knicks #NewYorkKnicks #basketball</t>
+          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>79150</v>
+        <v>83902</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1059</v>
+        <v>1085</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>407308</v>
+        <v>463223</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1651964</v>
+        <v>1797787</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>73097</v>
+        <v>80495</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>160000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157440</v>
+        <v>157103</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153957</v>
+        <v>153620</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149472</v>
+        <v>149135</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142970</v>
+        <v>142633</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139682</v>
+        <v>139345</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135834</v>
+        <v>135497</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124813</v>
+        <v>124476</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>120230</v>
+        <v>119893</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116612</v>
+        <v>116275</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115608</v>
+        <v>115271</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110513</v>
+        <v>110176</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101498</v>
+        <v>101161</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97678</v>
+        <v>97341</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>94075</v>
+        <v>93738</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93573</v>
+        <v>93236</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>90001</v>
+        <v>89664</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88490</v>
+        <v>88153</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88325</v>
+        <v>87988</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88243</v>
+        <v>87906</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87321</v>
+        <v>86984</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86968</v>
+        <v>86631</v>
       </c>
     </row>
     <row r="6">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>52</v>
@@ -6760,34 +6760,34 @@
         <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>35</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>38</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>11</v>
@@ -6796,7 +6796,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>14</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.775</v>
+        <v>0.768</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2132369</v>
+        <v>2341505</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>73097</v>
+        <v>80495</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 19, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 20, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63360</v>
+        <v>63368</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40613</v>
+        <v>40679</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26821</v>
+        <v>26890</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>715</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25056</v>
+        <v>25076</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19666</v>
+        <v>19952</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>61623</v>
+        <v>63210</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1363</v>
+        <v>1382</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>57703</v>
+        <v>58051</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>48245</v>
+        <v>57671</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1148</v>
+        <v>1329</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>38422</v>
+        <v>40478</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>The Media Is Wrong About The Spurs — Perk Explains Why</t>
+          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29301</v>
+        <v>32715</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>314</v>
+        <v>650</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>484616</v>
+        <v>485097</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18215</v>
+        <v>18226</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>243765</v>
+        <v>253345</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6088</v>
+        <v>6340</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>146256</v>
+        <v>236131</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8713</v>
+        <v>12571</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9913,19 +9913,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>105884</v>
+        <v>124020</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1197</v>
+        <v>2179</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
+          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>83902</v>
+        <v>106176</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1085</v>
+        <v>1204</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>463223</v>
+        <v>522650</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1797787</v>
+        <v>2062338</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80495</v>
+        <v>82796</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>160000</v>
+        <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157103</v>
+        <v>157617</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153620</v>
+        <v>154134</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149135</v>
+        <v>149649</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142633</v>
+        <v>143147</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139345</v>
+        <v>139859</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135497</v>
+        <v>136011</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124476</v>
+        <v>124990</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119893</v>
+        <v>120407</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116275</v>
+        <v>116789</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115271</v>
+        <v>115785</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110176</v>
+        <v>110690</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101161</v>
+        <v>101675</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97341</v>
+        <v>97855</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93738</v>
+        <v>94252</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93236</v>
+        <v>93750</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89664</v>
+        <v>90178</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88153</v>
+        <v>88667</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87988</v>
+        <v>88502</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87906</v>
+        <v>88420</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86984</v>
+        <v>87498</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86631</v>
+        <v>87145</v>
       </c>
     </row>
     <row r="6">
@@ -6748,28 +6748,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>52</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>29</v>
@@ -6778,7 +6778,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>38</v>
@@ -6787,7 +6787,7 @@
         <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>11</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.768</v>
+        <v>0.773</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2341505</v>
+        <v>2667784</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80495</v>
+        <v>82796</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 20, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 21, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63368</v>
+        <v>63382</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40679</v>
+        <v>40754</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26890</v>
+        <v>26933</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25076</v>
+        <v>25083</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19952</v>
+        <v>20122</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>63210</v>
+        <v>64434</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1382</v>
+        <v>1411</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>58051</v>
+        <v>63565</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>789</v>
+        <v>1463</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
+          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>57671</v>
+        <v>58217</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1329</v>
+        <v>791</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
+          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>40478</v>
+        <v>52720</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>856</v>
+        <v>908</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
+          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>32715</v>
+        <v>41690</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>650</v>
+        <v>876</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>485097</v>
+        <v>485405</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18226</v>
+        <v>18235</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
+          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>253345</v>
+        <v>260183</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6340</v>
+        <v>14026</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
+          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>236131</v>
+        <v>256134</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>12571</v>
+        <v>6392</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124020</v>
+        <v>124176</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>106176</v>
+        <v>106409</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>522650</v>
+        <v>574647</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2062338</v>
+        <v>2274027</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>82796</v>
+        <v>84025</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157617</v>
+        <v>157237</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>154134</v>
+        <v>153754</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149649</v>
+        <v>149269</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>143147</v>
+        <v>142767</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139859</v>
+        <v>139479</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>136011</v>
+        <v>135631</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124990</v>
+        <v>124610</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>120407</v>
+        <v>120027</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116789</v>
+        <v>116409</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115785</v>
+        <v>115405</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110690</v>
+        <v>110310</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101675</v>
+        <v>101295</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97855</v>
+        <v>97475</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>94252</v>
+        <v>93872</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93750</v>
+        <v>93370</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>90178</v>
+        <v>89798</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88667</v>
+        <v>88287</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88502</v>
+        <v>88122</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88420</v>
+        <v>88040</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87498</v>
+        <v>87118</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87145</v>
+        <v>86765</v>
       </c>
     </row>
     <row r="6">
@@ -6751,19 +6751,19 @@
         <v>40</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>24</v>
@@ -6772,7 +6772,7 @@
         <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>24</v>
@@ -6784,10 +6784,10 @@
         <v>38</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>11</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2667784</v>
+        <v>2932699</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>82796</v>
+        <v>84025</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 21, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 22, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63382</v>
+        <v>63394</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40754</v>
+        <v>40777</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26933</v>
+        <v>26975</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>716</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25083</v>
+        <v>25097</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20122</v>
+        <v>20334</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9636,19 +9636,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>64434</v>
+        <v>67430</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1411</v>
+        <v>1549</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
+          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>63565</v>
+        <v>66245</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1463</v>
+        <v>1443</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
+          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>58217</v>
+        <v>66052</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>791</v>
+        <v>1044</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
+          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>52720</v>
+        <v>58280</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>908</v>
+        <v>792</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>41690</v>
+        <v>43464</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>485405</v>
+        <v>485568</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18235</v>
+        <v>18242</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>260183</v>
+        <v>272439</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>14026</v>
+        <v>14691</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>256134</v>
+        <v>257181</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6392</v>
+        <v>6414</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124176</v>
+        <v>124326</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>106409</v>
+        <v>102726</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1210</v>
+        <v>1333</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,9 +119,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -696,7 +693,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -768,71 +765,115 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>574647</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>697914</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>790809</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>999377</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>456937</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>733899</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>1819209</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>1237011</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>951387</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>461276</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>1296821</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>1515762</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>606682</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>629557</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>115398</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>322450</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>87239</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>67472</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>48198</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>114534</v>
-      </c>
-      <c r="V5" s="7" t="n">
-        <v>75408</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>55180</v>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -841,71 +882,115 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>2274027</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>2062452</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>2731804</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2437458</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>1412041</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1021398</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>1102899</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>920589</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>542576</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>390738</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>1348061</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>2030353</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>545861</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>130006</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>89465</v>
-      </c>
-      <c r="Q6" s="7" t="n">
-        <v>90474</v>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v>56970</v>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>34237</v>
-      </c>
-      <c r="T6" s="7" t="n">
-        <v>24015</v>
-      </c>
-      <c r="U6" s="7" t="n">
-        <v>17758</v>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>11180</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>9896</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -914,71 +999,115 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>84025</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>164514</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>178277</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>211738</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>209927</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>90638</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>365</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>405</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>381</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>220</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>386</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>697</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>37296</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>4972</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>7173</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>1399</v>
-      </c>
-      <c r="R7" s="7" t="n">
-        <v>78402</v>
-      </c>
-      <c r="S7" s="7" t="n">
-        <v>3965</v>
-      </c>
-      <c r="T7" s="7" t="n">
-        <v>11199</v>
-      </c>
-      <c r="U7" s="7" t="n">
-        <v>40604</v>
-      </c>
-      <c r="V7" s="7" t="n">
-        <v>33838</v>
-      </c>
-      <c r="W7" s="7" t="n">
-        <v>1926</v>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -987,104 +1116,104 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>23182</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>25288</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>24712</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>22620</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1394,7 +1523,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -2116,112 +2245,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2233,112 +2362,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2350,112 +2479,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2701,112 +2830,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2818,112 +2947,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2935,112 +3064,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3286,112 +3415,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3403,112 +3532,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3520,112 +3649,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3871,112 +4000,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3988,112 +4117,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4105,112 +4234,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4456,112 +4585,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4573,112 +4702,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4690,112 +4819,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4924,112 +5053,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5041,112 +5170,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5158,112 +5287,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5605,67 +5734,67 @@
         <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157237</v>
+        <v>156992</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153754</v>
+        <v>153509</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149269</v>
+        <v>149024</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142767</v>
+        <v>142522</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139479</v>
+        <v>139234</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135631</v>
+        <v>135386</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124610</v>
+        <v>124365</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>120027</v>
+        <v>119782</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116409</v>
+        <v>116164</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115405</v>
+        <v>115160</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110310</v>
+        <v>110065</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101295</v>
+        <v>101050</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97475</v>
+        <v>97230</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93872</v>
+        <v>93627</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93370</v>
+        <v>93125</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89798</v>
+        <v>89553</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88287</v>
+        <v>88042</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88122</v>
+        <v>87877</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88040</v>
+        <v>87795</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87118</v>
+        <v>86873</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86765</v>
+        <v>86520</v>
       </c>
     </row>
     <row r="6">
@@ -5674,91 +5803,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="8">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="8">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="8">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="8">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="8">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="8">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="8">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="8">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="8">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="8">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="8">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="8">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5777,112 +5906,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5894,112 +6023,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6106,91 +6235,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="8">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="8">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="8">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="8">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="8">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="8">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="8">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="8">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="8">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="8">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="8">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="8">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="8">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="8">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6747,70 +6876,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="B8" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" s="7" t="n">
+      <c r="E8" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="M8" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="N8" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="K8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="P8" s="7" t="n">
+      <c r="O8" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" s="7" t="n">
+      <c r="Q8" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="R8" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="S8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="T8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="U8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="7" t="n">
+      <c r="V8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="W8" s="7" t="n">
+      <c r="W8" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6820,71 +6949,115 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="R9" s="12" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="S9" s="12" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="U9" s="12" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="V9" s="12" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.148</v>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -8243,27 +8416,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>VIEWS PER</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>TAPED + LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="14" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8383,112 +8556,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8612,112 +8785,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8841,112 +9014,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8958,95 +9131,139 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>2932699</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2924880</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3700890</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>3648573</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2078905</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1845935</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>2922473</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>2158005</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>1494344</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>852234</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>2645268</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>3546812</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>1189839</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>764535</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>212036</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>414323</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>222611</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>105674</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>83412</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>172896</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>120426</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>67002</v>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>LIVES</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9171,71 +9388,115 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>84025</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>164514</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>178277</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>211738</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>209927</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>90638</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>365</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>405</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>381</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>220</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>386</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>697</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>37296</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>4972</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>7173</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>1399</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>78402</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>3965</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>11199</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>40604</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>33838</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>1926</v>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -9390,7 +9651,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 22, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 23, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9401,83 +9662,83 @@
       <c r="G1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Views</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Likes</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Show</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>★ TOP FULL EPISODES</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Knicks vs Spurs NBA Finals PREVIEW w/ James Worthy, Robert Horry &amp; DeAndre Jordan</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>63394</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="D5" s="8" t="n">
+        <v>63403</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>1092</v>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9489,7 +9750,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
@@ -9500,7 +9761,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40777</v>
+        <v>40792</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9517,33 +9778,33 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>26975</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>716</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="8" t="n">
+        <v>27001</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>717</v>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9555,7 +9816,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
@@ -9566,7 +9827,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25097</v>
+        <v>25104</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9583,79 +9844,79 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>20334</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>716</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D9" s="8" t="n">
+        <v>20464</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>719</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>67430</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1549</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>71998</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9667,61 +9928,61 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>69032</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1582</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>66245</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1443</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="D14" s="8" t="n">
+        <v>66824</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>66052</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1044</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9733,7 +9994,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
         </is>
@@ -9744,10 +10005,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58280</v>
+        <v>58339</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9761,79 +10022,79 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>43464</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="D16" s="8" t="n">
+        <v>44166</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>908</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
-        <v>485568</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>18242</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="D19" s="8" t="n">
+        <v>485678</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>18245</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9845,7 +10106,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
@@ -9856,10 +10117,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>272439</v>
+        <v>279412</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>14691</v>
+        <v>15056</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9873,33 +10134,33 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>257181</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>6414</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="D21" s="8" t="n">
+        <v>258057</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9911,7 +10172,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
         </is>
@@ -9922,10 +10183,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124326</v>
+        <v>124472</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9939,40 +10200,40 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>102726</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>1333</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>106817</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +119,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -765,115 +768,71 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B5" s="7" t="n">
+        <v>617509</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>697914</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>790809</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>999377</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>456937</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>733899</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1819209</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1237011</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>951387</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>461276</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>1296821</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>1515762</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>606682</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>629557</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>115398</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>322450</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>87239</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>67472</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>48198</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>114534</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>75408</v>
+      </c>
+      <c r="W5" s="7" t="n">
+        <v>55180</v>
       </c>
     </row>
     <row r="6">
@@ -882,115 +841,71 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B6" s="7" t="n">
+        <v>2361549</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2062452</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2731804</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2437458</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1412041</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1021398</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1102899</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>920589</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>542576</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>390738</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>1348061</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>2030353</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>545861</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>130006</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>89465</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>90474</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>56970</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>34237</v>
+      </c>
+      <c r="T6" s="7" t="n">
+        <v>24015</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>17758</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>11180</v>
+      </c>
+      <c r="W6" s="7" t="n">
+        <v>9896</v>
       </c>
     </row>
     <row r="7">
@@ -999,115 +914,71 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>84797</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>164514</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>178277</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>211738</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>209927</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>90638</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>365</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>405</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>381</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>386</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>697</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>37296</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>4972</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>7173</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>1399</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>78402</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>3965</v>
+      </c>
+      <c r="T7" s="7" t="n">
+        <v>11199</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>40604</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>33838</v>
+      </c>
+      <c r="W7" s="7" t="n">
+        <v>1926</v>
       </c>
     </row>
     <row r="8">
@@ -1116,104 +987,104 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>23182</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>25288</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>24712</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>22620</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2245,112 +2116,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2362,112 +2233,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2479,112 +2350,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2830,112 +2701,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2947,112 +2818,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3064,112 +2935,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3415,112 +3286,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3532,112 +3403,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3649,112 +3520,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4000,112 +3871,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4117,112 +3988,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4234,112 +4105,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4585,112 +4456,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4702,112 +4573,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4819,112 +4690,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5053,112 +4924,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5170,112 +5041,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5287,112 +5158,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5803,91 +5674,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="7">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5906,112 +5777,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6023,112 +5894,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6235,91 +6106,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="7">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="7">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="7">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="7">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6876,70 +6747,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="K8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="O8" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="P8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" s="8" t="n">
+      <c r="Q8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6949,115 +6820,71 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="12" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T9" s="12" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="U9" s="12" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="10">
@@ -8416,27 +8243,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>VIEWS PER</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>TAPED + LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8556,112 +8383,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8785,112 +8612,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9014,112 +8841,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9131,139 +8958,95 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="6" t="n">
+        <v>3063855</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2924880</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>3700890</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3648573</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>2078905</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1845935</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>2922473</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>2158005</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>1494344</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>852234</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>2645268</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>3546812</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>1189839</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>764535</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>212036</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>414323</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>222611</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>105674</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>83412</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>172896</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>120426</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>67002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>LIVES</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9388,115 +9171,71 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C14" s="6" t="n">
+        <v>84797</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>164514</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>178277</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>211738</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>209927</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>90638</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>405</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>697</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>37296</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>4972</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>7173</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>1399</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>78402</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>3965</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>11199</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>40604</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>33838</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>1926</v>
       </c>
     </row>
     <row r="15">
@@ -9662,83 +9401,83 @@
       <c r="G1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Views</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Likes</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>Show</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>★ TOP FULL EPISODES</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Knicks vs Spurs NBA Finals PREVIEW w/ James Worthy, Robert Horry &amp; DeAndre Jordan</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>63403</v>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="D5" s="7" t="n">
+        <v>63405</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>1092</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9750,7 +9489,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
@@ -9761,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40792</v>
+        <v>40797</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9778,33 +9517,33 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>27001</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="D7" s="7" t="n">
+        <v>27010</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>717</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9816,7 +9555,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
@@ -9827,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25104</v>
+        <v>25105</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9844,79 +9583,79 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>20464</v>
-      </c>
-      <c r="E9" s="8" t="n">
+      <c r="D9" s="7" t="n">
+        <v>20479</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>719</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>71998</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>1118</v>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>73416</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1139</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9928,7 +9667,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
@@ -9939,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>69032</v>
+        <v>69323</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1582</v>
+        <v>1596</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9956,33 +9695,33 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>66824</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="D14" s="7" t="n">
+        <v>66895</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9994,7 +9733,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
         </is>
@@ -10005,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58339</v>
+        <v>58342</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -10022,79 +9761,79 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>44166</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>908</v>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="D16" s="7" t="n">
+        <v>44262</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>911</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>485678</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>18245</v>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="D19" s="7" t="n">
+        <v>485714</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>18247</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -10106,7 +9845,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
@@ -10117,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>279412</v>
+        <v>280811</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15056</v>
+        <v>15132</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -10134,33 +9873,33 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>258057</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>6427</v>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="D21" s="7" t="n">
+        <v>258114</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -10172,7 +9911,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
         </is>
@@ -10183,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124472</v>
+        <v>124502</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -10200,40 +9939,40 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>106817</v>
-      </c>
-      <c r="E23" s="8" t="n">
+      <c r="D23" s="7" t="n">
+        <v>106834</v>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>1214</v>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40797</v>
+        <v>40798</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25105</v>
+        <v>25106</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>73416</v>
+        <v>73452</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1139</v>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>69323</v>
+        <v>69328</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>1596</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58342</v>
+        <v>58343</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44262</v>
+        <v>44267</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>911</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>280811</v>
+        <v>280836</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15132</v>
+        <v>15135</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>106834</v>
+        <v>106824</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>1214</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6751,16 +6751,16 @@
         <v>42</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>50</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>37</v>
@@ -6772,10 +6772,10 @@
         <v>41</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>28</v>
@@ -6784,7 +6784,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27010</v>
+        <v>27011</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>717</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25106</v>
+        <v>25105</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>654</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20479</v>
+        <v>20487</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>719</v>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>73452</v>
+        <v>73557</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1139</v>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>69328</v>
+        <v>69352</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>1596</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58343</v>
+        <v>58352</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44267</v>
+        <v>44272</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>911</v>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>485714</v>
+        <v>485719</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>18247</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>280836</v>
+        <v>280901</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15135</v>
+        <v>15141</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>258114</v>
+        <v>258116</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>6431</v>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124502</v>
+        <v>124507</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>106824</v>
+        <v>106842</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>617509</v>
+        <v>653828</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2361549</v>
+        <v>2410232</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>84797</v>
+        <v>85484</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156992</v>
+        <v>156824</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153509</v>
+        <v>153341</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149024</v>
+        <v>148856</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142522</v>
+        <v>142354</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139234</v>
+        <v>139066</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135386</v>
+        <v>135218</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124365</v>
+        <v>124197</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119782</v>
+        <v>119614</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116164</v>
+        <v>115996</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115160</v>
+        <v>114992</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110065</v>
+        <v>109897</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101050</v>
+        <v>100882</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97230</v>
+        <v>97062</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93627</v>
+        <v>93459</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93125</v>
+        <v>92957</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89553</v>
+        <v>89385</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88042</v>
+        <v>87874</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87877</v>
+        <v>87709</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87795</v>
+        <v>87627</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86873</v>
+        <v>86705</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86520</v>
+        <v>86352</v>
       </c>
     </row>
     <row r="6">
@@ -6748,40 +6748,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>32</v>
       </c>
       <c r="G8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>37</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>35</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.771</v>
+        <v>0.765</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3063855</v>
+        <v>3149544</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>84797</v>
+        <v>85484</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 23, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 24, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63405</v>
+        <v>63409</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40798</v>
+        <v>40810</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27011</v>
+        <v>27033</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>717</v>
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25105</v>
+        <v>25110</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20487</v>
+        <v>20556</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>719</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>73557</v>
+        <v>77898</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1139</v>
+        <v>1173</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>69352</v>
+        <v>70320</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1596</v>
+        <v>1611</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>66895</v>
+        <v>67199</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58352</v>
+        <v>58395</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44272</v>
+        <v>44577</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>485719</v>
+        <v>485840</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18247</v>
+        <v>18249</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>280901</v>
+        <v>283107</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15141</v>
+        <v>15269</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>258116</v>
+        <v>258342</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6431</v>
+        <v>6436</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9913,19 +9913,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
+          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124507</v>
+        <v>144537</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2190</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>106842</v>
+        <v>124674</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1215</v>
+        <v>2194</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>653828</v>
+        <v>685020</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2410232</v>
+        <v>2486993</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>85484</v>
+        <v>96433</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156824</v>
+        <v>156637</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153341</v>
+        <v>153154</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148856</v>
+        <v>148669</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142354</v>
+        <v>142167</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139066</v>
+        <v>138879</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135218</v>
+        <v>135031</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124197</v>
+        <v>124010</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119614</v>
+        <v>119427</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>115996</v>
+        <v>115809</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>114992</v>
+        <v>114805</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109897</v>
+        <v>109710</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100882</v>
+        <v>100695</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97062</v>
+        <v>96875</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93459</v>
+        <v>93272</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92957</v>
+        <v>92770</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89385</v>
+        <v>89198</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87874</v>
+        <v>87687</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87709</v>
+        <v>87522</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87627</v>
+        <v>87440</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86705</v>
+        <v>86518</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86352</v>
+        <v>86165</v>
       </c>
     </row>
     <row r="6">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>25</v>
@@ -6793,7 +6793,7 @@
         <v>11</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>13</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.765</v>
+        <v>0.761</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3149544</v>
+        <v>3268446</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>85484</v>
+        <v>96433</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 24, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 25, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63409</v>
+        <v>63421</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40810</v>
+        <v>40819</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27033</v>
+        <v>27058</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>717</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25110</v>
+        <v>25117</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>653</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20556</v>
+        <v>20603</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>77898</v>
+        <v>79527</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>70320</v>
+        <v>71279</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1611</v>
+        <v>1624</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67199</v>
+        <v>67456</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58395</v>
+        <v>58397</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44577</v>
+        <v>44876</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>485840</v>
+        <v>486041</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18249</v>
+        <v>18259</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>283107</v>
+        <v>285715</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15269</v>
+        <v>15422</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>258342</v>
+        <v>258717</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6436</v>
+        <v>6446</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>144537</v>
+        <v>240237</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3000</v>
+        <v>4589</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>124674</v>
+        <v>124802</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2194</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>685020</v>
+        <v>716325</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2486993</v>
+        <v>2658998</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>96433</v>
+        <v>99115</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5605,67 +5605,67 @@
         <v>161000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156637</v>
+        <v>156449</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153154</v>
+        <v>152966</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148669</v>
+        <v>148481</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142167</v>
+        <v>141979</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>138879</v>
+        <v>138691</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135031</v>
+        <v>134843</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124010</v>
+        <v>123822</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119427</v>
+        <v>119239</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>115809</v>
+        <v>115621</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>114805</v>
+        <v>114617</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109710</v>
+        <v>109522</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100695</v>
+        <v>100507</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>96875</v>
+        <v>96687</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93272</v>
+        <v>93084</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92770</v>
+        <v>92582</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89198</v>
+        <v>89010</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87687</v>
+        <v>87499</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87522</v>
+        <v>87334</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87440</v>
+        <v>87252</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86518</v>
+        <v>86330</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86165</v>
+        <v>85977</v>
       </c>
     </row>
     <row r="6">
@@ -6748,34 +6748,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>55</v>
-      </c>
       <c r="F8" s="7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>40</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>27</v>
@@ -6784,7 +6784,7 @@
         <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6793,7 +6793,7 @@
         <v>11</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>13</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.761</v>
+        <v>0.765</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3268446</v>
+        <v>3474438</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>96433</v>
+        <v>99115</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 25, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 26, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63421</v>
+        <v>63432</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40819</v>
+        <v>40835</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27058</v>
+        <v>27086</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>717</v>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
+          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25117</v>
+        <v>26893</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>653</v>
+        <v>888</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9590,19 +9590,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
+          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20603</v>
+        <v>25123</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>720</v>
+        <v>653</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>79527</v>
+        <v>79942</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>71279</v>
+        <v>71795</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67456</v>
+        <v>67551</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58397</v>
+        <v>58403</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>794</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44876</v>
+        <v>45023</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>486041</v>
+        <v>486147</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18259</v>
+        <v>18266</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
+          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>285715</v>
+        <v>301451</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15422</v>
+        <v>5373</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
+          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>258717</v>
+        <v>287824</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6446</v>
+        <v>15531</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9913,19 +9913,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
+          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>240237</v>
+        <v>259403</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4589</v>
+        <v>6462</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>124802</v>
+        <v>124880</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>716325</v>
+        <v>733905</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2658998</v>
+        <v>2782004</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>99115</v>
+        <v>99905</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>161000</v>
+        <v>162000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156449</v>
+        <v>157314</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>152966</v>
+        <v>153831</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>148481</v>
+        <v>149346</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>141979</v>
+        <v>142844</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>138691</v>
+        <v>139556</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>134843</v>
+        <v>135708</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>123822</v>
+        <v>124687</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119239</v>
+        <v>120104</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>115621</v>
+        <v>116486</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>114617</v>
+        <v>115482</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>109522</v>
+        <v>110387</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>100507</v>
+        <v>101372</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>96687</v>
+        <v>97552</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93084</v>
+        <v>93949</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92582</v>
+        <v>93447</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89010</v>
+        <v>89875</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>87499</v>
+        <v>88364</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87334</v>
+        <v>88199</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87252</v>
+        <v>88117</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86330</v>
+        <v>87195</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>85977</v>
+        <v>86842</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>58</v>
-      </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.765</v>
+        <v>0.769</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3474438</v>
+        <v>3615814</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>99115</v>
+        <v>99905</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 26, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 27, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63432</v>
+        <v>63436</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40835</v>
+        <v>40851</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
+          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27086</v>
+        <v>35536</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>717</v>
+        <v>1078</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
+          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26893</v>
+        <v>27115</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>888</v>
+        <v>719</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>25123</v>
+        <v>25134</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>653</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>79942</v>
+        <v>80223</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>71795</v>
+        <v>72131</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67551</v>
+        <v>67651</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58403</v>
+        <v>58407</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>45023</v>
+        <v>45201</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>486147</v>
+        <v>486217</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>18266</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>301451</v>
+        <v>324586</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5373</v>
+        <v>5831</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>287824</v>
+        <v>288918</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>15531</v>
+        <v>15578</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>259403</v>
+        <v>259579</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>6462</v>
+        <v>6466</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>124880</v>
+        <v>124884</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2196</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>733905</v>
+        <v>746845</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2782004</v>
+        <v>2871959</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>99905</v>
+        <v>126157</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>162000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157314</v>
+        <v>157142</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153831</v>
+        <v>153659</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149346</v>
+        <v>149174</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142844</v>
+        <v>142672</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139556</v>
+        <v>139384</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135708</v>
+        <v>135536</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124687</v>
+        <v>124515</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>120104</v>
+        <v>119932</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116486</v>
+        <v>116314</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115482</v>
+        <v>115310</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110387</v>
+        <v>110215</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101372</v>
+        <v>101200</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97552</v>
+        <v>97380</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93949</v>
+        <v>93777</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93447</v>
+        <v>93275</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89875</v>
+        <v>89703</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88364</v>
+        <v>88192</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88199</v>
+        <v>88027</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88117</v>
+        <v>87945</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87195</v>
+        <v>87023</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86842</v>
+        <v>86670</v>
       </c>
     </row>
     <row r="6">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>26</v>
@@ -6772,16 +6772,16 @@
         <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3615814</v>
+        <v>3744961</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>99905</v>
+        <v>126157</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 27, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 28, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63436</v>
+        <v>63445</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1092</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40851</v>
+        <v>40867</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>840</v>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>35536</v>
+        <v>40700</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1078</v>
+        <v>1162</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>27115</v>
+        <v>27160</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>719</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>25134</v>
+        <v>25147</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>653</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>80223</v>
+        <v>80442</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>72131</v>
+        <v>72417</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67651</v>
+        <v>67765</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58407</v>
+        <v>58412</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>795</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>45201</v>
+        <v>45543</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>486217</v>
+        <v>486286</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18266</v>
+        <v>18268</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>324586</v>
+        <v>340655</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5831</v>
+        <v>6443</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>288918</v>
+        <v>289989</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>15578</v>
+        <v>15639</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>259579</v>
+        <v>259996</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>6466</v>
+        <v>6473</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>124884</v>
+        <v>124901</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2196</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>746845</v>
+        <v>783812</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2871959</v>
+        <v>2944833</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>126157</v>
+        <v>135945</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5605,67 +5605,67 @@
         <v>162000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>157142</v>
+        <v>156972</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153659</v>
+        <v>153489</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149174</v>
+        <v>149004</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142672</v>
+        <v>142502</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139384</v>
+        <v>139214</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135536</v>
+        <v>135366</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124515</v>
+        <v>124345</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119932</v>
+        <v>119762</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116314</v>
+        <v>116144</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115310</v>
+        <v>115140</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110215</v>
+        <v>110045</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101200</v>
+        <v>101030</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97380</v>
+        <v>97210</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93777</v>
+        <v>93607</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93275</v>
+        <v>93105</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89703</v>
+        <v>89533</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88192</v>
+        <v>88022</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88027</v>
+        <v>87857</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87945</v>
+        <v>87775</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87023</v>
+        <v>86853</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86670</v>
+        <v>86500</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>52</v>
-      </c>
       <c r="F8" s="7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="N8" s="7" t="n">
         <v>30</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.767</v>
+        <v>0.762</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3744961</v>
+        <v>3864590</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>126157</v>
+        <v>135945</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 28, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 29, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63445</v>
+        <v>63449</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
+          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40867</v>
+        <v>43663</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>840</v>
+        <v>1205</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
+          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>40700</v>
+        <v>40873</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1162</v>
+        <v>840</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>27160</v>
+        <v>27208</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>719</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>25147</v>
+        <v>25152</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>653</v>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>80442</v>
+        <v>80586</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>72417</v>
+        <v>72827</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67765</v>
+        <v>67908</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58412</v>
+        <v>58417</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>795</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>45543</v>
+        <v>45917</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9814,19 +9814,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
+          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>486286</v>
+        <v>352810</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18268</v>
+        <v>6955</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
+          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>340655</v>
+        <v>290723</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6443</v>
+        <v>15670</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
+          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>289989</v>
+        <v>260453</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>15639</v>
+        <v>6479</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9913,19 +9913,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
+          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>259996</v>
+        <v>124916</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>6473</v>
+        <v>2196</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
+          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>124901</v>
+        <v>107490</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2196</v>
+        <v>1219</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>783812</v>
+        <v>822754</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>697914</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2944833</v>
+        <v>3012847</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2062452</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>135945</v>
+        <v>141882</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164514</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11</v>
@@ -5605,67 +5605,67 @@
         <v>162000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>156972</v>
+        <v>156798</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>153489</v>
+        <v>153315</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>149004</v>
+        <v>148830</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>142502</v>
+        <v>142328</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>139214</v>
+        <v>139040</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>135366</v>
+        <v>135192</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>124345</v>
+        <v>124171</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>119762</v>
+        <v>119588</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>116144</v>
+        <v>115970</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115140</v>
+        <v>114966</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>110045</v>
+        <v>109871</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>101030</v>
+        <v>100856</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>97210</v>
+        <v>97036</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>93607</v>
+        <v>93433</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93105</v>
+        <v>92931</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>89533</v>
+        <v>89359</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88022</v>
+        <v>87848</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87857</v>
+        <v>87683</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87775</v>
+        <v>87601</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>86853</v>
+        <v>86679</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86500</v>
+        <v>86326</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>34</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>21</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.762</v>
+        <v>0.757</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.705</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3864590</v>
+        <v>3977483</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2924880</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>135945</v>
+        <v>141882</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 29, 2026</t>
+          <t>⭐ BEST OF — Jun 01 – Jun 30, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63449</v>
+        <v>63459</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1091</v>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>43663</v>
+        <v>44771</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Knicks vs Spurs Finals SPECIAL w/ Malika Andrews, James Jones &amp; Will Reeve</t>
+          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>40873</v>
+        <v>27264</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>718</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
+          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>27208</v>
+        <v>25155</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>719</v>
+        <v>653</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9590,19 +9590,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
+          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>25152</v>
+        <v>20834</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>653</v>
+        <v>722</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9636,19 +9636,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Kyrie Skipped This? 2016 Cavs Reunion in Scotland Had EVERYONE Talking</t>
+          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>80586</v>
+        <v>73334</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1193</v>
+        <v>1660</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
+          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>72827</v>
+        <v>67984</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1653</v>
+        <v>1465</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
+          <t>Rich Paul Controls The Whole NBA And Perk Just Explained How</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>67908</v>
+        <v>46287</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1465</v>
+        <v>638</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9735,19 +9735,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Malika Andrews on The REAL Reason Wemby Plays Like Time’s Running Out</t>
+          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58417</v>
+        <v>46065</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>795</v>
+        <v>939</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9768,19 +9768,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
+          <t>The Cavs Drank So Many Spritzes One Guy Made Them For 2 Hours</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>45917</v>
+        <v>36200</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>938</v>
+        <v>610</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9814,19 +9814,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
+          <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>352810</v>
+        <v>486484</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6955</v>
+        <v>18267</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Jalen Brunson &amp; The Knicks Have Changed The NBA Narrative #knicks #nba #basketball</t>
+          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>290723</v>
+        <v>361022</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15670</v>
+        <v>7297</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>260453</v>
+        <v>260893</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6479</v>
+        <v>6483</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>124916</v>
+        <v>124925</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Former Knick RIPS Knicks Fans “Did You Think New York Was Ever Safe”!? #knicks #spurs #nba</t>
+          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>107490</v>
+        <v>108017</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1219</v>
+        <v>1391</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,16 +103,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,16 +129,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -580,112 +577,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -695,71 +692,73 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="W4" s="7" t="n">
         <v>6</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -768,71 +767,73 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>822754</v>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>871402</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>697914</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="E5" s="9" t="n">
         <v>790809</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="9" t="n">
         <v>999377</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="9" t="n">
         <v>456937</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="9" t="n">
         <v>733899</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>1819209</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="J5" s="9" t="n">
         <v>1237011</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="9" t="n">
         <v>951387</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="L5" s="9" t="n">
         <v>461276</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="9" t="n">
         <v>1296821</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="9" t="n">
         <v>1515762</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="9" t="n">
         <v>606682</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="P5" s="9" t="n">
         <v>629557</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="9" t="n">
         <v>115398</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="R5" s="9" t="n">
         <v>322450</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="9" t="n">
         <v>87239</v>
       </c>
-      <c r="S5" s="7" t="n">
+      <c r="T5" s="9" t="n">
         <v>67472</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="9" t="n">
         <v>48198</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="V5" s="9" t="n">
         <v>114534</v>
       </c>
-      <c r="V5" s="7" t="n">
+      <c r="W5" s="9" t="n">
         <v>75408</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>55180</v>
       </c>
     </row>
     <row r="6">
@@ -841,71 +842,73 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>3012847</v>
-      </c>
-      <c r="C6" s="7" t="n">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3069295</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>2062452</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="9" t="n">
         <v>2731804</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="9" t="n">
         <v>2437458</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="9" t="n">
         <v>1412041</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="9" t="n">
         <v>1021398</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>1102899</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="J6" s="9" t="n">
         <v>920589</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="9" t="n">
         <v>542576</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="L6" s="9" t="n">
         <v>390738</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="9" t="n">
         <v>1348061</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="9" t="n">
         <v>2030353</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="9" t="n">
         <v>545861</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="P6" s="9" t="n">
         <v>130006</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="9" t="n">
         <v>89465</v>
       </c>
-      <c r="Q6" s="7" t="n">
+      <c r="R6" s="9" t="n">
         <v>90474</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="9" t="n">
         <v>56970</v>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="T6" s="9" t="n">
         <v>34237</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="9" t="n">
         <v>24015</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="V6" s="9" t="n">
         <v>17758</v>
       </c>
-      <c r="V6" s="7" t="n">
+      <c r="W6" s="9" t="n">
         <v>11180</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>9896</v>
       </c>
     </row>
     <row r="7">
@@ -914,71 +917,73 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>141882</v>
-      </c>
-      <c r="C7" s="7" t="n">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>145084</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>164514</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>178277</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="9" t="n">
         <v>211738</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="9" t="n">
         <v>209927</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="9" t="n">
         <v>90638</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="J7" s="9" t="n">
         <v>405</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="9" t="n">
         <v>381</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="L7" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="9" t="n">
         <v>386</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="9" t="n">
         <v>697</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="9" t="n">
         <v>37296</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="P7" s="9" t="n">
         <v>4972</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="9" t="n">
         <v>7173</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="R7" s="9" t="n">
         <v>1399</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="9" t="n">
         <v>78402</v>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="T7" s="9" t="n">
         <v>3965</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="9" t="n">
         <v>11199</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="V7" s="9" t="n">
         <v>40604</v>
       </c>
-      <c r="V7" s="7" t="n">
+      <c r="W7" s="9" t="n">
         <v>33838</v>
-      </c>
-      <c r="W7" s="7" t="n">
-        <v>1926</v>
       </c>
     </row>
     <row r="8">
@@ -992,22 +997,22 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>23182</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="9" t="n">
         <v>25288</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="9" t="n">
         <v>24712</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="9" t="n">
         <v>22620</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -1096,91 +1101,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="7">
         <f>SUM(K5:K8)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="7">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="7">
         <f>SUM(N5:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="7">
         <f>SUM(O5:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="7">
         <f>SUM(P5:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="7">
         <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="7">
         <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="7">
         <f>SUM(S5:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="7">
         <f>SUM(T5:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="7">
         <f>SUM(U5:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="6">
+      <c r="V9" s="7">
         <f>SUM(V5:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="7">
         <f>SUM(W5:W8)</f>
         <v/>
       </c>
@@ -1278,112 +1283,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -1393,71 +1398,73 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="W4" s="7" t="n">
         <v>6</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1466,102 +1473,102 @@
           <t>PER EP LISTENS</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>4887</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>4774</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>4425</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>5522</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1573,102 +1580,102 @@
           <t>TOTAL LISTENS</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>53760</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>62065</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>66378</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>49702</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1767,112 +1774,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -1882,112 +1889,112 @@
           <t>VIEWS PER POST AVG</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1999,112 +2006,112 @@
           <t>TOTAL FOLLOWERS</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2467,112 +2474,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2584,112 +2591,112 @@
           <t>FOLLOWER GAIN (NET)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3052,112 +3059,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3169,112 +3176,112 @@
           <t xml:space="preserve">TOTAL POSTS </t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3637,112 +3644,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3754,112 +3761,112 @@
           <t>TOTAL VIEWS</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4222,112 +4229,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4339,112 +4346,112 @@
           <t>TOP POSTS</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4807,112 +4814,112 @@
           <t>ENGAGEMENT RATE</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5275,112 +5282,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5479,112 +5486,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -5601,71 +5608,71 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>162000</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>156798</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>153315</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>148830</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>142328</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>139040</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>135192</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>124171</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>119588</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>115970</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>114966</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>109871</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>100856</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>97036</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>93433</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>92931</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>89359</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>87848</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>87683</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>87601</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>86679</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>86326</v>
+      <c r="C5" s="7" t="n">
+        <v>162000</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>156593</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>153110</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>148625</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>142123</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>138835</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>134987</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>123966</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>119383</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>115765</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>114761</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>109666</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>100651</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>96831</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>93228</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>92726</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>89154</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>87643</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>87478</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>87396</v>
+      </c>
+      <c r="W5" s="7" t="n">
+        <v>86474</v>
       </c>
     </row>
     <row r="6">
@@ -5674,87 +5681,87 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="9">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="9">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="9">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="9">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="9">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="9">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="9">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="9">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="9">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="9">
         <f>V5-W5</f>
         <v/>
       </c>
@@ -6011,91 +6018,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <f>SUM(B8:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>SUM(F8:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <f>SUM(G8:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <f>SUM(H8:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <f>SUM(I8:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <f>SUM(J8:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="7">
         <f>SUM(K8:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <f>SUM(L8:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="7">
         <f>SUM(M8:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="7">
         <f>SUM(N8:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="7">
         <f>SUM(O8:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="7">
         <f>SUM(P8:P9)</f>
         <v/>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="7">
         <f>SUM(Q8:Q9)</f>
         <v/>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="7">
         <f>SUM(R8:R9)</f>
         <v/>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="7">
         <f>SUM(S8:S9)</f>
         <v/>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="7">
         <f>SUM(T8:T9)</f>
         <v/>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="7">
         <f>SUM(U8:U9)</f>
         <v/>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="7">
         <f>SUM(V8:V9)</f>
         <v/>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="7">
         <f>SUM(W8:W9)</f>
         <v/>
       </c>
@@ -6106,87 +6113,87 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="9">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="9">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="9">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="9">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="9">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="9">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="9">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="9">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="9">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="9">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="9">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="9">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="9">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="9">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="9">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="9">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="9">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="9">
         <f>V10-W10</f>
         <v/>
       </c>
@@ -6202,91 +6209,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <f>SUM(B5,B10)</f>
         <v/>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <f>SUM(C5,C10)</f>
         <v/>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <f>SUM(D5,D10)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>SUM(E5,E10)</f>
         <v/>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <f>SUM(F5,F10)</f>
         <v/>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="7">
         <f>SUM(G5,G10)</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="7">
         <f>SUM(H5,H10)</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="7">
         <f>SUM(I5,I10)</f>
         <v/>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="7">
         <f>SUM(J5,J10)</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="7">
         <f>SUM(K5,K10)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="7">
         <f>SUM(L5,L10)</f>
         <v/>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="7">
         <f>SUM(M5,M10)</f>
         <v/>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="7">
         <f>SUM(N5,N10)</f>
         <v/>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="7">
         <f>SUM(O5,O10)</f>
         <v/>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="7">
         <f>SUM(P5,P10)</f>
         <v/>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="7">
         <f>SUM(Q5,Q10)</f>
         <v/>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="7">
         <f>SUM(R5,R10)</f>
         <v/>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="7">
         <f>SUM(S5,S10)</f>
         <v/>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="7">
         <f>SUM(T5,T10)</f>
         <v/>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="7">
         <f>SUM(U5,U10)</f>
         <v/>
       </c>
-      <c r="V12" s="6">
+      <c r="V12" s="7">
         <f>SUM(V5,V10)</f>
         <v/>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="7">
         <f>SUM(W5,W10)</f>
         <v/>
       </c>
@@ -6384,112 +6391,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -6747,71 +6754,71 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="E8" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" s="7" t="n">
+      <c r="R8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="T8" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="V8" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="7" t="n">
+      <c r="W8" s="9" t="n">
         <v>4</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6820,71 +6827,73 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>0.757</v>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C9" s="12" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>0.705</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.738</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.668</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.679</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.553</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="I9" s="12" t="n">
         <v>0.377</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="J9" s="12" t="n">
         <v>0.427</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="K9" s="12" t="n">
         <v>0.363</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="L9" s="12" t="n">
         <v>0.458</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="M9" s="12" t="n">
         <v>0.51</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="N9" s="12" t="n">
         <v>0.572</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="O9" s="12" t="n">
         <v>0.459</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="P9" s="12" t="n">
         <v>0.17</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="Q9" s="12" t="n">
         <v>0.422</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="R9" s="12" t="n">
         <v>0.218</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="S9" s="12" t="n">
         <v>0.256</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="T9" s="12" t="n">
         <v>0.324</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="U9" s="12" t="n">
         <v>0.288</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="V9" s="12" t="n">
         <v>0.103</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="W9" s="12" t="n">
         <v>0.093</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.148</v>
       </c>
     </row>
     <row r="10">
@@ -7579,112 +7588,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -7694,112 +7703,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7811,112 +7820,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7928,112 +7937,112 @@
           <t>YOUTUBE</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8133,112 +8142,112 @@
     <row r="3">
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>OCT 24</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>SEP 24</t>
         </is>
       </c>
     </row>
@@ -8271,112 +8280,112 @@
           <t>LONG-FORM</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8500,112 +8509,112 @@
           <t>MID-FORM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8729,112 +8738,112 @@
           <t>SHORT-FORM</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8958,71 +8967,73 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>3977483</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4085781</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>2924880</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>3700890</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>3648573</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>2078905</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>1845935</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>2922473</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>2158005</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>1494344</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>852234</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>2645268</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>3546812</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>1189839</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>764535</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>212036</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>414323</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>222611</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>105674</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>83412</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>172896</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>120426</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>67002</v>
       </c>
     </row>
     <row r="12">
@@ -9054,112 +9065,112 @@
           <t>PER EP</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9171,71 +9182,73 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>141882</v>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>145084</v>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>164514</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>178277</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>211738</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>209927</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>90638</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>365</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>381</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>386</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>697</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>37296</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>4972</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>7173</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>1399</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>78402</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>3965</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>11199</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>40604</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>33838</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>1926</v>
       </c>
     </row>
     <row r="15">
@@ -9244,112 +9257,112 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9375,7 +9388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9390,7 +9403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jun 01 – Jun 30, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 01, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9450,529 +9463,81 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SEGMENT CLIPS</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Knicks vs Spurs NBA Finals PREVIEW w/ James Worthy, Robert Horry &amp; DeAndre Jordan</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>63459</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>1091</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>6311</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>302</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>LaMelo Ball TRADED To The Timberwolves, Giannis Traded To The Heat + 2016 Cavs Trip Recap</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>44771</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1219</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Biggest Comeback In Finals HISTORY! OG's Game-Winner &amp; Finals MVP Race Heats Up</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>27264</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Spurs STEAL Game 3! Knicks vs Wemby With The NBA FINALS On The LINE</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>25155</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>653</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Tracy Morgan Gets EMOTIONAL After Knicks Championship + The Crew DIVIDED on If Brunson is TOP 5</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>20834</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>722</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SEGMENT CLIPS</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>“Your Ass Never Was An Athlete Then” — Perk Responds To Vince Goodwill</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>73334</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1660</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Perk GOES OFF After Robert Horry Snubs Brunson</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>67984</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1465</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14">
       <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Rich Paul Controls The Whole NBA And Perk Just Explained How</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>638</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Perk &amp; RJ Disagree On What The Spurs Should Do With Dillon Harper</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>46065</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>939</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>The Cavs Drank So Many Spritzes One Guy Made Them For 2 Hours</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>36200</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>610</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins Reacts To New York Giants’ QB Jaxson Dart Introducing President Trump</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>486484</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>18267</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Anthony Edwards LEAVING Minnesota!? #AntMan #anthonyedwards #NBA #minnesotatimberwolves</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>361022</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>7297</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Jalen Brunson MOST CLUTCH Player Ever!? “He’s Built For This” #NewYorkKnicks #NBA</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>260893</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>6483</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Does National Championship Experience Translate To The NBA Finals? #nba #collegehoops #basketball</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>124925</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>2195</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Is Wemby Still Face of the NBA After Finals Loss? #Wemby #Spurs #victorwembanyama #nba</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>108017</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>1391</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9980,9 +9545,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>939508</v>
+        <v>984277</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>697914</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3164363</v>
+        <v>3322546</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>2062452</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>163663</v>
+        <v>170117</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>164514</v>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5608,70 +5608,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>163000</v>
+        <v>165000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163000</v>
+        <v>165000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157276</v>
+        <v>159046</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153793</v>
+        <v>155563</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149308</v>
+        <v>151078</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142806</v>
+        <v>144576</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139518</v>
+        <v>141288</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135670</v>
+        <v>137440</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124649</v>
+        <v>126419</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120066</v>
+        <v>121836</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116448</v>
+        <v>118218</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115444</v>
+        <v>117214</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110349</v>
+        <v>112119</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101334</v>
+        <v>103104</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97514</v>
+        <v>99284</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93911</v>
+        <v>95681</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93409</v>
+        <v>95179</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89837</v>
+        <v>91607</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88326</v>
+        <v>90096</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88161</v>
+        <v>89931</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88079</v>
+        <v>89849</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87157</v>
+        <v>88927</v>
       </c>
     </row>
     <row r="6">
@@ -6754,31 +6754,31 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>60</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>24</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>30</v>
@@ -6787,13 +6787,13 @@
         <v>24</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" s="8" t="n">
         <v>38</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>20</v>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.705</v>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4267534</v>
+        <v>4476940</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2924880</v>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>163663</v>
+        <v>170117</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>164514</v>
@@ -9387,7 +9387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9402,7 +9402,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 02, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 03, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>42843</v>
+        <v>53248</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1370</v>
+        <v>1646</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Girls Tripp |  EP 7</t>
+          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -9512,314 +9512,380 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SEGMENT CLIPS</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>146253</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>2974</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29950</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>547</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>6499</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4473</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Perk And RJ DISAGREE On Whether Ja Gets His Jersey Retired</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SEGMENT CLIPS</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>44838</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1236</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="D17" s="8" t="n">
+        <v>1058374</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>28652</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>264585</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>6587</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="D19" s="8" t="n">
+        <v>46774</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Ty Young explains Aja Wilson’s HILARIOUS nickname #WNBA #AjaWilson #LasVegasAces</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="D20" s="6" t="n">
+        <v>2528</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>HowIsJaRemembered Clip</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>KahwiTradedToToronto Clip</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>108817</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>5272</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>37078</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1116</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9827,8 +9893,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -768,72 +768,70 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>984277</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="B5" s="7" t="n">
+        <v>60880</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>984066</v>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>697914</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <v>790809</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="7" t="n">
         <v>999377</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <v>456937</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="7" t="n">
         <v>733899</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>1819209</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="7" t="n">
         <v>1237011</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="K5" s="7" t="n">
         <v>951387</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="7" t="n">
         <v>461276</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>1296821</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="7" t="n">
         <v>1515762</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="7" t="n">
         <v>606682</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>629557</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="7" t="n">
         <v>115398</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="7" t="n">
         <v>322450</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="7" t="n">
         <v>87239</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="7" t="n">
         <v>67472</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="7" t="n">
         <v>48198</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="7" t="n">
         <v>114534</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="7" t="n">
         <v>75408</v>
       </c>
     </row>
@@ -843,72 +841,70 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>3322546</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="B6" s="7" t="n">
+        <v>237530</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3321502</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>2062452</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>2731804</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="7" t="n">
         <v>2437458</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="7" t="n">
         <v>1412041</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="7" t="n">
         <v>1021398</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="7" t="n">
         <v>1102899</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="7" t="n">
         <v>920589</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="K6" s="7" t="n">
         <v>542576</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="7" t="n">
         <v>390738</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>1348061</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="7" t="n">
         <v>2030353</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="O6" s="7" t="n">
         <v>545861</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="P6" s="7" t="n">
         <v>130006</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="7" t="n">
         <v>89465</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="7" t="n">
         <v>90474</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="7" t="n">
         <v>56970</v>
       </c>
-      <c r="T6" s="8" t="n">
+      <c r="T6" s="7" t="n">
         <v>34237</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="7" t="n">
         <v>24015</v>
       </c>
-      <c r="V6" s="8" t="n">
+      <c r="V6" s="7" t="n">
         <v>17758</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="7" t="n">
         <v>11180</v>
       </c>
     </row>
@@ -918,72 +914,70 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>170117</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="B7" s="7" t="n">
+        <v>43852</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>170057</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>164514</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>178277</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="7" t="n">
         <v>211738</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="7" t="n">
         <v>209927</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="7" t="n">
         <v>90638</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="7" t="n">
         <v>365</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="K7" s="7" t="n">
         <v>381</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>386</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="7" t="n">
         <v>697</v>
       </c>
-      <c r="O7" s="8" t="n">
+      <c r="O7" s="7" t="n">
         <v>37296</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="P7" s="7" t="n">
         <v>4972</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="7" t="n">
         <v>7173</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="7" t="n">
         <v>1399</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="7" t="n">
         <v>78402</v>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="T7" s="7" t="n">
         <v>3965</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="7" t="n">
         <v>11199</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="7" t="n">
         <v>40604</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="7" t="n">
         <v>33838</v>
       </c>
     </row>
@@ -993,104 +987,104 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>23182</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>25288</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>24712</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>22620</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2122,112 +2116,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2239,112 +2233,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2356,112 +2350,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2707,112 +2701,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2824,112 +2818,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2941,112 +2935,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3292,112 +3286,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3409,112 +3403,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3526,112 +3520,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3877,112 +3871,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3994,112 +3988,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4111,112 +4105,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4462,112 +4456,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4579,112 +4573,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4696,112 +4690,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4930,112 +4924,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5047,112 +5041,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5164,112 +5158,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5611,67 +5605,67 @@
         <v>165000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>165000</v>
+        <v>164367</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>159046</v>
+        <v>158413</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>155563</v>
+        <v>154930</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>151078</v>
+        <v>150445</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>144576</v>
+        <v>143943</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>141288</v>
+        <v>140655</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>137440</v>
+        <v>136807</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>126419</v>
+        <v>125786</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>121836</v>
+        <v>121203</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>118218</v>
+        <v>117585</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>117214</v>
+        <v>116581</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>112119</v>
+        <v>111486</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>103104</v>
+        <v>102471</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>99284</v>
+        <v>98651</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>95681</v>
+        <v>95048</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>95179</v>
+        <v>94546</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>91607</v>
+        <v>90974</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>90096</v>
+        <v>89463</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89931</v>
+        <v>89298</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89849</v>
+        <v>89216</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88927</v>
+        <v>88294</v>
       </c>
     </row>
     <row r="6">
@@ -5680,91 +5674,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="7">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5783,112 +5777,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5900,112 +5894,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6112,91 +6106,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="7">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="7">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="7">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="7">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6753,70 +6747,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="B8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="G8" s="8" t="n">
+      <c r="E8" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="K8" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M8" s="8" t="n">
+      <c r="L8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="M8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+      <c r="P8" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6826,10 +6820,8 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="12" t="n">
+        <v>0.694</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8391,112 +8383,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8620,112 +8612,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8849,112 +8841,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8966,13 +8958,11 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="6" t="n">
+        <v>342262</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4476940</v>
+        <v>4475625</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2924880</v>
@@ -9181,13 +9171,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C14" s="6" t="n">
+        <v>43852</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>170117</v>
+        <v>170057</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>164514</v>
@@ -9387,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9402,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 03, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 04, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9478,11 +9466,11 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>53248</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>1646</v>
+      <c r="D5" s="7" t="n">
+        <v>58346</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1746</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9512,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>548</v>
+        <v>880</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9544,10 +9532,10 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="D7" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -9590,11 +9578,11 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>146253</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>2974</v>
+      <c r="D10" s="7" t="n">
+        <v>168703</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>3355</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9624,10 +9612,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>29950</v>
+        <v>69810</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>547</v>
+        <v>1090</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9656,11 +9644,11 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>6499</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>126</v>
+      <c r="D12" s="7" t="n">
+        <v>9432</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>179</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9690,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4473</v>
+        <v>5799</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9714,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Perk And RJ DISAGREE On Whether Ja Gets His Jersey Retired</t>
+          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>5521</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>115</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9768,11 +9756,11 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>1058374</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>28652</v>
+      <c r="D17" s="7" t="n">
+        <v>1263708</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>32830</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9802,10 +9790,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>264585</v>
+        <v>445755</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>6587</v>
+        <v>10374</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9834,11 +9822,11 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>46774</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>1299</v>
+      <c r="D19" s="7" t="n">
+        <v>51065</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1384</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9859,33 +9847,66 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>19927</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>981</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
           <t>Ty Young explains Aja Wilson’s HILARIOUS nickname #WNBA #AjaWilson #LasVegasAces</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>2528</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D21" s="7" t="n">
+        <v>4586</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>60880</v>
+        <v>222809</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>984066</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>237530</v>
+        <v>1677178</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3321502</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>43852</v>
+        <v>56363</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>170057</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>165000</v>
+        <v>166000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>164367</v>
+        <v>163672</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>158413</v>
+        <v>157718</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154930</v>
+        <v>154235</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>150445</v>
+        <v>149750</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143943</v>
+        <v>143248</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>140655</v>
+        <v>139960</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>136807</v>
+        <v>136112</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>125786</v>
+        <v>125091</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>121203</v>
+        <v>120508</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>117585</v>
+        <v>116890</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116581</v>
+        <v>115886</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>111486</v>
+        <v>110791</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>102471</v>
+        <v>101776</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>98651</v>
+        <v>97956</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>95048</v>
+        <v>94353</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>94546</v>
+        <v>93851</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90974</v>
+        <v>90279</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89463</v>
+        <v>88768</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89298</v>
+        <v>88603</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89216</v>
+        <v>88521</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88294</v>
+        <v>87599</v>
       </c>
     </row>
     <row r="6">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.694</v>
+        <v>0.857</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>342262</v>
+        <v>1956350</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4475625</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>43852</v>
+        <v>56363</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>170057</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 04, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 05, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>58346</v>
+        <v>60767</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1746</v>
+        <v>1802</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>880</v>
+        <v>1194</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>168703</v>
+        <v>182890</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3355</v>
+        <v>3564</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>69810</v>
+        <v>107689</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1090</v>
+        <v>1551</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9432</v>
+        <v>10822</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
+          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5799</v>
+        <v>9140</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9702,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
+          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5521</v>
+        <v>6424</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1263708</v>
+        <v>1408761</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>32830</v>
+        <v>36046</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>445755</v>
+        <v>596964</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10374</v>
+        <v>14147</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9814,19 +9814,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>51065</v>
+        <v>121032</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1384</v>
+        <v>3312</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>19927</v>
+        <v>53774</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>981</v>
+        <v>1434</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>4586</v>
+        <v>6311</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>222809</v>
+        <v>314722</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>984066</v>
+        <v>983319</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>697914</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1677178</v>
+        <v>2217900</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3321502</v>
+        <v>3317425</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>2062452</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>56363</v>
+        <v>62675</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>170057</v>
+        <v>169907</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>164514</v>
@@ -5605,67 +5605,67 @@
         <v>166000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163672</v>
+        <v>163049</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157718</v>
+        <v>157095</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154235</v>
+        <v>153612</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149750</v>
+        <v>149127</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143248</v>
+        <v>142625</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139960</v>
+        <v>139337</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>136112</v>
+        <v>135489</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>125091</v>
+        <v>124468</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120508</v>
+        <v>119885</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116890</v>
+        <v>116267</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115886</v>
+        <v>115263</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110791</v>
+        <v>110168</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101776</v>
+        <v>101153</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97956</v>
+        <v>97333</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>94353</v>
+        <v>93730</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93851</v>
+        <v>93228</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90279</v>
+        <v>89656</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88768</v>
+        <v>88145</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88603</v>
+        <v>87980</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88521</v>
+        <v>87898</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87599</v>
+        <v>86976</v>
       </c>
     </row>
     <row r="6">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>60</v>
@@ -6760,10 +6760,10 @@
         <v>54</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>37</v>
@@ -6772,7 +6772,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>30</v>
@@ -6781,7 +6781,7 @@
         <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>38</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.857</v>
+        <v>0.855</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1956350</v>
+        <v>2595297</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4475625</v>
+        <v>4470651</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2924880</v>
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>56363</v>
+        <v>62675</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>170057</v>
+        <v>169907</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>164514</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 05, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 06, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>60767</v>
+        <v>63059</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1802</v>
+        <v>1850</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1194</v>
+        <v>1498</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>182890</v>
+        <v>192213</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3564</v>
+        <v>3677</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>107689</v>
+        <v>135222</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1551</v>
+        <v>1857</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10822</v>
+        <v>11645</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>9140</v>
+        <v>10464</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>6424</v>
+        <v>6969</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1408761</v>
+        <v>1461454</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>36046</v>
+        <v>37356</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>596964</v>
+        <v>745473</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>14147</v>
+        <v>17885</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>121032</v>
+        <v>145982</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3312</v>
+        <v>4136</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>53774</v>
+        <v>56034</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1434</v>
+        <v>1485</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>6311</v>
+        <v>7602</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>314722</v>
+        <v>386969</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2217900</v>
+        <v>2699278</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>62675</v>
+        <v>65918</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5602,70 +5602,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>166000</v>
+        <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163049</v>
+        <v>163545</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157095</v>
+        <v>157591</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153612</v>
+        <v>154108</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149127</v>
+        <v>149623</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142625</v>
+        <v>143121</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139337</v>
+        <v>139833</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135489</v>
+        <v>135985</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124468</v>
+        <v>124964</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119885</v>
+        <v>120381</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116267</v>
+        <v>116763</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115263</v>
+        <v>115759</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110168</v>
+        <v>110664</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101153</v>
+        <v>101649</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97333</v>
+        <v>97829</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93730</v>
+        <v>94226</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93228</v>
+        <v>93724</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89656</v>
+        <v>90152</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88145</v>
+        <v>88641</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87980</v>
+        <v>88476</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87898</v>
+        <v>88394</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86976</v>
+        <v>87472</v>
       </c>
     </row>
     <row r="6">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>56</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.855</v>
+        <v>0.856</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2595297</v>
+        <v>3152165</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>62675</v>
+        <v>65918</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 06, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 07, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>63059</v>
+        <v>64616</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1850</v>
+        <v>1886</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1498</v>
+        <v>1723</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9516,397 +9516,364 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SEGMENT CLIPS</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>197386</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3713</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>153658</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="D11" s="7" t="n">
+        <v>12291</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>237</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SEGMENT CLIPS</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11188</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>222</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>7288</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>192213</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>3677</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="D16" s="7" t="n">
+        <v>1474766</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>37644</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>135222</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1857</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="D17" s="6" t="n">
+        <v>903664</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>21328</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>11645</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>222</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>171983</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>4972</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>10464</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>204</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>82303</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>3384</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>6969</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>119</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="D20" s="7" t="n">
+        <v>57227</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>1461454</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>37356</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>745473</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>17885</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>145982</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>4136</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>56034</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>1485</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Ty Young explains Aja Wilson’s HILARIOUS nickname #WNBA #AjaWilson #LasVegasAces</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>7602</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>217</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9914,8 +9881,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>386969</v>
+        <v>438573</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2699278</v>
+        <v>3005353</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>65918</v>
+        <v>68790</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5605,67 +5605,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163545</v>
+        <v>163200</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157591</v>
+        <v>157246</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154108</v>
+        <v>153763</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149623</v>
+        <v>149278</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143121</v>
+        <v>142776</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139833</v>
+        <v>139488</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135985</v>
+        <v>135640</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124964</v>
+        <v>124619</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120381</v>
+        <v>120036</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116763</v>
+        <v>116418</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115759</v>
+        <v>115414</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110664</v>
+        <v>110319</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101649</v>
+        <v>101304</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97829</v>
+        <v>97484</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>94226</v>
+        <v>93881</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93724</v>
+        <v>93379</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90152</v>
+        <v>89807</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88641</v>
+        <v>88296</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88476</v>
+        <v>88131</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88394</v>
+        <v>88049</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87472</v>
+        <v>87127</v>
       </c>
     </row>
     <row r="6">
@@ -6748,28 +6748,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>60</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>41</v>
@@ -6784,7 +6784,7 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3152165</v>
+        <v>3512716</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>65918</v>
+        <v>68790</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 07, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 08, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>64616</v>
+        <v>65654</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1723</v>
+        <v>1861</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>197386</v>
+        <v>199904</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3713</v>
+        <v>3733</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>153658</v>
+        <v>162699</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2024</v>
+        <v>2093</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>12291</v>
+        <v>12864</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11188</v>
+        <v>11817</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>7288</v>
+        <v>7433</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1474766</v>
+        <v>1480826</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>37644</v>
+        <v>37717</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>903664</v>
+        <v>1034197</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>21328</v>
+        <v>23880</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>171983</v>
+        <v>207241</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>4972</v>
+        <v>6085</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>82303</v>
+        <v>128125</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>3384</v>
+        <v>5025</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>57227</v>
+        <v>59229</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1520</v>
+        <v>1609</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>438573</v>
+        <v>475487</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3005353</v>
+        <v>3329827</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>68790</v>
+        <v>70926</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5605,67 +5605,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163200</v>
+        <v>162908</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157246</v>
+        <v>156954</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153763</v>
+        <v>153471</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149278</v>
+        <v>148986</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142776</v>
+        <v>142484</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139488</v>
+        <v>139196</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135640</v>
+        <v>135348</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124619</v>
+        <v>124327</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120036</v>
+        <v>119744</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116418</v>
+        <v>116126</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115414</v>
+        <v>115122</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110319</v>
+        <v>110027</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101304</v>
+        <v>101012</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97484</v>
+        <v>97192</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93881</v>
+        <v>93589</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93379</v>
+        <v>93087</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89807</v>
+        <v>89515</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88296</v>
+        <v>88004</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88131</v>
+        <v>87839</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88049</v>
+        <v>87757</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87127</v>
+        <v>86835</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>41</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.856</v>
+        <v>0.859</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3512716</v>
+        <v>3876240</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>68790</v>
+        <v>70926</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 08, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 09, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>65654</v>
+        <v>66272</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1896</v>
+        <v>1910</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1861</v>
+        <v>1974</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9516,364 +9516,397 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>LeBronCompilation BonusEpisode</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>199904</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>3733</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D10" s="7" t="n">
+        <v>201673</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>3752</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>162699</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>2093</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D11" s="6" t="n">
+        <v>167313</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>12864</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>242</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>13310</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>244</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>11817</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>231</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>12238</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>7433</v>
-      </c>
-      <c r="E13" s="7" t="n">
+      <c r="D14" s="7" t="n">
+        <v>7507</v>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>1480826</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>37717</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="D17" s="7" t="n">
+        <v>1484608</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>37829</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>1034197</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>23880</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D18" s="6" t="n">
+        <v>1060914</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>24334</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>207241</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>6085</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="D19" s="7" t="n">
+        <v>237934</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>7092</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>128125</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>5025</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="D20" s="6" t="n">
+        <v>147648</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>5843</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
-        <v>59229</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>1609</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="D21" s="7" t="n">
+        <v>59849</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9881,8 +9914,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>475487</v>
+        <v>496432</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3329827</v>
+        <v>3592263</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>70926</v>
+        <v>72440</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5605,67 +5605,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162908</v>
+        <v>162691</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156954</v>
+        <v>156737</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153471</v>
+        <v>153254</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148986</v>
+        <v>148769</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142484</v>
+        <v>142267</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139196</v>
+        <v>138979</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135348</v>
+        <v>135131</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124327</v>
+        <v>124110</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119744</v>
+        <v>119527</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116126</v>
+        <v>115909</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115122</v>
+        <v>114905</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110027</v>
+        <v>109810</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101012</v>
+        <v>100795</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97192</v>
+        <v>96975</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93589</v>
+        <v>93372</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93087</v>
+        <v>92870</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89515</v>
+        <v>89298</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88004</v>
+        <v>87787</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87839</v>
+        <v>87622</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87757</v>
+        <v>87540</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86835</v>
+        <v>86618</v>
       </c>
     </row>
     <row r="6">
@@ -6748,43 +6748,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.859</v>
+        <v>0.863</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3876240</v>
+        <v>4161135</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>70926</v>
+        <v>72440</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9390,7 +9390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 09, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 10, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>66272</v>
+        <v>66724</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
+          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1974</v>
+        <v>22656</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>71</v>
+        <v>423</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9524,19 +9524,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>LeBronCompilation BonusEpisode</t>
+          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>2005</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>201673</v>
+        <v>202517</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3752</v>
+        <v>3764</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>167313</v>
+        <v>169391</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2130</v>
+        <v>2150</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>13310</v>
+        <v>13582</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12238</v>
+        <v>12442</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>7507</v>
+        <v>7533</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1484608</v>
+        <v>1486246</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37829</v>
+        <v>37882</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1060914</v>
+        <v>1073010</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24334</v>
+        <v>24501</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>237934</v>
+        <v>250493</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7092</v>
+        <v>7554</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>147648</v>
+        <v>168890</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5843</v>
+        <v>6678</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>59849</v>
+        <v>60123</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>496432</v>
+        <v>508690</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3592263</v>
+        <v>3705152</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>72440</v>
+        <v>73249</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -992,10 +992,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C8" s="7" t="n">
+        <v>23305</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>23182</v>
@@ -1007,7 +1005,7 @@
         <v>24712</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>22620</v>
+        <v>22848</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -1394,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -1471,10 +1469,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C5" s="6" t="n">
+        <v>4091</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>4887</v>
@@ -1578,10 +1574,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C6" s="6" t="n">
+        <v>65456</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>53760</v>
@@ -5605,67 +5599,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162691</v>
+        <v>162585</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156737</v>
+        <v>156631</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153254</v>
+        <v>153148</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148769</v>
+        <v>148663</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142267</v>
+        <v>142161</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138979</v>
+        <v>138873</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135131</v>
+        <v>135025</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124110</v>
+        <v>124004</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119527</v>
+        <v>119421</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115909</v>
+        <v>115803</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114905</v>
+        <v>114799</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109810</v>
+        <v>109704</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100795</v>
+        <v>100689</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96975</v>
+        <v>96869</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93372</v>
+        <v>93266</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92870</v>
+        <v>92764</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89298</v>
+        <v>89192</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87787</v>
+        <v>87681</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87622</v>
+        <v>87516</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87540</v>
+        <v>87434</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86618</v>
+        <v>86512</v>
       </c>
     </row>
     <row r="6">
@@ -6821,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.863</v>
+        <v>0.864</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8959,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4161135</v>
+        <v>4287091</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9172,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>72440</v>
+        <v>73249</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9390,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 10, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 11, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>66724</v>
+        <v>66983</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1914</v>
+        <v>1920</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9500,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22656</v>
+        <v>28810</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>423</v>
+        <v>527</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9533,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2005</v>
+        <v>2033</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>71</v>
@@ -9579,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>202517</v>
+        <v>203011</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3764</v>
+        <v>3770</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9612,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>169391</v>
+        <v>170289</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2150</v>
+        <v>2163</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9636,19 +9630,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
+          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>13582</v>
+        <v>16428</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9669,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
+          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12442</v>
+        <v>13634</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9702,19 +9696,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Why LaMelo Sells Out Every AAU Gym But Couldn't Win In Charlotte</t>
+          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>7533</v>
+        <v>12558</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9757,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1486246</v>
+        <v>1486707</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37882</v>
+        <v>37888</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9790,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1073010</v>
+        <v>1092152</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24501</v>
+        <v>24816</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9823,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>250493</v>
+        <v>253495</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7554</v>
+        <v>7658</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9856,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>168890</v>
+        <v>188731</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6678</v>
+        <v>7550</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9889,7 +9883,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>60123</v>
+        <v>60226</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1654</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>66983</v>
+        <v>67023</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1920</v>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28810</v>
+        <v>29789</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>71</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>203011</v>
+        <v>203095</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>170289</v>
+        <v>170547</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>16428</v>
+        <v>18391</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13634</v>
+        <v>13643</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>246</v>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12558</v>
+        <v>12593</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>240</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1486707</v>
+        <v>1486849</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37888</v>
+        <v>37889</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1092152</v>
+        <v>1099229</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24816</v>
+        <v>24917</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>253495</v>
+        <v>253851</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7658</v>
+        <v>7667</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>188731</v>
+        <v>195344</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7550</v>
+        <v>7765</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>60226</v>
+        <v>60266</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1654</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>508690</v>
+        <v>537906</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3705152</v>
+        <v>3853094</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>73249</v>
+        <v>73962</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162585</v>
+        <v>162462</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156631</v>
+        <v>156508</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153148</v>
+        <v>153025</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148663</v>
+        <v>148540</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142161</v>
+        <v>142038</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138873</v>
+        <v>138750</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135025</v>
+        <v>134902</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124004</v>
+        <v>123881</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119421</v>
+        <v>119298</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115803</v>
+        <v>115680</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114799</v>
+        <v>114676</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109704</v>
+        <v>109581</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100689</v>
+        <v>100566</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96869</v>
+        <v>96746</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93266</v>
+        <v>93143</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92764</v>
+        <v>92641</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89192</v>
+        <v>89069</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87681</v>
+        <v>87558</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87516</v>
+        <v>87393</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87434</v>
+        <v>87311</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86512</v>
+        <v>86389</v>
       </c>
     </row>
     <row r="6">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4287091</v>
+        <v>4464962</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>73249</v>
+        <v>73962</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 11, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 12, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>67023</v>
+        <v>67354</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1920</v>
+        <v>1927</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>29789</v>
+        <v>33207</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2036</v>
+        <v>2047</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>71</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>203095</v>
+        <v>203478</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>170547</v>
+        <v>171720</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2166</v>
+        <v>2172</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>18391</v>
+        <v>24704</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>351</v>
+        <v>461</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13643</v>
+        <v>13686</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12593</v>
+        <v>12761</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1486849</v>
+        <v>1487428</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37889</v>
+        <v>37896</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1099229</v>
+        <v>1156199</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24917</v>
+        <v>25960</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>253851</v>
+        <v>254560</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7667</v>
+        <v>7690</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>195344</v>
+        <v>233077</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7765</v>
+        <v>9208</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>60266</v>
+        <v>60456</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>537906</v>
+        <v>537901</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3853094</v>
+        <v>3853023</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>73962</v>
+        <v>73959</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4464962</v>
+        <v>4464883</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>73962</v>
+        <v>73959</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>67354</v>
+        <v>67395</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1927</v>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>33207</v>
+        <v>33663</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2047</v>
+        <v>2054</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>203478</v>
+        <v>203527</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>171720</v>
+        <v>172058</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2172</v>
+        <v>2178</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>24704</v>
+        <v>25552</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13686</v>
+        <v>13703</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>247</v>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12761</v>
+        <v>12780</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>241</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1487428</v>
+        <v>1487527</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37896</v>
+        <v>37899</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1156199</v>
+        <v>1178021</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>25960</v>
+        <v>26473</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>254560</v>
+        <v>254696</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>233077</v>
+        <v>242331</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9208</v>
+        <v>9641</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>60456</v>
+        <v>60491</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>537901</v>
+        <v>569529</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3853023</v>
+        <v>3942704</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>73959</v>
+        <v>74502</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162462</v>
+        <v>162332</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156508</v>
+        <v>156378</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153025</v>
+        <v>152895</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148540</v>
+        <v>148410</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142038</v>
+        <v>141908</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138750</v>
+        <v>138620</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>134902</v>
+        <v>134772</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>123881</v>
+        <v>123751</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119298</v>
+        <v>119168</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115680</v>
+        <v>115550</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114676</v>
+        <v>114546</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109581</v>
+        <v>109451</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100566</v>
+        <v>100436</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96746</v>
+        <v>96616</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93143</v>
+        <v>93013</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92641</v>
+        <v>92511</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89069</v>
+        <v>88939</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87558</v>
+        <v>87428</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87393</v>
+        <v>87263</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87311</v>
+        <v>87181</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86389</v>
+        <v>86259</v>
       </c>
     </row>
     <row r="6">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.863</v>
+        <v>0.86</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4464883</v>
+        <v>4586735</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>73959</v>
+        <v>74502</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 12, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 13, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>67395</v>
+        <v>67556</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>33663</v>
+        <v>34297</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2054</v>
+        <v>2062</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>72</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>203527</v>
+        <v>203747</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3774</v>
+        <v>3777</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>172058</v>
+        <v>172926</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2178</v>
+        <v>2186</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>25552</v>
+        <v>27024</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13703</v>
+        <v>13739</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>247</v>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12780</v>
+        <v>12897</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1487527</v>
+        <v>1487801</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>37899</v>
+        <v>37901</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1178021</v>
+        <v>1232887</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>26473</v>
+        <v>27460</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9808,19 +9808,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>254696</v>
+        <v>255372</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7691</v>
+        <v>10094</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>242331</v>
+        <v>255107</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9641</v>
+        <v>7695</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>60491</v>
+        <v>60550</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1657</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>569529</v>
+        <v>584403</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3942704</v>
+        <v>4050002</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>74502</v>
+        <v>75051</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>167000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162332</v>
+        <v>162232</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156378</v>
+        <v>156278</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>152895</v>
+        <v>152795</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148410</v>
+        <v>148310</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>141908</v>
+        <v>141808</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138620</v>
+        <v>138520</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>134772</v>
+        <v>134672</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>123751</v>
+        <v>123651</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119168</v>
+        <v>119068</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115550</v>
+        <v>115450</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114546</v>
+        <v>114446</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109451</v>
+        <v>109351</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100436</v>
+        <v>100336</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96616</v>
+        <v>96516</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93013</v>
+        <v>92913</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92511</v>
+        <v>92411</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88939</v>
+        <v>88839</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87428</v>
+        <v>87328</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87263</v>
+        <v>87163</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87181</v>
+        <v>87081</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86259</v>
+        <v>86159</v>
       </c>
     </row>
     <row r="6">
@@ -6742,34 +6742,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>22</v>
@@ -6778,13 +6778,13 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4586735</v>
+        <v>4709456</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>74502</v>
+        <v>75051</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9369,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 13, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 14, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>67556</v>
+        <v>67724</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>34297</v>
+        <v>34801</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2062</v>
+        <v>2083</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>72</v>
@@ -9543,364 +9543,397 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>RoadTrippin 071426 FINALCUT Video NoDisclaimer</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>203747</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>3777</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="D11" s="7" t="n">
+        <v>204010</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3778</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>172926</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>2186</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D12" s="6" t="n">
+        <v>174081</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2191</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>27024</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>493</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="D13" s="7" t="n">
+        <v>27845</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>13739</v>
-      </c>
-      <c r="E13" s="6" t="n">
+      <c r="D14" s="6" t="n">
+        <v>13771</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>247</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>12897</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>243</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="D15" s="7" t="n">
+        <v>12994</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>1487801</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>37901</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="D18" s="7" t="n">
+        <v>1488550</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>37902</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
-        <v>1232887</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>27460</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="D19" s="6" t="n">
+        <v>1295374</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>28702</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
-        <v>255372</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>10094</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="D20" s="7" t="n">
+        <v>260241</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>10275</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>255107</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>7695</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D21" s="6" t="n">
+        <v>255571</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>7716</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>60550</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>1657</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="D22" s="7" t="n">
+        <v>60675</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>1658</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9908,9 +9941,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>584403</v>
+        <v>592422</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4050002</v>
+        <v>4156848</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>75051</v>
+        <v>75537</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>167000</v>
+        <v>168000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162232</v>
+        <v>163140</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156278</v>
+        <v>157186</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>152795</v>
+        <v>153703</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148310</v>
+        <v>149218</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>141808</v>
+        <v>142716</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138520</v>
+        <v>139428</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>134672</v>
+        <v>135580</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>123651</v>
+        <v>124559</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119068</v>
+        <v>119976</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115450</v>
+        <v>116358</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114446</v>
+        <v>115354</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109351</v>
+        <v>110259</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100336</v>
+        <v>101244</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96516</v>
+        <v>97424</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>92913</v>
+        <v>93821</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92411</v>
+        <v>93319</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88839</v>
+        <v>89747</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87328</v>
+        <v>88236</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87163</v>
+        <v>88071</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87081</v>
+        <v>87989</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86159</v>
+        <v>87067</v>
       </c>
     </row>
     <row r="6">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>57</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>54</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.86</v>
+        <v>0.862</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4709456</v>
+        <v>4824807</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>75051</v>
+        <v>75537</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 14, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 15, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9452,19 +9452,19 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>RT SOUNDS OFF On Ja &amp; Kawhi Trades, LeBron Plan &amp; More Free Agency MADNESS!</t>
+          <t>Boogie Cousins CALLS OUT The Lakers For Doing LeBron DIRTY</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>67724</v>
+        <v>73477</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1929</v>
+        <v>2029</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9485,19 +9485,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
+          <t>RT SOUNDS OFF On Ja &amp; Kawhi Trades, LeBron Plan &amp; More Free Agency MADNESS!</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>34801</v>
+        <v>68148</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>609</v>
+        <v>1937</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
+          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2083</v>
+        <v>35214</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>72</v>
+        <v>614</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>RoadTrippin 071426 FINALCUT Video NoDisclaimer</t>
+          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>204010</v>
+        <v>204151</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3778</v>
+        <v>3780</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>174081</v>
+        <v>175127</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27845</v>
+        <v>28486</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13771</v>
+        <v>13810</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>12994</v>
+        <v>13139</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1488550</v>
+        <v>1488844</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>37902</v>
+        <v>37906</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1295374</v>
+        <v>1334282</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>28702</v>
+        <v>29499</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>260241</v>
+        <v>260859</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>10275</v>
+        <v>10292</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>255571</v>
+        <v>255860</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>7716</v>
+        <v>7727</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Number 1 Option or Championship Co Star? #RichardJefferson #NBA #Knicks #karlanthonytowns</t>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>60675</v>
+        <v>92430</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1658</v>
+        <v>3127</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>592422</v>
+        <v>598014</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4156848</v>
+        <v>4246469</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>75537</v>
+        <v>75895</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>168000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163140</v>
+        <v>163074</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157186</v>
+        <v>157120</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153703</v>
+        <v>153637</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149218</v>
+        <v>149152</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142716</v>
+        <v>142650</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139428</v>
+        <v>139362</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135580</v>
+        <v>135514</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124559</v>
+        <v>124493</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119976</v>
+        <v>119910</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116358</v>
+        <v>116292</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115354</v>
+        <v>115288</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110259</v>
+        <v>110193</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101244</v>
+        <v>101178</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97424</v>
+        <v>97358</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93821</v>
+        <v>93755</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93319</v>
+        <v>93253</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89747</v>
+        <v>89681</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88236</v>
+        <v>88170</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88071</v>
+        <v>88005</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87989</v>
+        <v>87923</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87067</v>
+        <v>87001</v>
       </c>
     </row>
     <row r="6">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>55</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4824807</v>
+        <v>4920378</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>75537</v>
+        <v>75895</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9369,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 15, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 16, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>73477</v>
+        <v>106102</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2029</v>
+        <v>2648</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>68148</v>
+        <v>68454</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1937</v>
+        <v>1941</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>35214</v>
+        <v>35544</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2106</v>
+        <v>2118</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>72</v>
@@ -9576,364 +9576,397 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>GirlsTripp 071626 FinalCutVideo</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>204151</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>3780</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>204309</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3781</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>175127</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>2201</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>175992</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2202</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>40983</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>921</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>28486</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>510</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D15" s="6" t="n">
+        <v>28871</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>514</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>19230</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1489252</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>37913</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1365881</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>30023</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>261423</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>10305</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Channing REFUSES To Call Kawhi a Top 25 Player... Perk LOSES It</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>13810</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>248</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>256089</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>7732</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Shump Asks RJ: What Happened To The Showtime Lakers?</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>13139</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>248</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>150801</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>4571</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>1488844</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>37906</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1334282</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>29499</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>260859</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>10292</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>255860</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>7727</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>92430</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>3127</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9941,9 +9974,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>598014</v>
+        <v>677869</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4246469</v>
+        <v>4391355</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>75895</v>
+        <v>76657</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>168000</v>
+        <v>169000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163074</v>
+        <v>163524</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157120</v>
+        <v>157570</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153637</v>
+        <v>154087</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149152</v>
+        <v>149602</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142650</v>
+        <v>143100</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139362</v>
+        <v>139812</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135514</v>
+        <v>135964</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124493</v>
+        <v>124943</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119910</v>
+        <v>120360</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116292</v>
+        <v>116742</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115288</v>
+        <v>115738</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110193</v>
+        <v>110643</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101178</v>
+        <v>101628</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97358</v>
+        <v>97808</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93755</v>
+        <v>94205</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93253</v>
+        <v>93703</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89681</v>
+        <v>90131</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88170</v>
+        <v>88620</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88005</v>
+        <v>88455</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87923</v>
+        <v>88373</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87001</v>
+        <v>87451</v>
       </c>
     </row>
     <row r="6">
@@ -6742,25 +6742,25 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>56</v>
-      </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>26</v>
@@ -6772,19 +6772,19 @@
         <v>29</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.863</v>
+        <v>0.853</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4920378</v>
+        <v>5145881</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>75895</v>
+        <v>76657</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 16, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 17, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>106102</v>
+        <v>122393</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2648</v>
+        <v>2927</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>68454</v>
+        <v>68714</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>35544</v>
+        <v>35758</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
+          <t>Richard Jefferson Crashes Girls Tripp + Cynthia Cooper STILL 'Good for 10 Points' at WNBA All-Star</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2118</v>
+        <v>2270</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>GirlsTripp 071626 FinalCutVideo</t>
+          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204309</v>
+        <v>204455</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3781</v>
+        <v>3785</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>175992</v>
+        <v>176789</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2202</v>
+        <v>2210</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>40983</v>
+        <v>57930</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>921</v>
+        <v>1291</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
+          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>28871</v>
+        <v>33501</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>514</v>
+        <v>462</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
+          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>19230</v>
+        <v>29009</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>317</v>
+        <v>518</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1489252</v>
+        <v>1491296</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37913</v>
+        <v>37934</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1365881</v>
+        <v>1398074</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>30023</v>
+        <v>30648</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>261423</v>
+        <v>262097</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10305</v>
+        <v>10326</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>256089</v>
+        <v>256388</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7732</v>
+        <v>7741</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>150801</v>
+        <v>182651</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4571</v>
+        <v>5346</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>677869</v>
+        <v>771768</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4391355</v>
+        <v>4566399</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>76657</v>
+        <v>77385</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>169000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163524</v>
+        <v>163010</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157570</v>
+        <v>157056</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154087</v>
+        <v>153573</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149602</v>
+        <v>149088</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143100</v>
+        <v>142586</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139812</v>
+        <v>139298</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135964</v>
+        <v>135450</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124943</v>
+        <v>124429</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120360</v>
+        <v>119846</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116742</v>
+        <v>116228</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115738</v>
+        <v>115224</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110643</v>
+        <v>110129</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101628</v>
+        <v>101114</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97808</v>
+        <v>97294</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>94205</v>
+        <v>93691</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93703</v>
+        <v>93189</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90131</v>
+        <v>89617</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88620</v>
+        <v>88106</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88455</v>
+        <v>87941</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88373</v>
+        <v>87859</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87451</v>
+        <v>86937</v>
       </c>
     </row>
     <row r="6">
@@ -6742,34 +6742,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>23</v>
@@ -6778,7 +6778,7 @@
         <v>29</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.853</v>
+        <v>0.843</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5145881</v>
+        <v>5415552</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>76657</v>
+        <v>77385</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 17, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 18, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>122393</v>
+        <v>129336</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2927</v>
+        <v>3084</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>68714</v>
+        <v>68847</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>35758</v>
+        <v>35958</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2270</v>
+        <v>4986</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2136</v>
+        <v>2156</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204455</v>
+        <v>204548</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3785</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>176789</v>
+        <v>177795</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2210</v>
+        <v>2215</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>57930</v>
+        <v>69044</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1291</v>
+        <v>1556</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33501</v>
+        <v>44789</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>462</v>
+        <v>559</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29009</v>
+        <v>29125</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>518</v>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1491296</v>
+        <v>1492261</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37934</v>
+        <v>37946</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1398074</v>
+        <v>1425577</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>30648</v>
+        <v>31164</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>262097</v>
+        <v>262507</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10326</v>
+        <v>10337</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>256388</v>
+        <v>256704</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7741</v>
+        <v>7753</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>182651</v>
+        <v>225813</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>5346</v>
+        <v>6319</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>771768</v>
+        <v>831823</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4566399</v>
+        <v>4821423</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>77385</v>
+        <v>77946</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>169000</v>
+        <v>170000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163010</v>
+        <v>163624</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157056</v>
+        <v>157670</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153573</v>
+        <v>154187</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149088</v>
+        <v>149702</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142586</v>
+        <v>143200</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139298</v>
+        <v>139912</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135450</v>
+        <v>136064</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124429</v>
+        <v>125043</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119846</v>
+        <v>120460</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116228</v>
+        <v>116842</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115224</v>
+        <v>115838</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110129</v>
+        <v>110743</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101114</v>
+        <v>101728</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97294</v>
+        <v>97908</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93691</v>
+        <v>94305</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93189</v>
+        <v>93803</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89617</v>
+        <v>90231</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88106</v>
+        <v>88720</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87941</v>
+        <v>88555</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87859</v>
+        <v>88473</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86937</v>
+        <v>87551</v>
       </c>
     </row>
     <row r="6">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.843</v>
+        <v>0.841</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5415552</v>
+        <v>5731192</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>77385</v>
+        <v>77946</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 18, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 19, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>129336</v>
+        <v>136080</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3084</v>
+        <v>3202</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>68847</v>
+        <v>69077</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1948</v>
+        <v>1957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>35958</v>
+        <v>36120</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4986</v>
+        <v>6284</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2156</v>
+        <v>2165</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>73</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204548</v>
+        <v>204686</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3785</v>
+        <v>3787</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>177795</v>
+        <v>179400</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2215</v>
+        <v>2224</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>69044</v>
+        <v>76922</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1556</v>
+        <v>1694</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>44789</v>
+        <v>51735</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29125</v>
+        <v>29209</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>518</v>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1492261</v>
+        <v>1493362</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37946</v>
+        <v>37964</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1425577</v>
+        <v>1451281</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>31164</v>
+        <v>31757</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>262507</v>
+        <v>277493</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10337</v>
+        <v>7734</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>256704</v>
+        <v>262818</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7753</v>
+        <v>10345</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
+          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>225813</v>
+        <v>256908</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>6319</v>
+        <v>7757</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>831823</v>
+        <v>872763</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4821423</v>
+        <v>5076710</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>77946</v>
+        <v>78328</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5599,67 +5599,67 @@
         <v>170000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163624</v>
+        <v>163312</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157670</v>
+        <v>157358</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154187</v>
+        <v>153875</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149702</v>
+        <v>149390</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143200</v>
+        <v>142888</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139912</v>
+        <v>139600</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>136064</v>
+        <v>135752</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>125043</v>
+        <v>124731</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120460</v>
+        <v>120148</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116842</v>
+        <v>116530</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115838</v>
+        <v>115526</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110743</v>
+        <v>110431</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101728</v>
+        <v>101416</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97908</v>
+        <v>97596</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>94305</v>
+        <v>93993</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93803</v>
+        <v>93491</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90231</v>
+        <v>89919</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88720</v>
+        <v>88408</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88555</v>
+        <v>88243</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88473</v>
+        <v>88161</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87551</v>
+        <v>87239</v>
       </c>
     </row>
     <row r="6">
@@ -6742,28 +6742,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>60</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>53</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>32</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>37</v>
@@ -6775,13 +6775,13 @@
         <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>29</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5731192</v>
+        <v>6027801</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>77946</v>
+        <v>78328</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 19, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 20, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>136080</v>
+        <v>142679</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3202</v>
+        <v>3314</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69077</v>
+        <v>69300</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36120</v>
+        <v>36280</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6284</v>
+        <v>7050</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2165</v>
+        <v>2176</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>73</v>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204686</v>
+        <v>204815</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3787</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>179400</v>
+        <v>182639</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2224</v>
+        <v>2256</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>76922</v>
+        <v>80868</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1694</v>
+        <v>1753</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>51735</v>
+        <v>56836</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29209</v>
+        <v>29248</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1493362</v>
+        <v>1494449</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37964</v>
+        <v>37981</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1451281</v>
+        <v>1470651</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>31757</v>
+        <v>32234</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>277493</v>
+        <v>326353</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7734</v>
+        <v>9128</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>262818</v>
+        <v>264278</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10345</v>
+        <v>6626</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Is Ja Morant Memphis Grizzlies’ MOST POPULAR Player? RJ &amp; Perk Disagree #JaMorant #Nike #nba</t>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>256908</v>
+        <v>263180</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7757</v>
+        <v>10354</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>872763</v>
+        <v>902800</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5076710</v>
+        <v>5349329</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>78328</v>
+        <v>78836</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>170000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163312</v>
+        <v>162942</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157358</v>
+        <v>156988</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153875</v>
+        <v>153505</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149390</v>
+        <v>149020</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142888</v>
+        <v>142518</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139600</v>
+        <v>139230</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135752</v>
+        <v>135382</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124731</v>
+        <v>124361</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120148</v>
+        <v>119778</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116530</v>
+        <v>116160</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115526</v>
+        <v>115156</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110431</v>
+        <v>110061</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101416</v>
+        <v>101046</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97596</v>
+        <v>97226</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93993</v>
+        <v>93623</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93491</v>
+        <v>93121</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89919</v>
+        <v>89549</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88408</v>
+        <v>88038</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88243</v>
+        <v>87873</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88161</v>
+        <v>87791</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87239</v>
+        <v>86869</v>
       </c>
     </row>
     <row r="6">
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="K8" s="7" t="n">
+      <c r="M8" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>31</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>29</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.842</v>
+        <v>0.845</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6027801</v>
+        <v>6330965</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>78328</v>
+        <v>78836</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 20, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 21, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>142679</v>
+        <v>146620</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3314</v>
+        <v>3385</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69300</v>
+        <v>69488</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36280</v>
+        <v>36448</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Richard Jefferson Crashes Girls Tripp + Cynthia Cooper STILL 'Good for 10 Points' at WNBA All-Star</t>
+          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>7050</v>
+        <v>26369</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>201</v>
+        <v>569</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Ty Young: They Told Me to "Just Play Basketball" &amp; How the W Finally Caught Up</t>
+          <t>Richard Jefferson Crashes Girls Tripp + Cynthia Cooper STILL 'Good for 10 Points' at WNBA All-Star</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2176</v>
+        <v>7557</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204815</v>
+        <v>204961</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3787</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>182639</v>
+        <v>185654</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2256</v>
+        <v>2273</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>80868</v>
+        <v>83697</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1753</v>
+        <v>1807</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>56836</v>
+        <v>60884</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29248</v>
+        <v>29280</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1494449</v>
+        <v>1495009</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37981</v>
+        <v>37988</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1470651</v>
+        <v>1483667</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>32234</v>
+        <v>32522</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
+          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>326353</v>
+        <v>382660</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>9128</v>
+        <v>5524</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>264278</v>
+        <v>356880</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>6626</v>
+        <v>9890</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>263180</v>
+        <v>309083</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10354</v>
+        <v>7346</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>902800</v>
+        <v>927284</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5349329</v>
+        <v>5566525</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>78836</v>
+        <v>79292</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>170000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162942</v>
+        <v>162683</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156988</v>
+        <v>156729</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153505</v>
+        <v>153246</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149020</v>
+        <v>148761</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142518</v>
+        <v>142259</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139230</v>
+        <v>138971</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135382</v>
+        <v>135123</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124361</v>
+        <v>124102</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119778</v>
+        <v>119519</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116160</v>
+        <v>115901</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115156</v>
+        <v>114897</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110061</v>
+        <v>109802</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101046</v>
+        <v>100787</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97226</v>
+        <v>96967</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93623</v>
+        <v>93364</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93121</v>
+        <v>92862</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89549</v>
+        <v>89290</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88038</v>
+        <v>87779</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87873</v>
+        <v>87614</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87791</v>
+        <v>87532</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86869</v>
+        <v>86610</v>
       </c>
     </row>
     <row r="6">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.845</v>
+        <v>0.847</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6330965</v>
+        <v>6573101</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>78836</v>
+        <v>79292</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 21, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 22, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>146620</v>
+        <v>149389</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3385</v>
+        <v>3430</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69488</v>
+        <v>69674</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
+          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36448</v>
+        <v>37351</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>636</v>
+        <v>762</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
+          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26369</v>
+        <v>36533</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>569</v>
+        <v>638</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7557</v>
+        <v>7849</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>204961</v>
+        <v>205040</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>185654</v>
+        <v>188679</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2273</v>
+        <v>2295</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>83697</v>
+        <v>85505</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1807</v>
+        <v>1845</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>60884</v>
+        <v>63796</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29280</v>
+        <v>29307</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
+          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1495009</v>
+        <v>1498782</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>37988</v>
+        <v>32825</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
+          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1483667</v>
+        <v>1495469</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>32522</v>
+        <v>37991</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>382660</v>
+        <v>445469</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5524</v>
+        <v>6233</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>356880</v>
+        <v>381352</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>9890</v>
+        <v>10312</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>309083</v>
+        <v>335070</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7346</v>
+        <v>7815</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>927284</v>
+        <v>972207</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5566525</v>
+        <v>5918852</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>79292</v>
+        <v>79718</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5599,67 +5599,67 @@
         <v>170000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162683</v>
+        <v>162367</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156729</v>
+        <v>156413</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153246</v>
+        <v>152930</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148761</v>
+        <v>148445</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142259</v>
+        <v>141943</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138971</v>
+        <v>138655</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135123</v>
+        <v>134807</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124102</v>
+        <v>123786</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119519</v>
+        <v>119203</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115901</v>
+        <v>115585</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114897</v>
+        <v>114581</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109802</v>
+        <v>109486</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100787</v>
+        <v>100471</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96967</v>
+        <v>96651</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93364</v>
+        <v>93048</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92862</v>
+        <v>92546</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89290</v>
+        <v>88974</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87779</v>
+        <v>87463</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87614</v>
+        <v>87298</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87532</v>
+        <v>87216</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86610</v>
+        <v>86294</v>
       </c>
     </row>
     <row r="6">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>59</v>
@@ -6754,19 +6754,19 @@
         <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>38</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>30</v>
@@ -6775,13 +6775,13 @@
         <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.847</v>
+        <v>0.849</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6573101</v>
+        <v>6970777</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>79292</v>
+        <v>79718</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 22, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 23, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>149389</v>
+        <v>150913</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3430</v>
+        <v>3473</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69674</v>
+        <v>69769</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>37351</v>
+        <v>40302</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>762</v>
+        <v>805</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36533</v>
+        <v>36603</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>638</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7849</v>
+        <v>8043</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205040</v>
+        <v>205094</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3788</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>188679</v>
+        <v>191155</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2295</v>
+        <v>2311</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>85505</v>
+        <v>86523</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1845</v>
+        <v>1874</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>63796</v>
+        <v>66229</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29307</v>
+        <v>29331</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>521</v>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1498782</v>
+        <v>1506297</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>32825</v>
+        <v>32968</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1495469</v>
+        <v>1495882</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>37991</v>
+        <v>37995</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>445469</v>
+        <v>456137</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6233</v>
+        <v>6372</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>381352</v>
+        <v>390623</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10312</v>
+        <v>10474</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>335070</v>
+        <v>339156</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7815</v>
+        <v>7890</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>972207</v>
+        <v>1011322</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5918852</v>
+        <v>6103362</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>79718</v>
+        <v>80173</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162367</v>
+        <v>163151</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156413</v>
+        <v>157197</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>152930</v>
+        <v>153714</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148445</v>
+        <v>149229</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>141943</v>
+        <v>142727</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138655</v>
+        <v>139439</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>134807</v>
+        <v>135591</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>123786</v>
+        <v>124570</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119203</v>
+        <v>119987</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115585</v>
+        <v>116369</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114581</v>
+        <v>115365</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109486</v>
+        <v>110270</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100471</v>
+        <v>101255</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96651</v>
+        <v>97435</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93048</v>
+        <v>93832</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92546</v>
+        <v>93330</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>88974</v>
+        <v>89758</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87463</v>
+        <v>88247</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87298</v>
+        <v>88082</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87216</v>
+        <v>88000</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86294</v>
+        <v>87078</v>
       </c>
     </row>
     <row r="6">
@@ -6742,25 +6742,25 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>25</v>
@@ -6769,7 +6769,7 @@
         <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
@@ -6778,10 +6778,10 @@
         <v>26</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6970777</v>
+        <v>7194857</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>79718</v>
+        <v>80173</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 23, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 24, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>150913</v>
+        <v>152521</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3473</v>
+        <v>3502</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69769</v>
+        <v>69890</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>40302</v>
+        <v>41762</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>805</v>
+        <v>824</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36603</v>
+        <v>36685</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8043</v>
+        <v>8178</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205094</v>
+        <v>205146</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3788</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>191155</v>
+        <v>193353</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2311</v>
+        <v>2323</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>86523</v>
+        <v>87610</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1874</v>
+        <v>1892</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66229</v>
+        <v>67703</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
+          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29331</v>
+        <v>33184</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>521</v>
+        <v>762</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1506297</v>
+        <v>1512842</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>32968</v>
+        <v>33070</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1495882</v>
+        <v>1496407</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>37995</v>
+        <v>38003</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>456137</v>
+        <v>459325</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6372</v>
+        <v>6416</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>390623</v>
+        <v>397676</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10474</v>
+        <v>10592</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>339156</v>
+        <v>339857</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7890</v>
+        <v>7914</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1011322</v>
+        <v>1032437</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6103362</v>
+        <v>6165747</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80173</v>
+        <v>80479</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>171000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163151</v>
+        <v>163033</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157197</v>
+        <v>157079</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153714</v>
+        <v>153596</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149229</v>
+        <v>149111</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142727</v>
+        <v>142609</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139439</v>
+        <v>139321</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135591</v>
+        <v>135473</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124570</v>
+        <v>124452</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119987</v>
+        <v>119869</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116369</v>
+        <v>116251</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115365</v>
+        <v>115247</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110270</v>
+        <v>110152</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101255</v>
+        <v>101137</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97435</v>
+        <v>97317</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93832</v>
+        <v>93714</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93330</v>
+        <v>93212</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89758</v>
+        <v>89640</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88247</v>
+        <v>88129</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88082</v>
+        <v>87964</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88000</v>
+        <v>87882</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87078</v>
+        <v>86960</v>
       </c>
     </row>
     <row r="6">
@@ -6742,22 +6742,22 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>36</v>
@@ -6781,7 +6781,7 @@
         <v>38</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.848</v>
+        <v>0.847</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7194857</v>
+        <v>7278663</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80173</v>
+        <v>80479</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>152521</v>
+        <v>153516</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3502</v>
+        <v>3510</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69890</v>
+        <v>69931</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1964</v>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>41762</v>
+        <v>42317</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36685</v>
+        <v>36724</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8178</v>
+        <v>8200</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205146</v>
+        <v>205166</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3788</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>193353</v>
+        <v>194416</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2323</v>
+        <v>2330</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>87610</v>
+        <v>87828</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>67703</v>
+        <v>68138</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>33184</v>
+        <v>44004</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>762</v>
+        <v>952</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1512842</v>
+        <v>1515531</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33070</v>
+        <v>33117</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1496407</v>
+        <v>1496711</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38003</v>
+        <v>38010</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>459325</v>
+        <v>463545</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6416</v>
+        <v>6502</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>397676</v>
+        <v>401006</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10592</v>
+        <v>10645</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>339857</v>
+        <v>340138</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7914</v>
+        <v>7923</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -6748,28 +6748,28 @@
         <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
@@ -6778,13 +6778,13 @@
         <v>26</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 24, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 25, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>153516</v>
+        <v>154188</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3510</v>
+        <v>3525</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69931</v>
+        <v>69979</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1964</v>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>42317</v>
+        <v>42661</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36724</v>
+        <v>36748</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>641</v>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8200</v>
+        <v>8237</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>237</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205166</v>
+        <v>205193</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>194416</v>
+        <v>195054</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2330</v>
+        <v>2335</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>87828</v>
+        <v>87979</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>68138</v>
+        <v>68606</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>44004</v>
+        <v>49920</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>952</v>
+        <v>1048</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1515531</v>
+        <v>1521740</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33117</v>
+        <v>33211</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
+          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1496711</v>
+        <v>467942</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38010</v>
+        <v>6570</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>463545</v>
+        <v>405216</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6502</v>
+        <v>10699</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
+          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>401006</v>
+        <v>340509</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10645</v>
+        <v>7927</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
+          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>340138</v>
+        <v>264035</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7923</v>
+        <v>10393</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1032437</v>
+        <v>1081130</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6165747</v>
+        <v>6252752</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80479</v>
+        <v>80757</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>171000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163033</v>
+        <v>162861</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157079</v>
+        <v>156907</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153596</v>
+        <v>153424</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149111</v>
+        <v>148939</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142609</v>
+        <v>142437</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139321</v>
+        <v>139149</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135473</v>
+        <v>135301</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124452</v>
+        <v>124280</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119869</v>
+        <v>119697</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116251</v>
+        <v>116079</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115247</v>
+        <v>115075</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110152</v>
+        <v>109980</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101137</v>
+        <v>100965</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97317</v>
+        <v>97145</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93714</v>
+        <v>93542</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93212</v>
+        <v>93040</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89640</v>
+        <v>89468</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88129</v>
+        <v>87957</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87964</v>
+        <v>87792</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87882</v>
+        <v>87710</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86960</v>
+        <v>86788</v>
       </c>
     </row>
     <row r="6">
@@ -6742,16 +6742,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>60</v>
@@ -6760,31 +6760,31 @@
         <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.847</v>
+        <v>0.843</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7278663</v>
+        <v>7414639</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80479</v>
+        <v>80757</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>154188</v>
+        <v>154892</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3525</v>
+        <v>3539</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>69979</v>
+        <v>70009</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>42661</v>
+        <v>42839</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36748</v>
+        <v>36756</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>641</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8237</v>
+        <v>8269</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205193</v>
+        <v>205209</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9663,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
+          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>195054</v>
+        <v>88121</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2335</v>
+        <v>1900</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,19 +9696,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
+          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>87979</v>
+        <v>68931</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1898</v>
+        <v>726</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
+          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>68606</v>
+        <v>52903</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>725</v>
+        <v>1108</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
+          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>49920</v>
+        <v>29361</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1048</v>
+        <v>524</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1521740</v>
+        <v>1524483</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33211</v>
+        <v>33263</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>467942</v>
+        <v>469538</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6570</v>
+        <v>6601</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>405216</v>
+        <v>407106</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10699</v>
+        <v>10734</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>340509</v>
+        <v>340639</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7927</v>
+        <v>7928</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>264035</v>
+        <v>264067</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10393</v>
+        <v>10394</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1081130</v>
+        <v>1081149</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6252752</v>
+        <v>6252846</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80757</v>
+        <v>80759</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>33</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7414639</v>
+        <v>7414754</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80757</v>
+        <v>80759</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 25, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 26, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>154892</v>
+        <v>155836</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3539</v>
+        <v>3556</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70009</v>
+        <v>70068</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>42839</v>
+        <v>43128</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36756</v>
+        <v>36792</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8269</v>
+        <v>8293</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205209</v>
+        <v>205234</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9663,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
+          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>88121</v>
+        <v>196179</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1900</v>
+        <v>2342</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,19 +9696,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
+          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>68931</v>
+        <v>88235</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>726</v>
+        <v>1903</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
+          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>52903</v>
+        <v>69320</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1108</v>
+        <v>727</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Channing Frye Predicts Where LeBron WON’T Sign</t>
+          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>29361</v>
+        <v>56596</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>524</v>
+        <v>1169</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1524483</v>
+        <v>1531191</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33263</v>
+        <v>33355</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
+          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>469538</v>
+        <v>1497234</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6601</v>
+        <v>38021</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
+          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>407106</v>
+        <v>472999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10734</v>
+        <v>6659</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
+          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>340639</v>
+        <v>410349</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7928</v>
+        <v>10786</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Iman Shumpert Shares Cavs 2016 Championship BANGER! #nba #Cavs</t>
+          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>264067</v>
+        <v>341109</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10394</v>
+        <v>7937</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1081149</v>
+        <v>1116439</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6252846</v>
+        <v>6365590</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80759</v>
+        <v>80964</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5599,67 +5599,67 @@
         <v>171000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162861</v>
+        <v>171000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156907</v>
+        <v>171000</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153424</v>
+        <v>171000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148939</v>
+        <v>171000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142437</v>
+        <v>171000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139149</v>
+        <v>171000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135301</v>
+        <v>171000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124280</v>
+        <v>171000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119697</v>
+        <v>171000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116079</v>
+        <v>171000</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115075</v>
+        <v>171000</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109980</v>
+        <v>171000</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100965</v>
+        <v>171000</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97145</v>
+        <v>171000</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93542</v>
+        <v>171000</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93040</v>
+        <v>171000</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89468</v>
+        <v>171000</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87957</v>
+        <v>171000</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87792</v>
+        <v>171000</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87710</v>
+        <v>171000</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86788</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="6">
@@ -6742,40 +6742,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>52</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>38</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.843</v>
+        <v>0.842</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7414754</v>
+        <v>7562993</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80759</v>
+        <v>80964</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 26, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 27, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>155836</v>
+        <v>157462</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3556</v>
+        <v>3585</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70068</v>
+        <v>70156</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1966</v>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>43128</v>
+        <v>43624</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36792</v>
+        <v>36827</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8293</v>
+        <v>8322</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205234</v>
+        <v>205272</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>196179</v>
+        <v>197182</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2342</v>
+        <v>2348</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88235</v>
+        <v>88393</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69320</v>
+        <v>69955</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>56596</v>
+        <v>61872</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1169</v>
+        <v>1262</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1531191</v>
+        <v>1545523</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33355</v>
+        <v>33619</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1497234</v>
+        <v>1497469</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38021</v>
+        <v>38025</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>472999</v>
+        <v>479048</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6659</v>
+        <v>6788</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>410349</v>
+        <v>415432</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10786</v>
+        <v>10870</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>341109</v>
+        <v>341960</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7937</v>
+        <v>7961</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1116439</v>
+        <v>1135411</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6365590</v>
+        <v>6492636</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80964</v>
+        <v>81151</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5599,67 +5599,67 @@
         <v>171000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>171000</v>
+        <v>162565</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>171000</v>
+        <v>156611</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171000</v>
+        <v>153128</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>171000</v>
+        <v>148643</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>171000</v>
+        <v>142141</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>171000</v>
+        <v>138853</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>171000</v>
+        <v>135005</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>171000</v>
+        <v>123984</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>171000</v>
+        <v>119401</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>171000</v>
+        <v>115783</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>171000</v>
+        <v>114779</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>171000</v>
+        <v>109684</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>171000</v>
+        <v>100669</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>171000</v>
+        <v>96849</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>171000</v>
+        <v>93246</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>171000</v>
+        <v>92744</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>171000</v>
+        <v>89172</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>171000</v>
+        <v>87661</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>171000</v>
+        <v>87496</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>171000</v>
+        <v>87414</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>171000</v>
+        <v>86492</v>
       </c>
     </row>
     <row r="6">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7562993</v>
+        <v>7709198</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>80964</v>
+        <v>81151</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157462</v>
+        <v>158318</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3585</v>
+        <v>3602</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70156</v>
+        <v>70203</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>43624</v>
+        <v>43883</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36827</v>
+        <v>36844</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>643</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8322</v>
+        <v>8334</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205272</v>
+        <v>205276</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>197182</v>
+        <v>197872</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2348</v>
+        <v>2355</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88393</v>
+        <v>88468</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69955</v>
+        <v>70161</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>61872</v>
+        <v>64896</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1262</v>
+        <v>1319</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1545523</v>
+        <v>1555492</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33619</v>
+        <v>33838</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1497469</v>
+        <v>1497700</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38025</v>
+        <v>38029</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>479048</v>
+        <v>483314</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6788</v>
+        <v>6897</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>415432</v>
+        <v>418753</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10870</v>
+        <v>10948</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>341960</v>
+        <v>342340</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7961</v>
+        <v>7973</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1135411</v>
+        <v>1135119</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6492636</v>
+        <v>6492141</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>81151</v>
+        <v>81149</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -6742,43 +6742,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>61</v>
-      </c>
       <c r="E8" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
@@ -6790,7 +6790,7 @@
         <v>11</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>13</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7709198</v>
+        <v>7708409</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>81151</v>
+        <v>81149</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 27, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 28, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158318</v>
+        <v>159268</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3602</v>
+        <v>3619</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70203</v>
+        <v>70266</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
+          <t>LeBron SIGNS With Philly! Why Didn’t He Return To Miami + What’s Next For The Lakers?</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>43883</v>
+        <v>69047</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>854</v>
+        <v>1529</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
+          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>36844</v>
+        <v>44084</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>643</v>
+        <v>857</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Richard Jefferson Crashes Girls Tripp + Cynthia Cooper STILL 'Good for 10 Points' at WNBA All-Star</t>
+          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8334</v>
+        <v>36879</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>240</v>
+        <v>643</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205276</v>
+        <v>205283</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>197872</v>
+        <v>198368</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88468</v>
+        <v>88507</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>70161</v>
+        <v>70379</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>64896</v>
+        <v>67036</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1319</v>
+        <v>1350</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1555492</v>
+        <v>1567334</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33838</v>
+        <v>34047</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1497700</v>
+        <v>1497917</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38029</v>
+        <v>38032</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>483314</v>
+        <v>486224</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6897</v>
+        <v>6957</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>418753</v>
+        <v>421626</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10948</v>
+        <v>11010</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>342340</v>
+        <v>342667</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7973</v>
+        <v>7979</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1135119</v>
+        <v>1152170</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6492141</v>
+        <v>6608979</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>81149</v>
+        <v>81383</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>171000</v>
+        <v>172000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162565</v>
+        <v>163453</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156611</v>
+        <v>157499</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153128</v>
+        <v>154016</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148643</v>
+        <v>149531</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142141</v>
+        <v>143029</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138853</v>
+        <v>139741</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135005</v>
+        <v>135893</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>123984</v>
+        <v>124872</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119401</v>
+        <v>120289</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115783</v>
+        <v>116671</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114779</v>
+        <v>115667</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109684</v>
+        <v>110572</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100669</v>
+        <v>101557</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96849</v>
+        <v>97737</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93246</v>
+        <v>94134</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92744</v>
+        <v>93632</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89172</v>
+        <v>90060</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87661</v>
+        <v>88549</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87496</v>
+        <v>88384</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87414</v>
+        <v>88302</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86492</v>
+        <v>87380</v>
       </c>
     </row>
     <row r="6">
@@ -6742,37 +6742,37 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>27</v>
@@ -6784,13 +6784,13 @@
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>13</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7708409</v>
+        <v>7842532</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>81149</v>
+        <v>81383</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 28, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 29, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>159268</v>
+        <v>162052</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3619</v>
+        <v>3660</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9485,19 +9485,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>RT SOUNDS OFF On Ja &amp; Kawhi Trades, LeBron Plan &amp; More Free Agency MADNESS!</t>
+          <t>LeBron SIGNS With Philly! Why Didn’t He Return To Miami + What’s Next For The Lakers?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70266</v>
+        <v>119148</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1969</v>
+        <v>2288</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>LeBron SIGNS With Philly! Why Didn’t He Return To Miami + What’s Next For The Lakers?</t>
+          <t>RT SOUNDS OFF On Ja &amp; Kawhi Trades, LeBron Plan &amp; More Free Agency MADNESS!</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>69047</v>
+        <v>70378</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1529</v>
+        <v>1969</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>44084</v>
+        <v>44445</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>36879</v>
+        <v>36956</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>643</v>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205283</v>
+        <v>205299</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3789</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>198368</v>
+        <v>199453</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2358</v>
+        <v>2367</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88507</v>
+        <v>88552</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
+          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>70379</v>
+        <v>73596</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>731</v>
+        <v>1459</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
+          <t>Greg Oden &amp; Boogie On The Most UNGUARDABLE Bigs They Faced</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>67036</v>
+        <v>32151</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1350</v>
+        <v>381</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1567334</v>
+        <v>1590194</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>34047</v>
+        <v>34528</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1497917</v>
+        <v>1498481</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38032</v>
+        <v>38036</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>486224</v>
+        <v>488341</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6957</v>
+        <v>6994</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>421626</v>
+        <v>427662</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>11010</v>
+        <v>11114</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>342667</v>
+        <v>343203</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7979</v>
+        <v>7988</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1152170</v>
+        <v>1233684</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>983319</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6608979</v>
+        <v>6758446</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3317425</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>81383</v>
+        <v>81625</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>169907</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5599,67 +5599,67 @@
         <v>172000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163453</v>
+        <v>163094</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157499</v>
+        <v>157140</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154016</v>
+        <v>153657</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149531</v>
+        <v>149172</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>143029</v>
+        <v>142670</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139741</v>
+        <v>139382</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135893</v>
+        <v>135534</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124872</v>
+        <v>124513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>120289</v>
+        <v>119930</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116671</v>
+        <v>116312</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115667</v>
+        <v>115308</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110572</v>
+        <v>110213</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101557</v>
+        <v>101198</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97737</v>
+        <v>97378</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>94134</v>
+        <v>93775</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93632</v>
+        <v>93273</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>90060</v>
+        <v>89701</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88549</v>
+        <v>88190</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88384</v>
+        <v>88025</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88302</v>
+        <v>87943</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87380</v>
+        <v>87021</v>
       </c>
     </row>
     <row r="6">
@@ -6745,46 +6745,46 @@
         <v>46</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>36</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>37</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.843</v>
+        <v>0.837</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7842532</v>
+        <v>8073755</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4470651</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>81383</v>
+        <v>81625</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>169907</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 29, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 30, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162052</v>
+        <v>164531</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3660</v>
+        <v>3695</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>119148</v>
+        <v>137900</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2288</v>
+        <v>2546</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70378</v>
+        <v>70457</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>44445</v>
+        <v>44741</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>36956</v>
+        <v>37000</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>643</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205299</v>
+        <v>205325</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>199453</v>
+        <v>200536</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2367</v>
+        <v>2379</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88552</v>
+        <v>88594</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1910</v>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>73596</v>
+        <v>81952</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1459</v>
+        <v>1583</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Greg Oden &amp; Boogie On The Most UNGUARDABLE Bigs They Faced</t>
+          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>32151</v>
+        <v>71682</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>381</v>
+        <v>736</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1590194</v>
+        <v>1611822</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>34528</v>
+        <v>34957</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1498481</v>
+        <v>1499147</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38036</v>
+        <v>38045</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>488341</v>
+        <v>489382</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6994</v>
+        <v>7006</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>427662</v>
+        <v>433061</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>11114</v>
+        <v>11222</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>343203</v>
+        <v>343867</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7988</v>
+        <v>8007</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1233684</v>
+        <v>1315757</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>983319</v>
+        <v>983168</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>697914</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6758446</v>
+        <v>6980885</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3317425</v>
+        <v>3317091</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>2062452</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>81625</v>
+        <v>81897</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>169907</v>
+        <v>169880</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>164514</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
@@ -5599,67 +5599,67 @@
         <v>172000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>163094</v>
+        <v>162709</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>157140</v>
+        <v>156755</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153657</v>
+        <v>153272</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>149172</v>
+        <v>148787</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142670</v>
+        <v>142285</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>139382</v>
+        <v>138997</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135534</v>
+        <v>135149</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124513</v>
+        <v>124128</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119930</v>
+        <v>119545</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>116312</v>
+        <v>115927</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115308</v>
+        <v>114923</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>110213</v>
+        <v>109828</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>101198</v>
+        <v>100813</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>97378</v>
+        <v>96993</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93775</v>
+        <v>93390</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93273</v>
+        <v>92888</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89701</v>
+        <v>89316</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88190</v>
+        <v>87805</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88025</v>
+        <v>87640</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87943</v>
+        <v>87558</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87021</v>
+        <v>86636</v>
       </c>
     </row>
     <row r="6">
@@ -6742,40 +6742,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>36</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.837</v>
+        <v>0.833</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.742</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8073755</v>
+        <v>8378539</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4470651</v>
+        <v>4470139</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2924880</v>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>81625</v>
+        <v>81897</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>169907</v>
+        <v>169880</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>164514</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 30, 2026</t>
+          <t>⭐ BEST OF — Jul 01 – Jul 31, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>164531</v>
+        <v>167339</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3695</v>
+        <v>3734</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>137900</v>
+        <v>146652</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2546</v>
+        <v>2641</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70457</v>
+        <v>70554</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>44741</v>
+        <v>45050</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>37000</v>
+        <v>37031</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>643</v>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>205325</v>
+        <v>205351</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>3790</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>200536</v>
+        <v>201541</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2379</v>
+        <v>2386</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88594</v>
+        <v>88638</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>81952</v>
+        <v>87201</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1583</v>
+        <v>1653</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>71682</v>
+        <v>72390</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1611822</v>
+        <v>1629747</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>34957</v>
+        <v>35304</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1499147</v>
+        <v>1499819</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>38045</v>
+        <v>38052</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>489382</v>
+        <v>490249</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7006</v>
+        <v>7022</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>433061</v>
+        <v>438288</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>11222</v>
+        <v>11346</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>343867</v>
+        <v>344603</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8007</v>
+        <v>8031</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1315757</v>
+        <v>1315769</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>983168</v>
+        <v>983319</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>697914</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6980885</v>
+        <v>6980921</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3317091</v>
+        <v>3317425</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>2062452</v>
@@ -918,7 +918,7 @@
         <v>81897</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>169880</v>
+        <v>169907</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>164514</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8378539</v>
+        <v>8378587</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4470139</v>
+        <v>4470651</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2924880</v>
@@ -9169,7 +9169,7 @@
         <v>81897</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>169880</v>
+        <v>169907</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>164514</v>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>167339</v>
+        <v>167418</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3734</v>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>146652</v>
+        <v>146904</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2641</v>
+        <v>2646</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45050</v>
+        <v>45060</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>873</v>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>37031</v>
+        <v>37032</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>643</v>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>201541</v>
+        <v>201595</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>87201</v>
+        <v>87306</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1629747</v>
+        <v>1630213</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>35304</v>
+        <v>35328</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1499819</v>
+        <v>1499836</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>38052</v>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>490249</v>
+        <v>490279</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7022</v>
+        <v>7023</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>438288</v>
+        <v>438457</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>11346</v>
+        <v>11348</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>344603</v>
+        <v>344629</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8031</v>
+        <v>8032</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,15 +128,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -580,112 +571,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -696,22 +687,22 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>9</v>
@@ -720,46 +711,46 @@
         <v>9</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="U4" s="6" t="n">
         <v>5</v>
       </c>
       <c r="V4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -768,71 +759,73 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>1315769</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>983319</v>
-      </c>
-      <c r="D5" s="7" t="n">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>1376497</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>983168</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>697914</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>790809</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>999377</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>456937</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>733899</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <v>1819209</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="8" t="n">
         <v>1237011</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="L5" s="8" t="n">
         <v>951387</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>461276</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="8" t="n">
         <v>1296821</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="8" t="n">
         <v>1515762</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="P5" s="8" t="n">
         <v>606682</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="8" t="n">
         <v>629557</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="R5" s="8" t="n">
         <v>115398</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="8" t="n">
         <v>322450</v>
       </c>
-      <c r="S5" s="7" t="n">
+      <c r="T5" s="8" t="n">
         <v>87239</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="8" t="n">
         <v>67472</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="V5" s="8" t="n">
         <v>48198</v>
       </c>
-      <c r="V5" s="7" t="n">
+      <c r="W5" s="8" t="n">
         <v>114534</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>75408</v>
       </c>
     </row>
     <row r="6">
@@ -841,71 +834,73 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>6980921</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3317425</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>7143146</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>3317091</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>2062452</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>2731804</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>2437458</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>1412041</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>1021398</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>1102899</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="8" t="n">
         <v>920589</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="L6" s="8" t="n">
         <v>542576</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>390738</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="8" t="n">
         <v>1348061</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="8" t="n">
         <v>2030353</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="P6" s="8" t="n">
         <v>545861</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="8" t="n">
         <v>130006</v>
       </c>
-      <c r="Q6" s="7" t="n">
+      <c r="R6" s="8" t="n">
         <v>89465</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="8" t="n">
         <v>90474</v>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="T6" s="8" t="n">
         <v>56970</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="8" t="n">
         <v>34237</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="V6" s="8" t="n">
         <v>24015</v>
       </c>
-      <c r="V6" s="7" t="n">
+      <c r="W6" s="8" t="n">
         <v>17758</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>11180</v>
       </c>
     </row>
     <row r="7">
@@ -914,71 +909,73 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>81897</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>169907</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>82082</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>169880</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>164514</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>178277</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="8" t="n">
         <v>211738</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>209927</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>90638</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>365</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="8" t="n">
         <v>405</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="L7" s="8" t="n">
         <v>381</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>220</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="8" t="n">
         <v>386</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="P7" s="8" t="n">
         <v>37296</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="8" t="n">
         <v>4972</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="R7" s="8" t="n">
         <v>7173</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="8" t="n">
         <v>1399</v>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="T7" s="8" t="n">
         <v>78402</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="8" t="n">
         <v>3965</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="V7" s="8" t="n">
         <v>11199</v>
       </c>
-      <c r="V7" s="7" t="n">
+      <c r="W7" s="8" t="n">
         <v>40604</v>
-      </c>
-      <c r="W7" s="7" t="n">
-        <v>33838</v>
       </c>
     </row>
     <row r="8">
@@ -987,102 +984,102 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>23305</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>23182</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>25288</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>24712</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>22848</v>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1276,112 +1273,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1389,22 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>9</v>
@@ -1416,46 +1413,46 @@
         <v>9</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="U4" s="6" t="n">
         <v>5</v>
       </c>
       <c r="V4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1469,28 +1466,28 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>4091</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>4887</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>4774</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>4425</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>5522</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
@@ -1574,28 +1571,28 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>65456</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>53760</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>62065</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>66378</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>49702</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>27</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
@@ -1761,112 +1758,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -2110,112 +2107,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2227,112 +2224,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2344,112 +2341,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2695,112 +2692,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2812,112 +2809,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2929,112 +2926,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3280,112 +3277,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3397,112 +3394,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3514,112 +3511,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3865,112 +3862,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3982,112 +3979,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4099,112 +4096,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4450,112 +4447,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4567,112 +4564,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4684,112 +4681,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4918,112 +4915,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5035,112 +5032,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5152,112 +5149,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5473,112 +5470,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -5599,67 +5596,67 @@
         <v>172000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>162709</v>
+        <v>172000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156755</v>
+        <v>162434</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>153272</v>
+        <v>156480</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>148787</v>
+        <v>152997</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>142285</v>
+        <v>148512</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>138997</v>
+        <v>142010</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>135149</v>
+        <v>138722</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>124128</v>
+        <v>134874</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>119545</v>
+        <v>123853</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>115927</v>
+        <v>119270</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>114923</v>
+        <v>115652</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>109828</v>
+        <v>114648</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100813</v>
+        <v>109553</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>96993</v>
+        <v>100538</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>93390</v>
+        <v>96718</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92888</v>
+        <v>93115</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>89316</v>
+        <v>92613</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>87805</v>
+        <v>89041</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87640</v>
+        <v>87530</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87558</v>
+        <v>87365</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>86636</v>
+        <v>87283</v>
       </c>
     </row>
     <row r="6">
@@ -5668,91 +5665,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="8">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="8">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="8">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="8">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="8">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="8">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="8">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="8">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="8">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="8">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="8">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="8">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5771,112 +5768,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5888,112 +5885,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6100,91 +6097,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="8">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="8">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="8">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="8">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="8">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="8">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="8">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="8">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="8">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="8">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="8">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="8">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="8">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="8">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6378,112 +6375,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -6741,71 +6738,73 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C8" s="7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="E8" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="J8" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="J8" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="N8" s="7" t="n">
+      <c r="K8" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="O8" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="P8" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" s="7" t="n">
+      <c r="R8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="T8" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="V8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="7" t="n">
+      <c r="W8" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6814,71 +6813,73 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>0.833</v>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C9" s="12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>0.742</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.705</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.738</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.668</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.679</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="I9" s="12" t="n">
         <v>0.553</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="J9" s="12" t="n">
         <v>0.377</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="K9" s="12" t="n">
         <v>0.427</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="L9" s="12" t="n">
         <v>0.363</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="M9" s="12" t="n">
         <v>0.458</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="N9" s="12" t="n">
         <v>0.51</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="O9" s="12" t="n">
         <v>0.572</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="P9" s="12" t="n">
         <v>0.459</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="Q9" s="12" t="n">
         <v>0.17</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="R9" s="12" t="n">
         <v>0.422</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="S9" s="12" t="n">
         <v>0.218</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="T9" s="12" t="n">
         <v>0.256</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="U9" s="12" t="n">
         <v>0.324</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="V9" s="12" t="n">
         <v>0.288</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="W9" s="12" t="n">
         <v>0.103</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.093</v>
       </c>
     </row>
     <row r="10">
@@ -7573,112 +7574,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -8127,112 +8128,112 @@
     <row r="3">
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>DEC 24</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>NOV 24</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>OCT 24</t>
         </is>
       </c>
     </row>
@@ -8377,112 +8378,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8606,112 +8607,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8835,112 +8836,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8952,71 +8953,73 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>8378587</v>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4470651</v>
+        <v>8601725</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>4470139</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>2924880</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>3700890</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>3648573</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>2078905</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>1845935</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>2922473</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>2158005</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>1494344</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>852234</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>2645268</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>3546812</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>1189839</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="6" t="n">
         <v>764535</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="6" t="n">
         <v>212036</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="T11" s="6" t="n">
         <v>414323</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="6" t="n">
         <v>222611</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="V11" s="6" t="n">
         <v>105674</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="W11" s="6" t="n">
         <v>83412</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>172896</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>120426</v>
       </c>
     </row>
     <row r="12">
@@ -9165,71 +9168,73 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>81897</v>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>169907</v>
+        <v>82082</v>
       </c>
       <c r="E14" s="6" t="n">
+        <v>169880</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>164514</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>178277</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="6" t="n">
         <v>211738</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>209927</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>90638</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>365</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="L14" s="6" t="n">
         <v>405</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>381</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="6" t="n">
         <v>386</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="P14" s="6" t="n">
         <v>697</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="6" t="n">
         <v>37296</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="R14" s="6" t="n">
         <v>4972</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="6" t="n">
         <v>7173</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="T14" s="6" t="n">
         <v>1399</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="6" t="n">
         <v>78402</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="V14" s="6" t="n">
         <v>3965</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="W14" s="6" t="n">
         <v>11199</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="X14" s="6" t="n">
         <v>40604</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>33838</v>
       </c>
     </row>
     <row r="15">
@@ -9369,7 +9374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9384,7 +9389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Jul 01 – Jul 31, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 01, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9444,529 +9449,55 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Boogie Cousins CALLS OUT The Lakers For Doing LeBron DIRTY</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>167418</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>3734</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>LeBron SIGNS With Philly! Why Didn’t He Return To Miami + What’s Next For The Lakers?</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>146904</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>2646</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>RT SOUNDS OFF On Ja &amp; Kawhi Trades, LeBron Plan &amp; More Free Agency MADNESS!</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>70554</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Jaylen Brown’s Team USA SNUB, Hawks FAILED Trae Young &amp; LeBron w/ Grant Hill</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>45060</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>873</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>We Talked About LeBron All Year... Now He’s About to Decide</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>37032</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>643</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SEGMENT CLIPS</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SEGMENT CLIPS</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>RJ Says He KNOWS LeBron's Real Plan... And He's Not Telling</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>205351</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>3790</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Channing Breaks Down the REAL Reason Portland Saves Ja Morant</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>201595</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>"They Like Bron Ain't LeBron" - Boogie Cousins UNLOADS on Lakers</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>88638</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Dillon Brooks BREAKS DOWN The LeBron Meme, 3,000 Makes A Week &amp; His NEW Villain Role</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>87306</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1654</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>The 2016 Cavs Scotland Trip Cost Almost $1 MILLION</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>72390</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Top High School Basketball Recruit is BABY GIANNIS!? #nba #marcusspears #basketball</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>1630213</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>35328</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Imam Shumpert GOES OFF on Lakers Free Agency #LosAngelesLakers #lukadoncic #Lakers</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>1499836</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>38052</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>LeBron’s Next Move Will RUN The NBA?! #NBA #LebronJames</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>490279</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>7023</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>The Time DeMarcus Cousins Learned Why You NEVER Trash Talk Tim Duncan... #nba #basketball</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>438457</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>11348</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Richard Jefferson GOES IN On Fake NBA Narratives #NBA #lebronjames #Lebron</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>344629</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>8032</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9974,9 +9505,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +130,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -765,10 +771,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1376497</v>
+        <v>1432570</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>983168</v>
+        <v>983319</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>697914</v>
@@ -840,10 +846,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>7143146</v>
+        <v>7261977</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3317091</v>
+        <v>3317425</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>2062452</v>
@@ -915,10 +921,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>82082</v>
+        <v>82282</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>169880</v>
+        <v>169907</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>164514</v>
@@ -5599,64 +5605,64 @@
         <v>172000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162434</v>
+        <v>162232</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156480</v>
+        <v>156278</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>152997</v>
+        <v>152795</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148512</v>
+        <v>148310</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142010</v>
+        <v>141808</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>138722</v>
+        <v>138520</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>134874</v>
+        <v>134672</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>123853</v>
+        <v>123651</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119270</v>
+        <v>119068</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115652</v>
+        <v>115450</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114648</v>
+        <v>114446</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109553</v>
+        <v>109351</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100538</v>
+        <v>100336</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>96718</v>
+        <v>96516</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93115</v>
+        <v>92913</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92613</v>
+        <v>92411</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89041</v>
+        <v>88839</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87530</v>
+        <v>87328</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87365</v>
+        <v>87163</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87283</v>
+        <v>87081</v>
       </c>
     </row>
     <row r="6">
@@ -6738,40 +6744,38 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B8" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>51</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>37</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>23</v>
@@ -6780,7 +6784,7 @@
         <v>29</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>31</v>
@@ -6819,7 +6823,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.83</v>
+        <v>0.827</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.742</v>
@@ -8959,10 +8963,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8601725</v>
+        <v>8776829</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4470139</v>
+        <v>4470651</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>2924880</v>
@@ -9174,10 +9178,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>82082</v>
+        <v>82282</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>169880</v>
+        <v>169907</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>164514</v>
@@ -9469,10 +9473,36 @@
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="14" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>No data for this period</t>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>533</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>
@@ -9489,10 +9519,36 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>No data for this period</t>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>2192</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1432570</v>
+        <v>1432543</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>983319</v>
+        <v>983168</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>697914</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>7261977</v>
+        <v>7261886</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3317425</v>
+        <v>3317091</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>2062452</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>169907</v>
+        <v>169880</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>164514</v>
@@ -5599,70 +5599,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>172000</v>
+        <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172000</v>
+        <v>173000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162232</v>
+        <v>163232</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156278</v>
+        <v>157278</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>152795</v>
+        <v>153795</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148310</v>
+        <v>149310</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>141808</v>
+        <v>142808</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>138520</v>
+        <v>139520</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>134672</v>
+        <v>135672</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>123651</v>
+        <v>124651</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119068</v>
+        <v>120068</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115450</v>
+        <v>116450</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114446</v>
+        <v>115446</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109351</v>
+        <v>110351</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100336</v>
+        <v>101336</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>96516</v>
+        <v>97516</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>92913</v>
+        <v>93913</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92411</v>
+        <v>93411</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>88839</v>
+        <v>89839</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87328</v>
+        <v>88328</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87163</v>
+        <v>88163</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87081</v>
+        <v>88081</v>
       </c>
     </row>
     <row r="6">
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8776829</v>
+        <v>8776710</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4470651</v>
+        <v>4470139</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>2924880</v>
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>169907</v>
+        <v>169880</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>164514</v>
@@ -9393,7 +9393,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 01, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 02, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>533</v>
+        <v>1701</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>2192</v>
+        <v>22363</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>58</v>
+        <v>419</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -129,13 +129,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -771,7 +774,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1432543</v>
+        <v>1471778</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>983168</v>
@@ -846,7 +849,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>7261886</v>
+        <v>7378701</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>3317091</v>
@@ -921,7 +924,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>82281</v>
+        <v>82453</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>169880</v>
@@ -5605,64 +5608,64 @@
         <v>173000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163232</v>
+        <v>163090</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157278</v>
+        <v>157136</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153795</v>
+        <v>153653</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149310</v>
+        <v>149168</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142808</v>
+        <v>142666</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139520</v>
+        <v>139378</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135672</v>
+        <v>135530</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124651</v>
+        <v>124509</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120068</v>
+        <v>119926</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116450</v>
+        <v>116308</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115446</v>
+        <v>115304</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110351</v>
+        <v>110209</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101336</v>
+        <v>101194</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97516</v>
+        <v>97374</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93913</v>
+        <v>93771</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93411</v>
+        <v>93269</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89839</v>
+        <v>89697</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88328</v>
+        <v>88186</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88163</v>
+        <v>88021</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88081</v>
+        <v>87939</v>
       </c>
     </row>
     <row r="6">
@@ -6745,7 +6748,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>51</v>
@@ -6757,37 +6760,37 @@
         <v>60</v>
       </c>
       <c r="F8" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>53</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>31</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>21</v>
@@ -6823,7 +6826,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.742</v>
@@ -8963,7 +8966,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8776710</v>
+        <v>8932932</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9178,7 +9181,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>82281</v>
+        <v>82453</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>169880</v>
@@ -9378,7 +9381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9393,7 +9396,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 02, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 03, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9453,10 +9456,36 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>No data for this period</t>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>2246</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>
@@ -9474,33 +9503,33 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1701</v>
+        <v>3287</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9520,40 +9549,139 @@
       <c r="G10" s="14" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22363</v>
+        <v>34786</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>419</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
+        <v>576</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2936</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Lamar Jackson DOESN’T Need A Ring. Here’s Why. #NFL #baltimoreravens #quarterback</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>2720</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>The MOST Intense NFL Rivalry Ever Made Terrell Suggs SICK #nfl #ravens #steelers</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>987</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -768,72 +768,70 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="B5" s="7" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>1471778</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>983168</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <v>697914</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="7" t="n">
         <v>790809</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <v>999377</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="7" t="n">
         <v>456937</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>733899</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="7" t="n">
         <v>1819209</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="K5" s="7" t="n">
         <v>1237011</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="7" t="n">
         <v>951387</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>461276</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="7" t="n">
         <v>1296821</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="7" t="n">
         <v>1515762</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>606682</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="7" t="n">
         <v>629557</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="7" t="n">
         <v>115398</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="7" t="n">
         <v>322450</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="7" t="n">
         <v>87239</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="7" t="n">
         <v>67472</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="7" t="n">
         <v>48198</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="7" t="n">
         <v>114534</v>
       </c>
     </row>
@@ -843,72 +841,70 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
+      <c r="B6" s="7" t="n">
+        <v>90910</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>7378701</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>3317091</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>2062452</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="7" t="n">
         <v>2731804</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="7" t="n">
         <v>2437458</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="7" t="n">
         <v>1412041</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="7" t="n">
         <v>1021398</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="7" t="n">
         <v>1102899</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="K6" s="7" t="n">
         <v>920589</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="7" t="n">
         <v>542576</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>390738</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="7" t="n">
         <v>1348061</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="O6" s="7" t="n">
         <v>2030353</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="P6" s="7" t="n">
         <v>545861</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="7" t="n">
         <v>130006</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="7" t="n">
         <v>89465</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="7" t="n">
         <v>90474</v>
       </c>
-      <c r="T6" s="8" t="n">
+      <c r="T6" s="7" t="n">
         <v>56970</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="7" t="n">
         <v>34237</v>
       </c>
-      <c r="V6" s="8" t="n">
+      <c r="V6" s="7" t="n">
         <v>24015</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="7" t="n">
         <v>17758</v>
       </c>
     </row>
@@ -918,72 +914,70 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>82453</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>169880</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>164514</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="7" t="n">
         <v>178277</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="7" t="n">
         <v>211738</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="7" t="n">
         <v>209927</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="7" t="n">
         <v>90638</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="7" t="n">
         <v>365</v>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="K7" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="7" t="n">
         <v>381</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="7" t="n">
         <v>386</v>
       </c>
-      <c r="O7" s="8" t="n">
+      <c r="O7" s="7" t="n">
         <v>697</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="P7" s="7" t="n">
         <v>37296</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="7" t="n">
         <v>4972</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="7" t="n">
         <v>7173</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="7" t="n">
         <v>1399</v>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="T7" s="7" t="n">
         <v>78402</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="7" t="n">
         <v>3965</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="7" t="n">
         <v>11199</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="7" t="n">
         <v>40604</v>
       </c>
     </row>
@@ -993,102 +987,102 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>23305</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>23182</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>25288</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>24712</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>22848</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2116,112 +2110,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2233,112 +2227,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2350,112 +2344,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2701,112 +2695,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2818,112 +2812,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2935,112 +2929,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3286,112 +3280,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3403,112 +3397,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3520,112 +3514,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3871,112 +3865,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3988,112 +3982,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4105,112 +4099,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4456,112 +4450,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4573,112 +4567,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4690,112 +4684,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4924,112 +4918,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5041,112 +5035,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5158,112 +5152,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5605,67 +5599,67 @@
         <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173000</v>
+        <v>172864</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163090</v>
+        <v>162954</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157136</v>
+        <v>157000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153653</v>
+        <v>153517</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149168</v>
+        <v>149032</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142666</v>
+        <v>142530</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139378</v>
+        <v>139242</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135530</v>
+        <v>135394</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124509</v>
+        <v>124373</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119926</v>
+        <v>119790</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116308</v>
+        <v>116172</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115304</v>
+        <v>115168</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110209</v>
+        <v>110073</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101194</v>
+        <v>101058</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97374</v>
+        <v>97238</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93771</v>
+        <v>93635</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93269</v>
+        <v>93133</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89697</v>
+        <v>89561</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88186</v>
+        <v>88050</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88021</v>
+        <v>87885</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87939</v>
+        <v>87803</v>
       </c>
     </row>
     <row r="6">
@@ -5674,91 +5668,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="7">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5777,112 +5771,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5894,112 +5888,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6106,91 +6100,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="7">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="7">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="7">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="7">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6747,70 +6741,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="B8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="I8" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+      <c r="P8" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6820,10 +6814,8 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="12" t="n">
+        <v>0.662</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8385,112 +8377,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8614,112 +8606,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8843,112 +8835,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8960,10 +8952,8 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="6" t="n">
+        <v>137381</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8932932</v>
@@ -9175,10 +9165,8 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C14" s="6" t="n">
+        <v>152</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82453</v>
@@ -9381,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9396,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 03, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 04, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9472,11 +9460,11 @@
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>2246</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>84</v>
+      <c r="D5" s="7" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>111</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9518,11 +9506,11 @@
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>3287</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>51</v>
+      <c r="D8" s="7" t="n">
+        <v>4540</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>66</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9535,153 +9523,318 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>AntsViralPassTheBallExchange Clip</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>CoachFinchsAnthonyEdwardsRegret Clip</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>WhyMinnesotaTradedForLaMelo Clip</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>BrandonDefendsLaMelosLeadership Clip</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>34786</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>576</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D15" s="7" t="n">
+        <v>37970</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>611</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>2936</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>86</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D16" s="6" t="n">
+        <v>6072</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>146</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Lamar Jackson DOESN’T Need A Ring. Here’s Why. #NFL #baltimoreravens #quarterback</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>2720</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D17" s="7" t="n">
+        <v>4962</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>211</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3248</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>The MOST Intense NFL Rivalry Ever Made Terrell Suggs SICK #nfl #ravens #steelers</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>987</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="D19" s="7" t="n">
+        <v>1534</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9689,7 +9842,7 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46319</v>
+        <v>89230</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1471778</v>
+        <v>1469696</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>983168</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>90910</v>
+        <v>154519</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7378701</v>
+        <v>7376392</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3317091</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>152</v>
+        <v>336</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>82453</v>
+        <v>82444</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>169880</v>
@@ -5599,67 +5599,67 @@
         <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172864</v>
+        <v>172737</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162954</v>
+        <v>162827</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157000</v>
+        <v>156873</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153517</v>
+        <v>153390</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149032</v>
+        <v>148905</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142530</v>
+        <v>142403</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139242</v>
+        <v>139115</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135394</v>
+        <v>135267</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124373</v>
+        <v>124246</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119790</v>
+        <v>119663</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116172</v>
+        <v>116045</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115168</v>
+        <v>115041</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110073</v>
+        <v>109946</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101058</v>
+        <v>100931</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97238</v>
+        <v>97111</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93635</v>
+        <v>93508</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93133</v>
+        <v>93006</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89561</v>
+        <v>89434</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88050</v>
+        <v>87923</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87885</v>
+        <v>87758</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87803</v>
+        <v>87676</v>
       </c>
     </row>
     <row r="6">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>57</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.662</v>
+        <v>0.633</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>137381</v>
+        <v>244085</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8932932</v>
+        <v>8928532</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>152</v>
+        <v>336</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>82453</v>
+        <v>82444</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>169880</v>
@@ -9369,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 04, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 05, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9452,389 +9452,422 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
+          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>12555</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>376</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
           <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>3239</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="D6" s="6" t="n">
+        <v>3548</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>4540</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="D9" s="7" t="n">
+        <v>5410</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>814</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>AntsViralPassTheBallExchange Clip</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>CoachFinchsAnthonyEdwardsRegret Clip</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>WhyMinnesotaTradedForLaMelo Clip</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>40477</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>38974</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>CoachFinchsAnthonyEdwardsRegret Clip</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>7209</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>WhyMinnesotaTradedForLaMelo Clip</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>6277</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>BrandonDefendsLaMelosLeadership Clip</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Lamar Jackson DOESN’T Need A Ring. Here’s Why. #NFL #baltimoreravens #quarterback</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>37970</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>611</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>6072</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>146</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Lamar Jackson DOESN’T Need A Ring. Here’s Why. #NFL #baltimoreravens #quarterback</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>4962</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>211</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>3248</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>175</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>The MOST Intense NFL Rivalry Ever Made Terrell Suggs SICK #nfl #ravens #steelers</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>1534</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9842,9 +9875,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>89230</v>
+        <v>121809</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1469696</v>
+        <v>1469537</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>983168</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>154519</v>
+        <v>202746</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7376392</v>
+        <v>7376275</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3317091</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>336</v>
+        <v>477</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82444</v>
@@ -5599,67 +5599,67 @@
         <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172737</v>
+        <v>172610</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162827</v>
+        <v>162700</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156873</v>
+        <v>156746</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153390</v>
+        <v>153263</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148905</v>
+        <v>148778</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142403</v>
+        <v>142276</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139115</v>
+        <v>138988</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135267</v>
+        <v>135140</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124246</v>
+        <v>124119</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119663</v>
+        <v>119536</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116045</v>
+        <v>115918</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115041</v>
+        <v>114914</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109946</v>
+        <v>109819</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100931</v>
+        <v>100804</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97111</v>
+        <v>96984</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93508</v>
+        <v>93381</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93006</v>
+        <v>92879</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89434</v>
+        <v>89307</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87923</v>
+        <v>87796</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87758</v>
+        <v>87631</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87676</v>
+        <v>87549</v>
       </c>
     </row>
     <row r="6">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>56</v>
@@ -6754,22 +6754,22 @@
         <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>27</v>
@@ -6778,16 +6778,16 @@
         <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.633</v>
+        <v>0.624</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>244085</v>
+        <v>325032</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8928532</v>
+        <v>8928256</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>336</v>
+        <v>477</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82444</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 05, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 06, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>12555</v>
+        <v>15855</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>376</v>
+        <v>458</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3548</v>
+        <v>3661</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5410</v>
+        <v>5816</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>814</v>
+        <v>1482</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9597,19 +9597,19 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>AntsViralPassTheBallExchange Clip</t>
+          <t>Richard Jefferson Predicts Brandon Miller’s FIRST ALL-STAR Season</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>CoachFinchsAnthonyEdwardsRegret Clip</t>
+          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>WhyMinnesotaTradedForLaMelo Clip</t>
+          <t>Anthony Edwards APOLOGIZED To Chris Finch After Their Viral Sideline Blowup</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>40477</v>
+        <v>53213</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1180</v>
+        <v>1529</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>38974</v>
+        <v>39161</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9775,19 +9775,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
+          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>7209</v>
+        <v>8298</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9808,19 +9808,19 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6277</v>
+        <v>7823</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>5850</v>
+        <v>6727</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>121809</v>
+        <v>121122</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1469537</v>
+        <v>1469696</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>983168</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>202746</v>
+        <v>201570</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7376275</v>
+        <v>7376392</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3317091</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>325032</v>
+        <v>323169</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8928256</v>
+        <v>8928532</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>15855</v>
+        <v>17993</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>458</v>
+        <v>502</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3661</v>
+        <v>3652</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>126</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5816</v>
+        <v>6135</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1482</v>
+        <v>2229</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>310</v>
+        <v>661</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>53213</v>
+        <v>70130</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1529</v>
+        <v>1871</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>39161</v>
+        <v>39377</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9775,19 +9775,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>8298</v>
+        <v>19790</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>225</v>
+        <v>347</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9808,19 +9808,19 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
+          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7823</v>
+        <v>8978</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Lamar Jackson DOESN’T Need A Ring. Here’s Why. #NFL #baltimoreravens #quarterback</t>
+          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>6727</v>
+        <v>8159</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>121122</v>
+        <v>120605</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1469696</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>201570</v>
+        <v>201438</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7376392</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>49</v>
@@ -6751,43 +6751,43 @@
         <v>56</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.624</v>
+        <v>0.625</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>323169</v>
+        <v>322520</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8928532</v>
@@ -9369,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>17993</v>
+        <v>19164</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9485,131 +9485,131 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
+          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE” + Why LaMelo Changes Everything</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3920</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
           <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>3652</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D7" s="7" t="n">
+        <v>3684</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Olivia Miles Drops 28, Minnesota Beats Indiana 108-100: 'No Crack In This Team</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>6135</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Richard Jefferson Predicts Brandon Miller’s FIRST ALL-STAR Season</t>
+          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>661</v>
+        <v>6236</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9625,24 +9625,24 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
+          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1</v>
+        <v>3013</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9658,136 +9658,136 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Richard Jefferson Predicts Brandon Miller’s FIRST ALL-STAR Season</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>780</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Anthony Edwards APOLOGIZED To Chris Finch After Their Viral Sideline Blowup</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>ChanningMailbag 080726 FinalCut Video</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>70130</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>1871</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>39377</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>623</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>19790</v>
+        <v>81015</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>347</v>
+        <v>2204</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9803,24 +9803,24 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>8978</v>
+        <v>39463</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>229</v>
+        <v>625</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9836,38 +9836,104 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>25357</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>439</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9249</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Why Dak Prescott Will Never Win MVP Under Jerry Jones 🏈 #nfl #dakprescott #dallascowboys</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>8159</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>230</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>9084</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9875,9 +9941,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>120605</v>
+        <v>156746</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1469696</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>201438</v>
+        <v>297138</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7376392</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>477</v>
+        <v>650</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82444</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -5599,67 +5599,67 @@
         <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172610</v>
+        <v>172463</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162700</v>
+        <v>162553</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156746</v>
+        <v>156599</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153263</v>
+        <v>153116</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148778</v>
+        <v>148631</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142276</v>
+        <v>142129</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>138988</v>
+        <v>138841</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135140</v>
+        <v>134993</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124119</v>
+        <v>123972</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119536</v>
+        <v>119389</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115918</v>
+        <v>115771</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114914</v>
+        <v>114767</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109819</v>
+        <v>109672</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100804</v>
+        <v>100657</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>96984</v>
+        <v>96837</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93381</v>
+        <v>93234</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92879</v>
+        <v>92732</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89307</v>
+        <v>89160</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87796</v>
+        <v>87649</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87631</v>
+        <v>87484</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87549</v>
+        <v>87402</v>
       </c>
     </row>
     <row r="6">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>58</v>
@@ -6757,37 +6757,37 @@
         <v>52</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>38</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.625</v>
+        <v>0.654</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>322520</v>
+        <v>454534</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8928532</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>477</v>
+        <v>650</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82444</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>19164</v>
+        <v>19902</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3920</v>
+        <v>18684</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>265</v>
+        <v>708</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3684</v>
+        <v>3692</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6236</v>
+        <v>6291</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>89</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3013</v>
+        <v>3684</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>780</v>
+        <v>803</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>15</v>
@@ -9696,19 +9696,19 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
+          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9729,16 +9729,16 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>ChanningMailbag 080726 FinalCut Video</t>
+          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>81015</v>
+        <v>92991</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2204</v>
+        <v>2497</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>39463</v>
+        <v>39485</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>25357</v>
+        <v>29092</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>9249</v>
+        <v>20463</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>236</v>
+        <v>826</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>9084</v>
+        <v>9400</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>444</v>
+        <v>242</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6742,34 +6742,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>50</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>52</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>33</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>29</v>
@@ -6778,7 +6778,7 @@
         <v>24</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>38</v>
@@ -6787,7 +6787,7 @@
         <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 06, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 07, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9452,19 +9452,19 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
+          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE” + Why LaMelo Changes Everything</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>19902</v>
+        <v>42197</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>541</v>
+        <v>990</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9485,19 +9485,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE” + Why LaMelo Changes Everything</t>
+          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>18684</v>
+        <v>20925</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>708</v>
+        <v>556</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3692</v>
+        <v>3714</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>127</v>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>282</v>
+        <v>601</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6291</v>
+        <v>6411</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>89</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3684</v>
+        <v>4412</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>803</v>
+        <v>881</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>74</v>
+        <v>846</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>92991</v>
+        <v>120670</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2497</v>
+        <v>2984</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>39485</v>
+        <v>39645</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>29092</v>
+        <v>39127</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>477</v>
+        <v>1585</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>20463</v>
+        <v>33733</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>826</v>
+        <v>537</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>The TRUTH About LaMelo Ball In The Hornets Locker Room #nba #charlottehornets #BrandonMiller</t>
+          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>9400</v>
+        <v>33603</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>242</v>
+        <v>1064</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>156746</v>
+        <v>185212</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1469696</v>
+        <v>1469537</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>983168</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>297138</v>
+        <v>417305</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7376392</v>
+        <v>7376275</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3317091</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>650</v>
+        <v>793</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82444</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -5599,67 +5599,67 @@
         <v>173000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172463</v>
+        <v>172329</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162553</v>
+        <v>162419</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156599</v>
+        <v>156465</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153116</v>
+        <v>152982</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148631</v>
+        <v>148497</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142129</v>
+        <v>141995</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>138841</v>
+        <v>138707</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>134993</v>
+        <v>134859</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>123972</v>
+        <v>123838</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119389</v>
+        <v>119255</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115771</v>
+        <v>115637</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114767</v>
+        <v>114633</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109672</v>
+        <v>109538</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100657</v>
+        <v>100523</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>96837</v>
+        <v>96703</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93234</v>
+        <v>93100</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92732</v>
+        <v>92598</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89160</v>
+        <v>89026</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87649</v>
+        <v>87515</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87484</v>
+        <v>87350</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87402</v>
+        <v>87268</v>
       </c>
     </row>
     <row r="6">
@@ -6742,52 +6742,52 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>58</v>
       </c>
       <c r="E8" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>60</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.654</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>454534</v>
+        <v>603310</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8928532</v>
+        <v>8928256</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>650</v>
+        <v>793</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82444</v>
@@ -9369,7 +9369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 07, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 08, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>42197</v>
+        <v>72323</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>990</v>
+        <v>1530</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>20925</v>
+        <v>22725</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3714</v>
+        <v>3756</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>601</v>
+        <v>756</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9576,364 +9576,397 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>RoadTrippin 081126 CarterBryant FinalCut Video</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>6411</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>6557</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>4412</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>5081</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2371</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Richard Jefferson Predicts Brandon Miller’s FIRST ALL-STAR Season</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>881</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D16" s="7" t="n">
+        <v>947</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>184492</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>4683</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>63075</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2325</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>44545</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>846</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>40735</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>661</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Chris Finch REGRETS Publicly Calling Out Anthony Edwards</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>39927</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>634</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>120670</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>2984</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>39645</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>628</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>39127</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>1585</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>33733</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>537</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>33603</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>1064</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9941,9 +9974,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>185212</v>
+        <v>248566</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1469537</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>417305</v>
+        <v>629142</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7376275</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>793</v>
+        <v>941</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82444</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>173000</v>
+        <v>174000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172329</v>
+        <v>173086</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162419</v>
+        <v>163176</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156465</v>
+        <v>157222</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>152982</v>
+        <v>153739</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148497</v>
+        <v>149254</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>141995</v>
+        <v>142752</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>138707</v>
+        <v>139464</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>134859</v>
+        <v>135616</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>123838</v>
+        <v>124595</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119255</v>
+        <v>120012</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115637</v>
+        <v>116394</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114633</v>
+        <v>115390</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109538</v>
+        <v>110295</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100523</v>
+        <v>101280</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>96703</v>
+        <v>97460</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93100</v>
+        <v>93857</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92598</v>
+        <v>93355</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89026</v>
+        <v>89783</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87515</v>
+        <v>88272</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87350</v>
+        <v>88107</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87268</v>
+        <v>88025</v>
       </c>
     </row>
     <row r="6">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>48</v>
@@ -6751,22 +6751,22 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>41</v>
@@ -6781,7 +6781,7 @@
         <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>30</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>603310</v>
+        <v>878649</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8928256</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>793</v>
+        <v>941</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82444</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 08, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 09, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>72323</v>
+        <v>87171</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1530</v>
+        <v>1738</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22725</v>
+        <v>24150</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3756</v>
+        <v>3791</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>756</v>
+        <v>826</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>6557</v>
+        <v>6615</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5081</v>
+        <v>5381</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2371</v>
+        <v>3631</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1463</v>
+        <v>2419</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Richard Jefferson Predicts Brandon Miller’s FIRST ALL-STAR Season</t>
+          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>947</v>
+        <v>1320</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>184492</v>
+        <v>250715</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>4683</v>
+        <v>6270</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>63075</v>
+        <v>68393</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2325</v>
+        <v>2547</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>44545</v>
+        <v>51511</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1330</v>
+        <v>1527</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>40735</v>
+        <v>45504</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>661</v>
+        <v>762</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Richard Jefferson Roasted His Game SO HARD #nba  #ajdybantsa</t>
+          <t>Why Anthony Edwards Texted His Coach An Apology #nba #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>39927</v>
+        <v>41553</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>634</v>
+        <v>1196</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>248566</v>
+        <v>296695</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1469537</v>
+        <v>1467455</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>983168</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>629142</v>
+        <v>816898</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7376275</v>
+        <v>7373966</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3317091</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>941</v>
+        <v>1086</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>82444</v>
+        <v>82435</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>169880</v>
@@ -5599,67 +5599,67 @@
         <v>174000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173086</v>
+        <v>172913</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163176</v>
+        <v>163003</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157222</v>
+        <v>157049</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153739</v>
+        <v>153566</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149254</v>
+        <v>149081</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142752</v>
+        <v>142579</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139464</v>
+        <v>139291</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135616</v>
+        <v>135443</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124595</v>
+        <v>124422</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120012</v>
+        <v>119839</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116394</v>
+        <v>116221</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115390</v>
+        <v>115217</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110295</v>
+        <v>110122</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101280</v>
+        <v>101107</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97460</v>
+        <v>97287</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93857</v>
+        <v>93684</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93355</v>
+        <v>93182</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89783</v>
+        <v>89610</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88272</v>
+        <v>88099</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88107</v>
+        <v>87934</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88025</v>
+        <v>87852</v>
       </c>
     </row>
     <row r="6">
@@ -6741,71 +6741,115 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>6</v>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6815,7 +6859,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.716</v>
+        <v>0.733</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,10 +8997,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>878649</v>
+        <v>1114679</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8928256</v>
+        <v>8923856</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4470139</v>
@@ -9166,10 +9210,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>941</v>
+        <v>1086</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>82444</v>
+        <v>82435</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>169880</v>
@@ -9384,7 +9428,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 09, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 10, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9505,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>87171</v>
+        <v>97351</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1738</v>
+        <v>1887</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9538,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24150</v>
+        <v>25437</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>614</v>
+        <v>636</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9571,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3791</v>
+        <v>3832</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>131</v>
@@ -9560,10 +9604,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>826</v>
+        <v>935</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9639,10 +9683,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>6615</v>
+        <v>6691</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9663,19 +9707,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5381</v>
+        <v>5962</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,19 +9740,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3631</v>
+        <v>5573</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9782,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2419</v>
+        <v>2820</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,10 +9815,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1320</v>
+        <v>2146</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9861,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>250715</v>
+        <v>306914</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6270</v>
+        <v>7161</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9894,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>68393</v>
+        <v>73724</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2547</v>
+        <v>2783</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9927,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51511</v>
+        <v>54703</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1527</v>
+        <v>1614</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9951,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+          <t>Why Anthony Edwards Texted His Coach An Apology #nba #minnesotatimberwolves</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45504</v>
+        <v>48087</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>762</v>
+        <v>1481</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9984,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Why Anthony Edwards Texted His Coach An Apology #nba #minnesotatimberwolves</t>
+          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>41553</v>
+        <v>47450</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1196</v>
+        <v>797</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>296695</v>
+        <v>326280</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>816898</v>
+        <v>961602</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1086</v>
+        <v>1206</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -5599,67 +5599,67 @@
         <v>174000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172913</v>
+        <v>172790</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163003</v>
+        <v>162880</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157049</v>
+        <v>156926</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153566</v>
+        <v>153443</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149081</v>
+        <v>148958</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142579</v>
+        <v>142456</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139291</v>
+        <v>139168</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135443</v>
+        <v>135320</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124422</v>
+        <v>124299</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119839</v>
+        <v>119716</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116221</v>
+        <v>116098</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115217</v>
+        <v>115094</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110122</v>
+        <v>109999</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101107</v>
+        <v>100984</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97287</v>
+        <v>97164</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93684</v>
+        <v>93561</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93182</v>
+        <v>93059</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89610</v>
+        <v>89487</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88099</v>
+        <v>87976</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87934</v>
+        <v>87811</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87852</v>
+        <v>87729</v>
       </c>
     </row>
     <row r="6">
@@ -6741,115 +6741,71 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -6859,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.733</v>
+        <v>0.746</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8997,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1114679</v>
+        <v>1289088</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9210,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1086</v>
+        <v>1206</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9428,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 10, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 11, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9505,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>97351</v>
+        <v>105435</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1887</v>
+        <v>2001</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9538,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>25437</v>
+        <v>26223</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9571,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3832</v>
+        <v>3873</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9604,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>935</v>
+        <v>1021</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>39</v>
@@ -9628,7 +9584,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>RoadTrippin 081126 CarterBryant FinalCut Video</t>
+          <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona + Got HUMBLED by Vets</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -9637,7 +9593,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
@@ -9674,19 +9630,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>6691</v>
+        <v>6952</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9707,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5962</v>
+        <v>6719</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9749,7 +9705,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5573</v>
+        <v>5683</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>82</v>
@@ -9773,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
+          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2820</v>
+        <v>3470</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9806,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
+          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2146</v>
+        <v>3242</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9861,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>306914</v>
+        <v>327924</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7161</v>
+        <v>7529</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9894,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>73724</v>
+        <v>78133</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2783</v>
+        <v>3017</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9927,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>54703</v>
+        <v>55579</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1614</v>
+        <v>1637</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9960,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>48087</v>
+        <v>54950</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1481</v>
+        <v>1710</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9993,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>47450</v>
+        <v>48577</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>797</v>
+        <v>813</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>326280</v>
+        <v>351489</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>961602</v>
+        <v>1065329</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1206</v>
+        <v>1349</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -5599,67 +5599,67 @@
         <v>174000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172790</v>
+        <v>172701</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162880</v>
+        <v>162791</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156926</v>
+        <v>156837</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153443</v>
+        <v>153354</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148958</v>
+        <v>148869</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142456</v>
+        <v>142367</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139168</v>
+        <v>139079</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135320</v>
+        <v>135231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124299</v>
+        <v>124210</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119716</v>
+        <v>119627</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116098</v>
+        <v>116009</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115094</v>
+        <v>115005</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109999</v>
+        <v>109910</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100984</v>
+        <v>100895</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97164</v>
+        <v>97075</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93561</v>
+        <v>93472</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93059</v>
+        <v>92970</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89487</v>
+        <v>89398</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87976</v>
+        <v>87887</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87811</v>
+        <v>87722</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87729</v>
+        <v>87640</v>
       </c>
     </row>
     <row r="6">
@@ -6742,40 +6742,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>27</v>
@@ -6787,7 +6787,7 @@
         <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1289088</v>
+        <v>1418167</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1206</v>
+        <v>1349</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 11, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 12, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>105435</v>
+        <v>110559</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2001</v>
+        <v>2079</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9485,19 +9485,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
+          <t>“I DON’T BELONG HERE” Carter Bryant’s Rookie Struggles + Devin Vassell’s BRUTAL NBA Welcome</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26223</v>
+        <v>40426</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>648</v>
+        <v>1362</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
+          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3873</v>
+        <v>26692</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>133</v>
+        <v>663</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Olivia Miles Drops 28, Minnesota Beats Indiana 108-100: 'No Crack In This Team</t>
+          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1021</v>
+        <v>3909</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona + Got HUMBLED by Vets</t>
+          <t>Olivia Miles Drops 28, Minnesota Beats Indiana 108-100: 'No Crack In This Team</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3</v>
+        <v>1062</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>6952</v>
+        <v>7301</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6719</v>
+        <v>6742</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>93</v>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5683</v>
+        <v>5750</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
+          <t>“I DON’T BELONG Here” Carter Bryant on Devin Vassell’s BRUTAL NBA Welcome</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3470</v>
+        <v>4760</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE”</t>
+          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3242</v>
+        <v>3957</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>327924</v>
+        <v>331331</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7529</v>
+        <v>7596</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
+          <t>The Real Reason Gilbert Arenas Went In The 2nd Round 😂 #nba #RichardJefferson #carterbryant</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>78133</v>
+        <v>131782</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3017</v>
+        <v>4215</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>55579</v>
+        <v>79589</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1637</v>
+        <v>3080</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>54950</v>
+        <v>58463</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1710</v>
+        <v>1803</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>If You Could STEAL Any NBA Skill, Who Are You Taking? #nba #giannisantetokounmpo #brandonmiller</t>
+          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>48577</v>
+        <v>56300</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>813</v>
+        <v>1662</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>351489</v>
+        <v>369904</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1065329</v>
+        <v>1138877</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1349</v>
+        <v>1465</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -5599,67 +5599,67 @@
         <v>174000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172701</v>
+        <v>172643</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162791</v>
+        <v>162733</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156837</v>
+        <v>156779</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153354</v>
+        <v>153296</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148869</v>
+        <v>148811</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142367</v>
+        <v>142309</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139079</v>
+        <v>139021</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135231</v>
+        <v>135173</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124210</v>
+        <v>124152</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119627</v>
+        <v>119569</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116009</v>
+        <v>115951</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115005</v>
+        <v>114947</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109910</v>
+        <v>109852</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100895</v>
+        <v>100837</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97075</v>
+        <v>97017</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93472</v>
+        <v>93414</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92970</v>
+        <v>92912</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89398</v>
+        <v>89340</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87887</v>
+        <v>87829</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87722</v>
+        <v>87664</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87640</v>
+        <v>87582</v>
       </c>
     </row>
     <row r="6">
@@ -6742,40 +6742,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>53</v>
-      </c>
       <c r="G8" s="7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>24</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>30</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>27</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.751</v>
+        <v>0.754</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1418167</v>
+        <v>1510246</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1349</v>
+        <v>1465</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 12, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 13, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>110559</v>
+        <v>114610</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2079</v>
+        <v>2140</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40426</v>
+        <v>70126</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1362</v>
+        <v>2095</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26692</v>
+        <v>27211</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3909</v>
+        <v>3968</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>133</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1062</v>
+        <v>1086</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9630,19 +9630,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Kelly Olynyk COOKED Carter Bryant for Two Straight Weeks in Spurs Practice</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>7301</v>
+        <v>15874</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9663,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
+          <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6742</v>
+        <v>8298</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,19 +9696,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5750</v>
+        <v>7443</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>“I DON’T BELONG Here” Carter Bryant on Devin Vassell’s BRUTAL NBA Welcome</t>
+          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>4760</v>
+        <v>6754</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>The REAL Reason Anthony Edwards Walked Away From Minnesota’s Bench</t>
+          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3957</v>
+        <v>5790</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>331331</v>
+        <v>332722</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7596</v>
+        <v>7623</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>131782</v>
+        <v>245440</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4215</v>
+        <v>7849</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>79589</v>
+        <v>80523</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3080</v>
+        <v>3109</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>58463</v>
+        <v>59899</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1803</v>
+        <v>1858</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Telling Lamar Jackson to SLOW DOWN as a Rookie #NFL #Ravens</t>
+          <t>What Coach Pop Is REALLY Like Behind Closed Doors #sanantoniospurs #nba #basketball</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>56300</v>
+        <v>58708</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1662</v>
+        <v>1693</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>369904</v>
+        <v>428290</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1138877</v>
+        <v>1349204</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1465</v>
+        <v>1595</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>174000</v>
+        <v>175000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>172643</v>
+        <v>173395</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>162733</v>
+        <v>163485</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>156779</v>
+        <v>157531</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153296</v>
+        <v>154048</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>148811</v>
+        <v>149563</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142309</v>
+        <v>143061</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139021</v>
+        <v>139773</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135173</v>
+        <v>135925</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124152</v>
+        <v>124904</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>119569</v>
+        <v>120321</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>115951</v>
+        <v>116703</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>114947</v>
+        <v>115699</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>109852</v>
+        <v>110604</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100837</v>
+        <v>101589</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97017</v>
+        <v>97769</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93414</v>
+        <v>94166</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92912</v>
+        <v>93664</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89340</v>
+        <v>90092</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87829</v>
+        <v>88581</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87664</v>
+        <v>88416</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87582</v>
+        <v>88334</v>
       </c>
     </row>
     <row r="6">
@@ -6742,52 +6742,52 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>57</v>
-      </c>
       <c r="G8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>11</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.754</v>
+        <v>0.758</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1510246</v>
+        <v>1779089</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1465</v>
+        <v>1595</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 13, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 14, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>114610</v>
+        <v>116906</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2140</v>
+        <v>2194</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>70126</v>
+        <v>87753</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2095</v>
+        <v>2469</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9518,19 +9518,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
+          <t>Rajon Rondo Says He’s READY to Be an NBA Head Coach + What He Learned From the Pelicans Interview</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27211</v>
+        <v>36863</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>675</v>
+        <v>844</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
+          <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3968</v>
+        <v>27628</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>133</v>
+        <v>683</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Olivia Miles Drops 28, Minnesota Beats Indiana 108-100: 'No Crack In This Team</t>
+          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1086</v>
+        <v>4007</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>15874</v>
+        <v>28894</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8298</v>
+        <v>17739</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,19 +9696,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Pop Told Carter Bryant His Jab Step Was The WORST He’s Seen</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>7443</v>
+        <v>8573</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6754</v>
+        <v>7447</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Brandon Miller Says The Media Got LaMelo Ball’s Leadership WRONG</t>
+          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>5790</v>
+        <v>6766</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>332722</v>
+        <v>333620</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7623</v>
+        <v>7645</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>245440</v>
+        <v>293398</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7849</v>
+        <v>9464</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>80523</v>
+        <v>81003</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3109</v>
+        <v>3129</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9907,19 +9907,19 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Why Anthony Edwards Texted His Coach An Apology #nba #minnesotatimberwolves</t>
+          <t>When You Realize You Have To Guard Grown Men in the NBA #basketball #rookie #sanantoniospurs</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>59899</v>
+        <v>79300</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1858</v>
+        <v>2246</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>58708</v>
+        <v>71928</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1693</v>
+        <v>2016</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>428290</v>
+        <v>492141</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1349204</v>
+        <v>1611659</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1595</v>
+        <v>1787</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -5599,67 +5599,67 @@
         <v>175000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173395</v>
+        <v>173099</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163485</v>
+        <v>163189</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157531</v>
+        <v>157235</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>154048</v>
+        <v>153752</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149563</v>
+        <v>149267</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>143061</v>
+        <v>142765</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139773</v>
+        <v>139477</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135925</v>
+        <v>135629</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124904</v>
+        <v>124608</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120321</v>
+        <v>120025</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116703</v>
+        <v>116407</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115699</v>
+        <v>115403</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110604</v>
+        <v>110308</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101589</v>
+        <v>101293</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97769</v>
+        <v>97473</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>94166</v>
+        <v>93870</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93664</v>
+        <v>93368</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>90092</v>
+        <v>89796</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88581</v>
+        <v>88285</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88416</v>
+        <v>88120</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88334</v>
+        <v>88038</v>
       </c>
     </row>
     <row r="6">
@@ -6742,28 +6742,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>56</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>26</v>
@@ -6772,16 +6772,16 @@
         <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>31</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.758</v>
+        <v>0.765</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1779089</v>
+        <v>2105587</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1595</v>
+        <v>1787</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 14, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 15, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>116906</v>
+        <v>118748</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2194</v>
+        <v>2228</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>87753</v>
+        <v>97515</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2469</v>
+        <v>2643</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36863</v>
+        <v>54168</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>844</v>
+        <v>1182</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>27628</v>
+        <v>28105</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Terrell Suggs: Lamar Jackson Needs HELP, Aaron Donald CAN Return &amp; Mahomes Wins MVP</t>
+          <t>“I'll Follow You. Just Lead Me." Inside Teresa Weatherspoon and Chennedy Carter's Bond</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>4007</v>
+        <v>8715</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>28894</v>
+        <v>41628</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>470</v>
+        <v>621</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>17739</v>
+        <v>29006</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>270</v>
+        <v>445</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>8573</v>
+        <v>12018</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>7447</v>
+        <v>7473</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>6766</v>
+        <v>6773</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>93</v>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>333620</v>
+        <v>334846</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7645</v>
+        <v>7685</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>293398</v>
+        <v>311988</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9464</v>
+        <v>10003</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
+          <t>Rajon Rondo Exposes RJ’s Worst Teammate Moment #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>81003</v>
+        <v>197687</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3129</v>
+        <v>7329</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>79300</v>
+        <v>96531</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2246</v>
+        <v>2713</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>What Coach Pop Is REALLY Like Behind Closed Doors #sanantoniospurs #nba #basketball</t>
+          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>71928</v>
+        <v>81403</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2016</v>
+        <v>3145</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>492141</v>
+        <v>587136</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1611659</v>
+        <v>1747692</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1787</v>
+        <v>1906</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>175000</v>
+        <v>176000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173099</v>
+        <v>173813</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163189</v>
+        <v>163903</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157235</v>
+        <v>157949</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>153752</v>
+        <v>154466</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149267</v>
+        <v>149981</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>142765</v>
+        <v>143479</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139477</v>
+        <v>140191</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135629</v>
+        <v>136343</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124608</v>
+        <v>125322</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120025</v>
+        <v>120739</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116407</v>
+        <v>117121</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115403</v>
+        <v>116117</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110308</v>
+        <v>111022</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101293</v>
+        <v>102007</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97473</v>
+        <v>98187</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>93870</v>
+        <v>94584</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93368</v>
+        <v>94082</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>89796</v>
+        <v>90510</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88285</v>
+        <v>88999</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88120</v>
+        <v>88834</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88038</v>
+        <v>88752</v>
       </c>
     </row>
     <row r="6">
@@ -6742,37 +6742,37 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>51</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>23</v>
@@ -6781,7 +6781,7 @@
         <v>29</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>31</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.765</v>
+        <v>0.748</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2105587</v>
+        <v>2336734</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1787</v>
+        <v>1906</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 15, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 16, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>118748</v>
+        <v>120352</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2228</v>
+        <v>2248</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>97515</v>
+        <v>101886</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2643</v>
+        <v>2728</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>54168</v>
+        <v>68240</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1182</v>
+        <v>1488</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28105</v>
+        <v>28479</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8715</v>
+        <v>12865</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>357</v>
+        <v>482</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9630,19 +9630,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Kelly Olynyk COOKED Carter Bryant for Two Straight Weeks in Spurs Practice</t>
+          <t>Why Rajon Rondo Calls Philadelphia a BRILLIANT Move for LeBron</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>41628</v>
+        <v>98407</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>621</v>
+        <v>1991</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9663,19 +9663,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona</t>
+          <t>Kelly Olynyk COOKED Carter Bryant for Two Straight Weeks in Spurs Practice</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>29006</v>
+        <v>48820</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>445</v>
+        <v>692</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Pop Told Carter Bryant His Jab Step Was The WORST He’s Seen</t>
+          <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12018</v>
+        <v>34753</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>202</v>
+        <v>538</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Pop Told Carter Bryant His Jab Step Was The WORST He’s Seen</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>7473</v>
+        <v>13713</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Why Making The PLAYOFFS Could Cost AJ Dybantsa Rookie Of The Year</t>
+          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>6773</v>
+        <v>7509</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>334846</v>
+        <v>338431</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7685</v>
+        <v>7755</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>311988</v>
+        <v>327100</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10003</v>
+        <v>10506</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>197687</v>
+        <v>319681</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7329</v>
+        <v>12899</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>96531</v>
+        <v>114608</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2713</v>
+        <v>3315</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Why the Timberwolves NEEDED LaMelo Ball 🏀👀 #NBA #anthonyedwards #basketball</t>
+          <t>What Coach Pop Is REALLY Like Behind Closed Doors #sanantoniospurs #nba #basketball</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>81403</v>
+        <v>89793</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3145</v>
+        <v>2525</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>587136</v>
+        <v>661197</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1747692</v>
+        <v>2048765</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1906</v>
+        <v>2035</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -5596,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>176000</v>
+        <v>177000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173813</v>
+        <v>174423</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163903</v>
+        <v>164513</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157949</v>
+        <v>158559</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>154466</v>
+        <v>155076</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149981</v>
+        <v>150591</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>143479</v>
+        <v>144089</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>140191</v>
+        <v>140801</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>136343</v>
+        <v>136953</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>125322</v>
+        <v>125932</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120739</v>
+        <v>121349</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>117121</v>
+        <v>117731</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>116117</v>
+        <v>116727</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>111022</v>
+        <v>111632</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102007</v>
+        <v>102617</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>98187</v>
+        <v>98797</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>94584</v>
+        <v>95194</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>94082</v>
+        <v>94692</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>90510</v>
+        <v>91120</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88999</v>
+        <v>89609</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88834</v>
+        <v>89444</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88752</v>
+        <v>89362</v>
       </c>
     </row>
     <row r="6">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>51</v>
@@ -6754,37 +6754,37 @@
         <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>53</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>21</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.748</v>
+        <v>0.755</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2336734</v>
+        <v>2711997</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1906</v>
+        <v>2035</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9384,7 +9384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 16, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 17, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>120352</v>
+        <v>122265</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2248</v>
+        <v>2267</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>101886</v>
+        <v>105755</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2728</v>
+        <v>2795</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>68240</v>
+        <v>80458</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1488</v>
+        <v>1714</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28479</v>
+        <v>28836</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>12865</v>
+        <v>14682</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>482</v>
+        <v>553</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>98407</v>
+        <v>162317</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1991</v>
+        <v>2961</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>48820</v>
+        <v>53907</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>692</v>
+        <v>727</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>34753</v>
+        <v>39801</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>538</v>
+        <v>587</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>13713</v>
+        <v>14990</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>7509</v>
+        <v>7543</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>181</v>
@@ -9808,19 +9808,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>NBA Rookie’s First Big Flex Isn’t What You Think… #ajdybantsa #washingtonwizards #nba</t>
+          <t>Rajon Rondo Exposes RJ’s Worst Teammate Moment #nba #basketball</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>338431</v>
+        <v>392351</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7755</v>
+        <v>16548</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>327100</v>
+        <v>339055</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10506</v>
+        <v>10809</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9874,19 +9874,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Rajon Rondo Exposes RJ’s Worst Teammate Moment #nba #basketball</t>
+          <t>Rondo Reveals The SCARIEST LeBron James Scenario #Lebron #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>319681</v>
+        <v>128718</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>12899</v>
+        <v>5339</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>114608</v>
+        <v>126187</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3315</v>
+        <v>3691</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>89793</v>
+        <v>97126</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2525</v>
+        <v>2728</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>661197</v>
+        <v>658039</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1467455</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2048765</v>
+        <v>2042936</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>7373966</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>82435</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.826</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2711997</v>
+        <v>2703004</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>8923856</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>82435</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>122265</v>
+        <v>122720</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2267</v>
+        <v>2275</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>105755</v>
+        <v>106595</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2795</v>
+        <v>2815</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>80458</v>
+        <v>83120</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1714</v>
+        <v>1775</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28836</v>
+        <v>28912</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>14682</v>
+        <v>15155</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>162317</v>
+        <v>173599</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2961</v>
+        <v>3149</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>53907</v>
+        <v>54687</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>39801</v>
+        <v>40566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>14990</v>
+        <v>15158</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9762,19 +9762,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>AI or CP3: Channing PICKS a Winner, Top 5 SNUBS Luka &amp; Kobe's Aura Lives On</t>
+          <t>Rajon Rondo Wants the 2008 Celtics Reunion to Last a MONTH</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>7543</v>
+        <v>7939</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>392351</v>
+        <v>400224</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>16548</v>
+        <v>17071</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>339055</v>
+        <v>341845</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10809</v>
+        <v>10942</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>128718</v>
+        <v>172678</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5339</v>
+        <v>8243</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>126187</v>
+        <v>128427</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3691</v>
+        <v>3788</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>97126</v>
+        <v>98194</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2728</v>
+        <v>2780</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>51</v>
       </c>
       <c r="D8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>55</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>21</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>122720</v>
+        <v>122879</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>106595</v>
+        <v>106878</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2815</v>
+        <v>2823</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>83120</v>
+        <v>83836</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28912</v>
+        <v>28965</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>15155</v>
+        <v>15275</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>173599</v>
+        <v>176960</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3149</v>
+        <v>3191</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>54687</v>
+        <v>54992</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>40566</v>
+        <v>41037</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>15158</v>
+        <v>15286</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>239</v>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>7939</v>
+        <v>8202</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>400224</v>
+        <v>402716</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>17071</v>
+        <v>17232</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>341845</v>
+        <v>342942</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10942</v>
+        <v>10959</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>172678</v>
+        <v>184236</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8243</v>
+        <v>8937</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>128427</v>
+        <v>129059</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3788</v>
+        <v>3814</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>98194</v>
+        <v>98676</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2780</v>
+        <v>2790</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,9 +119,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -696,7 +693,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -768,71 +765,115 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>658039</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>1467455</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>983168</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>697914</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>790809</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>999377</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>456937</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>733899</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>1819209</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>1237011</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>951387</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>461276</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>1296821</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>1515762</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>606682</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>629557</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>115398</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>322450</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>87239</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>67472</v>
-      </c>
-      <c r="V5" s="7" t="n">
-        <v>48198</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>114534</v>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -841,71 +882,115 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>2042936</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>7373966</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>3317091</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2062452</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>2731804</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>2437458</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>1412041</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>1021398</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>1102899</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>920589</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>542576</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>390738</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>1348061</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>2030353</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>545861</v>
-      </c>
-      <c r="Q6" s="7" t="n">
-        <v>130006</v>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v>89465</v>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>90474</v>
-      </c>
-      <c r="T6" s="7" t="n">
-        <v>56970</v>
-      </c>
-      <c r="U6" s="7" t="n">
-        <v>34237</v>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>24015</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>17758</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -914,71 +999,115 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2029</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>82435</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>169880</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>164514</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>178277</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>211738</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>209927</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>90638</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>365</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>405</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>381</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>220</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>386</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>697</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>37296</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>4972</v>
-      </c>
-      <c r="R7" s="7" t="n">
-        <v>7173</v>
-      </c>
-      <c r="S7" s="7" t="n">
-        <v>1399</v>
-      </c>
-      <c r="T7" s="7" t="n">
-        <v>78402</v>
-      </c>
-      <c r="U7" s="7" t="n">
-        <v>3965</v>
-      </c>
-      <c r="V7" s="7" t="n">
-        <v>11199</v>
-      </c>
-      <c r="W7" s="7" t="n">
-        <v>40604</v>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -987,102 +1116,102 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>23305</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>23182</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>25288</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>24712</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>22848</v>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1392,7 +1521,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -2110,112 +2239,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2227,112 +2356,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2344,112 +2473,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2695,112 +2824,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2812,112 +2941,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2929,112 +3058,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3280,112 +3409,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3397,112 +3526,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3514,112 +3643,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3865,112 +3994,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3982,112 +4111,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4099,112 +4228,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4450,112 +4579,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4567,112 +4696,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4684,112 +4813,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4918,112 +5047,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5035,112 +5164,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5152,112 +5281,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5599,67 +5728,67 @@
         <v>177000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>174423</v>
+        <v>173459</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>164513</v>
+        <v>163549</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>158559</v>
+        <v>157595</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>155076</v>
+        <v>154112</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>150591</v>
+        <v>149627</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>144089</v>
+        <v>143125</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>140801</v>
+        <v>139837</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>136953</v>
+        <v>135989</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>125932</v>
+        <v>124968</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>121349</v>
+        <v>120385</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>117731</v>
+        <v>116767</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>116727</v>
+        <v>115763</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>111632</v>
+        <v>110668</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102617</v>
+        <v>101653</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>98797</v>
+        <v>97833</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>95194</v>
+        <v>94230</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>94692</v>
+        <v>93728</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>91120</v>
+        <v>90156</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89609</v>
+        <v>88645</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89444</v>
+        <v>88480</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>89362</v>
+        <v>88398</v>
       </c>
     </row>
     <row r="6">
@@ -5668,91 +5797,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="8">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="8">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="8">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="8">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="8">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="8">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="8">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="8">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="8">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="8">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="8">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="8">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5771,112 +5900,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5888,112 +6017,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6100,91 +6229,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="8">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="8">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="8">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="8">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="8">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="8">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="8">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="8">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="8">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="8">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="8">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="8">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="8">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="8">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6741,70 +6870,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="D8" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="L8" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="K8" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="R8" s="7" t="n">
+      <c r="R8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="S8" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="T8" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="U8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="7" t="n">
+      <c r="V8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="W8" s="7" t="n">
+      <c r="W8" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6814,71 +6943,115 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R9" s="12" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="S9" s="12" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="U9" s="12" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="V9" s="12" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.103</v>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -8237,27 +8410,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>VIEWS PER</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>TAPED + LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="14" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8377,112 +8550,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8606,112 +8779,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8835,112 +9008,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8952,95 +9125,139 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>2703004</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>8923856</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4470139</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>2924880</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>3700890</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>3648573</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>2078905</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1845935</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>2922473</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>2158005</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>1494344</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>852234</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>2645268</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>3546812</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>1189839</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>764535</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>212036</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>414323</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>222611</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>105674</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>83412</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>172896</v>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>LIVES</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9165,71 +9382,115 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>82435</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>169880</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>164514</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>178277</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>211738</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>209927</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>90638</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>365</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>405</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>381</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>220</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>386</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>697</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>37296</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>4972</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>7173</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>1399</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>78402</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>3965</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>11199</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>40604</v>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -9384,7 +9645,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Aug 01 – Aug 17, 2026</t>
+          <t>⭐ BEST OF — Aug 01 – Aug 18, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9395,83 +9656,83 @@
       <c r="G1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Views</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Likes</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Show</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>★ TOP FULL EPISODES</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Chris Finch: “We Did Anthony Edwards A DISSERVICE” + Why LaMelo Changes Everything</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>122879</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>2278</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="D5" s="8" t="n">
+        <v>123838</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>2290</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9483,7 +9744,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>“I DON’T BELONG HERE” Carter Bryant’s Rookie Struggles + Devin Vassell’s BRUTAL NBA Welcome</t>
         </is>
@@ -9494,10 +9755,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>106878</v>
+        <v>108744</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2823</v>
+        <v>2853</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9511,33 +9772,33 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Rajon Rondo Says He’s READY to Be an NBA Head Coach + What He Learned From the Pelicans Interview</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>83836</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="8" t="n">
+        <v>89219</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1863</v>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9549,7 +9810,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>A Healthy Charlotte Team Is DANGEROUS! Brandon Miller’s Next Leap + Mike Miller Surprise</t>
         </is>
@@ -9560,10 +9821,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28965</v>
+        <v>29126</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9577,79 +9838,79 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>“I'll Follow You. Just Lead Me." Inside Teresa Weatherspoon and Chennedy Carter's Bond</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>15275</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>573</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D9" s="8" t="n">
+        <v>16087</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>597</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Why Rajon Rondo Calls Philadelphia a BRILLIANT Move for LeBron</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>176960</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>3191</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="D12" s="8" t="n">
+        <v>199825</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>3437</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9661,7 +9922,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Kelly Olynyk COOKED Carter Bryant for Two Straight Weeks in Spurs Practice</t>
         </is>
@@ -9672,10 +9933,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>54992</v>
+        <v>56913</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9689,33 +9950,33 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Carter Bryant PAID for Gilbert Arenas' Sins at Arizona</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>41037</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>612</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="D14" s="8" t="n">
+        <v>44538</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>643</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9727,7 +9988,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Pop Told Carter Bryant His Jab Step Was The WORST He’s Seen</t>
         </is>
@@ -9738,10 +9999,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>15286</v>
+        <v>15864</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9755,79 +10016,79 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Rajon Rondo Wants the 2008 Celtics Reunion to Last a MONTH</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>8202</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="D16" s="8" t="n">
+        <v>9120</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Rajon Rondo Exposes RJ’s Worst Teammate Moment #nba #basketball</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
-        <v>402716</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>17232</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="D19" s="8" t="n">
+        <v>424076</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>18298</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9839,7 +10100,7 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>The Real Reason Gilbert Arenas Went In The 2nd Round 😂 #nba #RichardJefferson #carterbryant</t>
         </is>
@@ -9850,10 +10111,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>342942</v>
+        <v>350350</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10959</v>
+        <v>11166</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9867,33 +10128,33 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Rondo Reveals The SCARIEST LeBron James Scenario #Lebron #nba #basketball</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>184236</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>8937</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="D21" s="8" t="n">
+        <v>257665</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9905,7 +10166,7 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>When You Realize You Have To Guard Grown Men in the NBA #basketball #rookie #sanantoniospurs</t>
         </is>
@@ -9916,10 +10177,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>129059</v>
+        <v>133921</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3814</v>
+        <v>3979</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9933,40 +10194,40 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>What Coach Pop Is REALLY Like Behind Closed Doors #sanantoniospurs #nba #basketball</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>98676</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>2790</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>The 44-0 High School Team Nobody Could Beat #basketball #oakhill</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>106063</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>3104</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +119,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -693,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -765,115 +768,71 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B5" s="7" t="n">
+        <v>920364</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>1467455</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>983168</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>697914</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>790809</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>999377</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>456937</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>733899</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>1819209</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1237011</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>951387</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>461276</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>1296821</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>1515762</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>606682</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>629557</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>115398</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>322450</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>87239</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>67472</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>48198</v>
+      </c>
+      <c r="W5" s="7" t="n">
+        <v>114534</v>
       </c>
     </row>
     <row r="6">
@@ -882,115 +841,71 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B6" s="7" t="n">
+        <v>2676635</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7373966</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3317091</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2062452</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2731804</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>2437458</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1412041</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1021398</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>1102899</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>920589</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>542576</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>390738</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>1348061</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>2030353</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>545861</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>130006</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>89465</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>90474</v>
+      </c>
+      <c r="T6" s="7" t="n">
+        <v>56970</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>34237</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>24015</v>
+      </c>
+      <c r="W6" s="7" t="n">
+        <v>17758</v>
       </c>
     </row>
     <row r="7">
@@ -999,115 +914,71 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>2370</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>82435</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>169880</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>164514</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>178277</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>211738</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>209927</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>90638</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>365</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>405</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>381</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>386</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>697</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>37296</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>4972</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>7173</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>1399</v>
+      </c>
+      <c r="T7" s="7" t="n">
+        <v>78402</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>3965</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>11199</v>
+      </c>
+      <c r="W7" s="7" t="n">
+        <v>40604</v>
       </c>
     </row>
     <row r="8">
@@ -1116,102 +987,102 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>23305</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>23182</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>25288</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>24712</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>22848</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1521,7 +1392,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>12</v>
@@ -2239,112 +2110,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2356,112 +2227,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2473,112 +2344,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2824,112 +2695,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2941,112 +2812,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3058,112 +2929,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3409,112 +3280,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3526,112 +3397,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3643,112 +3514,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3994,112 +3865,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4111,112 +3982,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4228,112 +4099,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4579,112 +4450,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4696,112 +4567,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4813,112 +4684,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5047,112 +4918,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5164,112 +5035,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5281,112 +5152,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5725,70 +5596,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>177000</v>
+        <v>178000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>173459</v>
+        <v>173699</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>163549</v>
+        <v>163789</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>157595</v>
+        <v>157835</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>154112</v>
+        <v>154352</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>149627</v>
+        <v>149867</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>143125</v>
+        <v>143365</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>139837</v>
+        <v>140077</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>135989</v>
+        <v>136229</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>124968</v>
+        <v>125208</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>120385</v>
+        <v>120625</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>116767</v>
+        <v>117007</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115763</v>
+        <v>116003</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>110668</v>
+        <v>110908</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>101653</v>
+        <v>101893</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>97833</v>
+        <v>98073</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>94230</v>
+        <v>94470</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93728</v>
+        <v>93968</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>90156</v>
+        <v>90396</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88645</v>
+        <v>88885</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88480</v>
+        <v>88720</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88398</v>
+        <v>88638</v>
       </c>
     </row>
     <row r="6">
@@ -5797,91 +5668,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="7">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5900,112 +5771,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6017,112 +5888,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6229,91 +6100,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="7">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="7">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="7">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="7">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6870,70 +6741,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C8" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" s="8" t="n">
+      <c r="P8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="O8" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+      <c r="Q8" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6943,115 +6814,71 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="12" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="T9" s="12" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="U9" s="12" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="10">
@@ -8410,27 +8237,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>VIEWS PER</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>TAPED + LIVE VIEWS</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8550,112 +8377,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8779,112 +8606,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9008,112 +8835,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9125,139 +8952,95 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="6" t="n">
+        <v>3599369</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>8923856</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>4470139</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2924880</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>3700890</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3648573</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>2078905</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1845935</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>2922473</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>2158005</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>1494344</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>8522